--- a/data/comercios_territorio_sp.xlsx
+++ b/data/comercios_territorio_sp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\as\Documents\00_TESIS\meu_tesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC39B647-99AC-440A-90FE-E46CB98ED725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B99F21D-094A-4959-A234-9EE112C76D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{7FC3CCF3-7BCA-42E8-BEEE-4B41A7F93BBF}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="392">
   <si>
     <t>Calle</t>
   </si>
@@ -245,9 +245,6 @@
     <t>Kiosco Mini Market</t>
   </si>
   <si>
-    <t>https://maps.google.com/maps?q=-34.59164810180664%2C-58.37923812866211&amp;z=17&amp;hl=es</t>
-  </si>
-  <si>
     <t>https://maps.google.com/maps?q=-34.59185791015625%2C-58.378448486328125&amp;z=17&amp;hl=es</t>
   </si>
   <si>
@@ -257,9 +254,6 @@
     <t>https://www.google.com/maps?q=-34.5927734375,-58.376285552978516&amp;z=17&amp;hl=es</t>
   </si>
   <si>
-    <t>https://www.google.com/maps?q=-34.5940055847168,-58.379276275634766&amp;z=17&amp;hl=es</t>
-  </si>
-  <si>
     <t>Supermercado Jumbo</t>
   </si>
   <si>
@@ -290,21 +284,12 @@
     <t>https://www.google.com/maps?q=-34.59343338012695,-58.39544677734375&amp;z=17&amp;hl=es</t>
   </si>
   <si>
-    <t>https://www.google.com/maps?q=-34.59342575073242,-58.394893646240234&amp;z=17&amp;hl=es</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps?q=-34.59400939941406,-58.39198303222656&amp;z=17&amp;hl=es</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps?q=-34.594173431396484,-58.390567779541016&amp;z=17&amp;hl=es</t>
   </si>
   <si>
     <t>https://www.google.com/maps?q=-34.592796325683594,-58.385894775390625&amp;z=17&amp;hl=es</t>
   </si>
   <si>
-    <t>https://www.google.com/maps?q=-34.5927619934082,-58.383609771728516&amp;z=17&amp;hl=es</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps?q=-34.59281921386719,-58.38087463378906&amp;z=17&amp;hl=es</t>
   </si>
   <si>
@@ -323,9 +308,6 @@
     <t>https://www.google.com/maps?q=-34.5966682434082,-58.380836486816406&amp;z=17&amp;hl=es</t>
   </si>
   <si>
-    <t>https://www.google.com/maps?q=-34.59677505493164,-58.384918212890625&amp;z=17&amp;hl=es</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps?q=-34.597015380859375,-58.386722564697266&amp;z=17&amp;hl=es</t>
   </si>
   <si>
@@ -386,9 +368,6 @@
     <t>https://www.google.com/maps?q=-34.59111022949219,-58.39280319213867&amp;z=17&amp;hl=es</t>
   </si>
   <si>
-    <t>https://www.google.com/maps?q=-34.59056854248047,-58.39310073852539&amp;z=17&amp;hl=es</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps?q=-34.59097671508789,-58.39504623413086&amp;z=17&amp;hl=es</t>
   </si>
   <si>
@@ -437,9 +416,6 @@
     <t>POINT(-58.39287294117505 -34.590880534397805)</t>
   </si>
   <si>
-    <t>POINT(-58.39308461049117 -34.59035649754325)</t>
-  </si>
-  <si>
     <t>POINT(-58.394997923984896 -34.59080002768448)</t>
   </si>
   <si>
@@ -530,18 +506,12 @@
     <t>POINT(-58.38743011233964 -34.58733888770553)</t>
   </si>
   <si>
-    <t>POINT(-58.37921128165579 -34.59146259690959)</t>
-  </si>
-  <si>
     <t>POINT(-58.3784753258331 -34.59167239737799)</t>
   </si>
   <si>
     <t>POINT(-58.37626951049113 -34.592587899421325)</t>
   </si>
   <si>
-    <t>POINT(-58.37932458350407 -34.5938112702195)</t>
-  </si>
-  <si>
     <t>POINT(-58.38104853932667 -34.59403893884416)</t>
   </si>
   <si>
@@ -563,21 +533,12 @@
     <t>POINT(-58.395484354668504 -34.59323906888116)</t>
   </si>
   <si>
-    <t>POINT(-58.39490969699758 -34.59323146886349)</t>
-  </si>
-  <si>
-    <t>POINT(-58.394856052820174 -34.59323146886349)</t>
-  </si>
-  <si>
     <t>POINT(-58.39057316816209 -34.5940408941348)</t>
   </si>
   <si>
     <t>POINT(-58.38591089699757 -34.59260196739151)</t>
   </si>
   <si>
-    <t>POINT(-58.3835937104911 -34.59249701059969)</t>
-  </si>
-  <si>
     <t>POINT(-58.380826323984714 -34.5926955240478)</t>
   </si>
   <si>
@@ -596,9 +557,6 @@
     <t>POINT(-58.38085259699755 -34.59652686644874)</t>
   </si>
   <si>
-    <t>POINT(-58.3849128393265 -34.59658077669623)</t>
-  </si>
-  <si>
     <t>POINT(-58.38674942583296 -34.59683874052231)</t>
   </si>
   <si>
@@ -863,9 +821,6 @@
     <t>cadena</t>
   </si>
   <si>
-    <t>https://www.google.com/maps?q=-34.58963394165039,-58.394901275634766&amp;z=17&amp;hl=es</t>
-  </si>
-  <si>
     <t>POINT(-58.394901 -34.589634)</t>
   </si>
   <si>
@@ -1230,6 +1185,60 @@
   </si>
   <si>
     <t>MEDIANA 12/06/25 A 11/12/25</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Marcelo+Torcuato+de+Alvear+1243,+C1058AAS+Cdad.+Aut%C3%B3noma+de+Buenos+Aires/@-34.5968983,-58.3850364,21z/data=!4m12!1m5!3m4!2zMzTCsDM1JzQ4LjQiUyA1OMKwMjMnMDUuNyJX!8m2!3d-34.5967751!4d-58.3849182!3m5!1s0x95bccab843ffe669:0xae79508bd3a18136!8m2!3d-34.5968551!4d-58.3848858!16s%2Fg%2F11c87kq9r3?hl=es&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>POINT(-58.384884525667495 -34.59684306658751)</t>
+  </si>
+  <si>
+    <t>POINT(-58.3858986436714 -34.59276756045055)</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@-34.5927433,-58.3859499,21z?hl=es&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@-34.5928081,-58.383655,21z?hl=es&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>POINT(-58.383572137063965 -34.59277833763642)</t>
+  </si>
+  <si>
+    <t>POINT(-58.39314941110279 -34.59060088690933)</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@-34.5905887,-58.3932738,21z?hl=es&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>POINT(-58.39462362708994 -34.589355170420546)</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Carnicer%C3%ADa+Rub%C3%A9n/@-34.5895037,-58.394738,21z/data=!4m6!3m5!1s0x95bcca987766253f:0x9a08e33acc0fc017!8m2!3d-34.589303!4d-58.394544!16s%2Fg%2F11b6v4jlsn?hl=es&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>POINT( -58.39491161951106 -34.593480469021166)</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@-34.5934683,-58.3950078,21z?hl=es&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>POINT(-58.39206286569123 -34.59404104867657)</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@-34.5940444,-58.3920163,21z?hl=es&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>POINT(-58.37937322983343 -34.5941396898721)</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@-34.5940337,-58.3793313,21z?hl=es&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@-34.5917245,-58.3792782,21z?hl=es&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>POINT(-58.37935967209949 -34.59165991469645)</t>
   </si>
 </sst>
 </file>
@@ -1766,19 +1775,19 @@
   <sheetData>
     <row r="1" spans="1:26" s="4" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>54</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -1799,7 +1808,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
@@ -1829,16 +1838,16 @@
         <v>14</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>16</v>
@@ -1852,7 +1861,7 @@
         <v>0.95277777777777772</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>17</v>
@@ -1889,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.4">
@@ -1900,7 +1909,7 @@
         <v>0.95486111111111116</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>19</v>
@@ -1927,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="Y3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.4">
@@ -1938,7 +1947,7 @@
         <v>0.95625000000000004</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>22</v>
@@ -1969,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="Y4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.4">
@@ -1980,7 +1989,7 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>23</v>
@@ -2015,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="Y5" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.4">
@@ -2026,7 +2035,7 @@
         <v>0.9604166666666667</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>27</v>
@@ -2053,7 +2062,7 @@
         <v>1</v>
       </c>
       <c r="Y6" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.4">
@@ -2064,7 +2073,7 @@
         <v>0.96111111111111114</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2101,7 +2110,7 @@
         <v>1</v>
       </c>
       <c r="Y7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.4">
@@ -2112,7 +2121,7 @@
         <v>0.96597222222222223</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>30</v>
@@ -2139,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="Y8" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.4">
@@ -2150,7 +2159,7 @@
         <v>0.96666666666666667</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>31</v>
@@ -2185,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="Y9" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.4">
@@ -2196,7 +2205,7 @@
         <v>0.96805555555555556</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>32</v>
@@ -2233,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="Y10" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.4">
@@ -2244,7 +2253,7 @@
         <v>0.97430555555555554</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>33</v>
@@ -2279,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="Y11" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.4">
@@ -2290,7 +2299,7 @@
         <v>0.97638888888888886</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>34</v>
@@ -2317,7 +2326,7 @@
         <v>1</v>
       </c>
       <c r="Y12" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.4">
@@ -2328,7 +2337,7 @@
         <v>0.97777777777777775</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>36</v>
@@ -2359,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="Y13" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.4">
@@ -2370,7 +2379,7 @@
         <v>0.97847222222222219</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>37</v>
@@ -2405,7 +2414,7 @@
         <v>1</v>
       </c>
       <c r="Y14" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.4">
@@ -2416,7 +2425,7 @@
         <v>0.98124999999999996</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>39</v>
@@ -2445,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="Y15" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.4">
@@ -2456,7 +2465,7 @@
         <v>0.98263888888888884</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>40</v>
@@ -2493,7 +2502,7 @@
         <v>1</v>
       </c>
       <c r="Y16" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.4">
@@ -2504,7 +2513,7 @@
         <v>0.98611111111111116</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>41</v>
@@ -2539,7 +2548,7 @@
         <v>1</v>
       </c>
       <c r="Y17" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.4">
@@ -2550,13 +2559,13 @@
         <v>0.99027777777777781</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>42</v>
       </c>
       <c r="J18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K18" s="21"/>
       <c r="L18" s="21"/>
@@ -2581,7 +2590,7 @@
         <v>1</v>
       </c>
       <c r="Y18" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.4">
@@ -2592,7 +2601,7 @@
         <v>0.99097222222222225</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>43</v>
@@ -2629,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="Y19" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.4">
@@ -2640,7 +2649,7 @@
         <v>0.99652777777777779</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>44</v>
@@ -2679,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="Y20" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.4">
@@ -2690,7 +2699,7 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>45</v>
@@ -2717,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="Y21" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.4">
@@ -2728,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>46</v>
@@ -2763,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="Y22" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.4">
@@ -2774,7 +2783,7 @@
         <v>2.7777777777777779E-3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>47</v>
@@ -2803,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="Y23" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.4">
@@ -2814,7 +2823,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>49</v>
@@ -2841,7 +2850,7 @@
         <v>1</v>
       </c>
       <c r="Y24" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.4">
@@ -2852,7 +2861,7 @@
         <v>4.8611111111111112E-3</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>50</v>
@@ -2881,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="Y25" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.4">
@@ -2892,7 +2901,7 @@
         <v>5.5555555555555558E-3</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>51</v>
@@ -2927,7 +2936,7 @@
         <v>1</v>
       </c>
       <c r="Y26" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.4">
@@ -2938,7 +2947,7 @@
         <v>9.0277777777777769E-3</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>52</v>
@@ -2975,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="Y27" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.4">
@@ -2986,7 +2995,7 @@
         <v>0.73541666666666672</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>53</v>
@@ -3023,7 +3032,7 @@
         <v>1</v>
       </c>
       <c r="Y28" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.4">
@@ -3034,7 +3043,7 @@
         <v>0.74583333333333335</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>55</v>
@@ -3069,7 +3078,7 @@
         <v>1</v>
       </c>
       <c r="Y29" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.4">
@@ -3080,7 +3089,7 @@
         <v>0.75069444444444444</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>56</v>
@@ -3107,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="Y30" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.4">
@@ -3118,7 +3127,7 @@
         <v>0.75138888888888888</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>57</v>
@@ -3157,7 +3166,7 @@
         <v>1</v>
       </c>
       <c r="Y31" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.4">
@@ -3168,7 +3177,7 @@
         <v>0.75972222222222219</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>58</v>
@@ -3192,7 +3201,7 @@
       <c r="P32" s="21"/>
       <c r="Q32" s="21"/>
       <c r="U32" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="V32" t="s">
         <v>26</v>
@@ -3204,7 +3213,7 @@
         <v>1</v>
       </c>
       <c r="Y32" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.4">
@@ -3215,10 +3224,10 @@
         <v>0.77013888888888893</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>60</v>
+        <v>390</v>
       </c>
       <c r="J33" t="s">
         <v>48</v>
@@ -3252,7 +3261,7 @@
         <v>1</v>
       </c>
       <c r="Y33" t="s">
-        <v>155</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.4">
@@ -3263,13 +3272,13 @@
         <v>0.77361111111111114</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="D34" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J34" t="s">
         <v>61</v>
-      </c>
-      <c r="J34" t="s">
-        <v>62</v>
       </c>
       <c r="K34" s="21">
         <v>1290</v>
@@ -3302,7 +3311,7 @@
         <v>1</v>
       </c>
       <c r="Y34" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.4">
@@ -3313,10 +3322,10 @@
         <v>0.78125</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J35" t="s">
         <v>48</v>
@@ -3344,7 +3353,7 @@
         <v>1</v>
       </c>
       <c r="Y35" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.4">
@@ -3355,13 +3364,13 @@
         <v>0.78680555555555554</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>64</v>
+        <v>389</v>
       </c>
       <c r="J36" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K36" s="21">
         <v>1950</v>
@@ -3394,7 +3403,7 @@
         <v>1</v>
       </c>
       <c r="Y36" t="s">
-        <v>158</v>
+        <v>388</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.4">
@@ -3405,10 +3414,10 @@
         <v>0.79236111111111107</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J37" t="s">
         <v>20</v>
@@ -3442,7 +3451,7 @@
         <v>1</v>
       </c>
       <c r="Y37" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.4">
@@ -3453,10 +3462,10 @@
         <v>0.79513888888888884</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J38" t="s">
         <v>35</v>
@@ -3480,7 +3489,7 @@
         <v>1</v>
       </c>
       <c r="Y38" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.4">
@@ -3491,10 +3500,10 @@
         <v>0.79583333333333328</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J39" t="s">
         <v>21</v>
@@ -3518,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="Y39" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.4">
@@ -3529,13 +3538,13 @@
         <v>0.79722222222222228</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K40" s="21"/>
       <c r="L40" s="21">
@@ -3560,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="Y40" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.4">
@@ -3571,10 +3580,10 @@
         <v>0.80625000000000002</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J41" t="s">
         <v>35</v>
@@ -3598,7 +3607,7 @@
         <v>1</v>
       </c>
       <c r="Y41" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.4">
@@ -3609,13 +3618,13 @@
         <v>0.81388888888888888</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K42" s="21">
         <v>1290</v>
@@ -3648,7 +3657,7 @@
         <v>1</v>
       </c>
       <c r="Y42" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.4">
@@ -3659,10 +3668,10 @@
         <v>0.82152777777777775</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J43" t="s">
         <v>35</v>
@@ -3686,7 +3695,7 @@
         <v>1</v>
       </c>
       <c r="Y43" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.4">
@@ -3697,10 +3706,10 @@
         <v>0.82222222222222219</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>75</v>
+        <v>385</v>
       </c>
       <c r="J44" t="s">
         <v>24</v>
@@ -3734,7 +3743,7 @@
         <v>1</v>
       </c>
       <c r="Y44" t="s">
-        <v>167</v>
+        <v>384</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.4">
@@ -3745,10 +3754,10 @@
         <v>0.82638888888888884</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>76</v>
+        <v>387</v>
       </c>
       <c r="J45" t="s">
         <v>35</v>
@@ -3772,7 +3781,7 @@
         <v>1</v>
       </c>
       <c r="Y45" t="s">
-        <v>166</v>
+        <v>386</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.4">
@@ -3783,10 +3792,10 @@
         <v>0.82777777777777772</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="J46" t="s">
         <v>35</v>
@@ -3810,7 +3819,7 @@
         <v>1</v>
       </c>
       <c r="Y46" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.4">
@@ -3821,10 +3830,10 @@
         <v>0.84652777777777777</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>78</v>
+        <v>377</v>
       </c>
       <c r="J47" t="s">
         <v>35</v>
@@ -3848,7 +3857,7 @@
         <v>1</v>
       </c>
       <c r="Y47" t="s">
-        <v>169</v>
+        <v>376</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.4">
@@ -3859,10 +3868,10 @@
         <v>0.84930555555555554</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>79</v>
+        <v>378</v>
       </c>
       <c r="J48" t="s">
         <v>35</v>
@@ -3886,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="Y48" t="s">
-        <v>170</v>
+        <v>379</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.4">
@@ -3897,10 +3906,10 @@
         <v>0.85277777777777775</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J49" t="s">
         <v>48</v>
@@ -3930,7 +3939,7 @@
         <v>1</v>
       </c>
       <c r="Y49" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.4">
@@ -3941,10 +3950,10 @@
         <v>0.85486111111111107</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J50" t="s">
         <v>24</v>
@@ -3976,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="Y50" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.4">
@@ -3987,10 +3996,10 @@
         <v>0.85763888888888884</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J51" t="s">
         <v>35</v>
@@ -4014,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="Y51" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.4">
@@ -4025,10 +4034,10 @@
         <v>0.86250000000000004</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J52" t="s">
         <v>20</v>
@@ -4064,7 +4073,7 @@
         <v>1</v>
       </c>
       <c r="Y52" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.4">
@@ -4075,10 +4084,10 @@
         <v>0.86284722222222221</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="J53" t="s">
         <v>21</v>
@@ -4102,7 +4111,7 @@
         <v>1</v>
       </c>
       <c r="Y53" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.4">
@@ -4113,10 +4122,10 @@
         <v>0.86597222222222225</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J54" t="s">
         <v>35</v>
@@ -4140,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="Y54" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.4">
@@ -4151,10 +4160,10 @@
         <v>0.87013888888888891</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>86</v>
+        <v>374</v>
       </c>
       <c r="J55" t="s">
         <v>24</v>
@@ -4186,7 +4195,7 @@
         <v>1</v>
       </c>
       <c r="Y55" t="s">
-        <v>177</v>
+        <v>375</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.4">
@@ -4197,10 +4206,10 @@
         <v>0.87569444444444444</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J56" t="s">
         <v>24</v>
@@ -4230,7 +4239,7 @@
         <v>1</v>
       </c>
       <c r="Y56" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.4">
@@ -4241,10 +4250,10 @@
         <v>0.88124999999999998</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J57" t="s">
         <v>38</v>
@@ -4280,7 +4289,7 @@
         <v>1</v>
       </c>
       <c r="Y57" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.4">
@@ -4291,10 +4300,10 @@
         <v>0.89027777777777772</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="J58" t="s">
         <v>35</v>
@@ -4318,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="Y58" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.4">
@@ -4329,10 +4338,10 @@
         <v>0.89097222222222228</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="J59" t="s">
         <v>24</v>
@@ -4364,7 +4373,7 @@
         <v>1</v>
       </c>
       <c r="Y59" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.4">
@@ -4375,10 +4384,10 @@
         <v>0.89513888888888893</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J60" t="s">
         <v>20</v>
@@ -4414,7 +4423,7 @@
         <v>1</v>
       </c>
       <c r="Y60" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.4">
@@ -4425,13 +4434,13 @@
         <v>0.8979166666666667</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="J61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K61" s="21">
         <v>1290</v>
@@ -4464,7 +4473,7 @@
         <v>1</v>
       </c>
       <c r="Y61" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.4">
@@ -4475,10 +4484,10 @@
         <v>0.90416666666666667</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J62" t="s">
         <v>35</v>
@@ -4502,7 +4511,7 @@
         <v>1</v>
       </c>
       <c r="Y62" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.4">
@@ -4513,13 +4522,13 @@
         <v>0.90486111111111112</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="J63" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K63" s="21"/>
       <c r="L63" s="21">
@@ -4544,7 +4553,7 @@
         <v>1</v>
       </c>
       <c r="Y63" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.4">
@@ -4555,13 +4564,13 @@
         <v>0.90694444444444444</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="J64" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K64" s="21"/>
       <c r="L64" s="21"/>
@@ -4582,7 +4591,7 @@
         <v>1</v>
       </c>
       <c r="Y64" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.4">
@@ -4593,10 +4602,10 @@
         <v>0.90729166666666672</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J65" t="s">
         <v>35</v>
@@ -4620,7 +4629,7 @@
         <v>1</v>
       </c>
       <c r="Y65" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.4">
@@ -4631,13 +4640,13 @@
         <v>0.90763888888888888</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="J66" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K66" s="21"/>
       <c r="L66" s="21"/>
@@ -4658,7 +4667,7 @@
         <v>1</v>
       </c>
       <c r="Y66" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.4">
@@ -4669,13 +4678,13 @@
         <v>0.90798611111111116</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="J67" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K67" s="21"/>
       <c r="L67" s="21"/>
@@ -4696,7 +4705,7 @@
         <v>1</v>
       </c>
       <c r="Y67" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.4">
@@ -4707,10 +4716,10 @@
         <v>0.90833333333333333</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J68" t="s">
         <v>35</v>
@@ -4734,7 +4743,7 @@
         <v>1</v>
       </c>
       <c r="Y68" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.4">
@@ -4745,10 +4754,10 @@
         <v>0.90902777777777777</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="J69" t="s">
         <v>35</v>
@@ -4772,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="Y69" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.4">
@@ -4783,10 +4792,10 @@
         <v>0.91041666666666665</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J70" t="s">
         <v>21</v>
@@ -4810,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="Y70" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.4">
@@ -4821,13 +4830,13 @@
         <v>0.91249999999999998</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="J71" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K71" s="21"/>
       <c r="L71" s="21"/>
@@ -4848,7 +4857,7 @@
         <v>1</v>
       </c>
       <c r="Y71" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.4">
@@ -4859,10 +4868,10 @@
         <v>0.92291666666666672</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="J72" t="s">
         <v>48</v>
@@ -4894,7 +4903,7 @@
         <v>1</v>
       </c>
       <c r="Y72" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.4">
@@ -4905,10 +4914,10 @@
         <v>0.92569444444444449</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="J73" t="s">
         <v>35</v>
@@ -4932,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="Y73" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.4">
@@ -4943,10 +4952,10 @@
         <v>0.92638888888888893</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="J74" t="s">
         <v>35</v>
@@ -4970,7 +4979,7 @@
         <v>1</v>
       </c>
       <c r="Y74" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.4">
@@ -4981,10 +4990,10 @@
         <v>0.92708333333333337</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>107</v>
+        <v>381</v>
       </c>
       <c r="J75" t="s">
         <v>20</v>
@@ -5020,7 +5029,7 @@
         <v>1</v>
       </c>
       <c r="Y75" t="s">
-        <v>124</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.4">
@@ -5031,10 +5040,10 @@
         <v>0.9291666666666667</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="J76" t="s">
         <v>24</v>
@@ -5068,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="Y76" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:25" s="15" customFormat="1" x14ac:dyDescent="0.4">
@@ -5083,10 +5092,10 @@
         <v>0.69861111111111107</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>266</v>
+        <v>383</v>
       </c>
       <c r="J78" t="s">
         <v>35</v>
@@ -5122,7 +5131,7 @@
         <v>2</v>
       </c>
       <c r="Y78" t="s">
-        <v>267</v>
+        <v>382</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.4">
@@ -5133,10 +5142,10 @@
         <v>0.7</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="J79" t="s">
         <v>24</v>
@@ -5172,7 +5181,7 @@
         <v>2</v>
       </c>
       <c r="Y79" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.4">
@@ -5183,10 +5192,10 @@
         <v>0.70277777777777772</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="J80" t="s">
         <v>21</v>
@@ -5222,7 +5231,7 @@
         <v>2</v>
       </c>
       <c r="Y80" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.4">
@@ -5233,13 +5242,13 @@
         <v>0.70972222222222225</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="J81" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K81" s="21">
         <v>0</v>
@@ -5272,7 +5281,7 @@
         <v>2</v>
       </c>
       <c r="Y81" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.4">
@@ -5283,10 +5292,10 @@
         <v>0.71875</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="J82" t="s">
         <v>21</v>
@@ -5322,7 +5331,7 @@
         <v>2</v>
       </c>
       <c r="Y82" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.4">
@@ -5333,10 +5342,10 @@
         <v>0.72152777777777777</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="J83" t="s">
         <v>20</v>
@@ -5372,7 +5381,7 @@
         <v>2</v>
       </c>
       <c r="Y83" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.4">
@@ -5383,10 +5392,10 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="J84" t="s">
         <v>35</v>
@@ -5422,7 +5431,7 @@
         <v>2</v>
       </c>
       <c r="Y84" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.4">
@@ -5433,10 +5442,10 @@
         <v>0.73819444444444449</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="J85" t="s">
         <v>24</v>
@@ -5472,7 +5481,7 @@
         <v>2</v>
       </c>
       <c r="Y85" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.4">
@@ -5483,13 +5492,13 @@
         <v>0.74097222222222225</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="J86" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K86" s="21">
         <v>1098.4615384615386</v>
@@ -5522,7 +5531,7 @@
         <v>2</v>
       </c>
       <c r="Y86" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.4">
@@ -5533,10 +5542,10 @@
         <v>0.76111111111111107</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="J87" t="s">
         <v>48</v>
@@ -5572,7 +5581,7 @@
         <v>2</v>
       </c>
       <c r="Y87" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.4">
@@ -5583,10 +5592,10 @@
         <v>0.7631944444444444</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="J88" t="s">
         <v>24</v>
@@ -5622,7 +5631,7 @@
         <v>2</v>
       </c>
       <c r="Y88" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.4">
@@ -5633,10 +5642,10 @@
         <v>0.77986111111111112</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="J89" t="s">
         <v>48</v>
@@ -5672,7 +5681,7 @@
         <v>2</v>
       </c>
       <c r="Y89" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.4">
@@ -5683,10 +5692,10 @@
         <v>0.79027777777777775</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="J90" t="s">
         <v>20</v>
@@ -5722,7 +5731,7 @@
         <v>2</v>
       </c>
       <c r="Y90" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.4">
@@ -5733,10 +5742,10 @@
         <v>0.8</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="J91" t="s">
         <v>48</v>
@@ -5772,7 +5781,7 @@
         <v>2</v>
       </c>
       <c r="Y91" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.4">
@@ -5783,10 +5792,10 @@
         <v>0.80972222222222223</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="J92" t="s">
         <v>24</v>
@@ -5822,7 +5831,7 @@
         <v>2</v>
       </c>
       <c r="Y92" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.4">
@@ -5833,10 +5842,10 @@
         <v>0.81666666666666665</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="J93" t="s">
         <v>24</v>
@@ -5872,7 +5881,7 @@
         <v>2</v>
       </c>
       <c r="Y93" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.4">
@@ -5883,10 +5892,10 @@
         <v>0.82222222222222219</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="J94" t="s">
         <v>21</v>
@@ -5922,7 +5931,7 @@
         <v>2</v>
       </c>
       <c r="Y94" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.4">
@@ -5933,10 +5942,10 @@
         <v>0.82708333333333328</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="J95" t="s">
         <v>24</v>
@@ -5972,7 +5981,7 @@
         <v>2</v>
       </c>
       <c r="Y95" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.4">
@@ -5983,10 +5992,10 @@
         <v>0.83819444444444446</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="J96" t="s">
         <v>35</v>
@@ -6022,7 +6031,7 @@
         <v>2</v>
       </c>
       <c r="Y96" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.4">
@@ -6033,10 +6042,10 @@
         <v>0.84027777777777779</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="J97" t="s">
         <v>48</v>
@@ -6072,7 +6081,7 @@
         <v>2</v>
       </c>
       <c r="Y97" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.4">
@@ -6083,10 +6092,10 @@
         <v>0.85069444444444442</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="J98" t="s">
         <v>38</v>
@@ -6122,7 +6131,7 @@
         <v>2</v>
       </c>
       <c r="Y98" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.4">
@@ -6133,10 +6142,10 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="J99" t="s">
         <v>35</v>
@@ -6172,7 +6181,7 @@
         <v>2</v>
       </c>
       <c r="Y99" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
     </row>
     <row r="100" spans="1:25" s="15" customFormat="1" x14ac:dyDescent="0.4">
@@ -6259,19 +6268,19 @@
   <sheetData>
     <row r="1" spans="1:26" s="4" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>54</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -6292,7 +6301,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
@@ -6322,16 +6331,16 @@
         <v>14</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>16</v>
@@ -6345,7 +6354,7 @@
         <v>0.95277777777777772</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>17</v>
@@ -6382,7 +6391,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.4">
@@ -6393,7 +6402,7 @@
         <v>0.95486111111111116</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>19</v>
@@ -6420,7 +6429,7 @@
         <v>1</v>
       </c>
       <c r="Y3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.4">
@@ -6431,7 +6440,7 @@
         <v>0.95625000000000004</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>22</v>
@@ -6462,7 +6471,7 @@
         <v>1</v>
       </c>
       <c r="Y4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.4">
@@ -6473,7 +6482,7 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>23</v>
@@ -6508,7 +6517,7 @@
         <v>1</v>
       </c>
       <c r="Y5" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.4">
@@ -6519,7 +6528,7 @@
         <v>0.9604166666666667</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>27</v>
@@ -6546,7 +6555,7 @@
         <v>1</v>
       </c>
       <c r="Y6" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.4">
@@ -6557,7 +6566,7 @@
         <v>0.96111111111111114</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -6594,7 +6603,7 @@
         <v>1</v>
       </c>
       <c r="Y7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.4">
@@ -6605,7 +6614,7 @@
         <v>0.96597222222222223</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>30</v>
@@ -6632,7 +6641,7 @@
         <v>1</v>
       </c>
       <c r="Y8" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.4">
@@ -6643,7 +6652,7 @@
         <v>0.96666666666666667</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>31</v>
@@ -6678,7 +6687,7 @@
         <v>1</v>
       </c>
       <c r="Y9" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.4">
@@ -6689,7 +6698,7 @@
         <v>0.96805555555555556</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>32</v>
@@ -6726,7 +6735,7 @@
         <v>1</v>
       </c>
       <c r="Y10" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.4">
@@ -6737,7 +6746,7 @@
         <v>0.97430555555555554</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>33</v>
@@ -6772,7 +6781,7 @@
         <v>1</v>
       </c>
       <c r="Y11" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.4">
@@ -6783,7 +6792,7 @@
         <v>0.97638888888888886</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>34</v>
@@ -6810,7 +6819,7 @@
         <v>1</v>
       </c>
       <c r="Y12" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.4">
@@ -6821,7 +6830,7 @@
         <v>0.97777777777777775</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>36</v>
@@ -6852,7 +6861,7 @@
         <v>1</v>
       </c>
       <c r="Y13" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.4">
@@ -6863,7 +6872,7 @@
         <v>0.97847222222222219</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>37</v>
@@ -6898,7 +6907,7 @@
         <v>1</v>
       </c>
       <c r="Y14" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.4">
@@ -6909,7 +6918,7 @@
         <v>0.98124999999999996</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>39</v>
@@ -6938,7 +6947,7 @@
         <v>1</v>
       </c>
       <c r="Y15" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.4">
@@ -6949,7 +6958,7 @@
         <v>0.98263888888888884</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>40</v>
@@ -6986,7 +6995,7 @@
         <v>1</v>
       </c>
       <c r="Y16" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.4">
@@ -6997,7 +7006,7 @@
         <v>0.98611111111111116</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>41</v>
@@ -7032,7 +7041,7 @@
         <v>1</v>
       </c>
       <c r="Y17" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.4">
@@ -7043,13 +7052,13 @@
         <v>0.99027777777777781</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>42</v>
       </c>
       <c r="J18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K18" s="21"/>
       <c r="L18" s="21"/>
@@ -7074,7 +7083,7 @@
         <v>1</v>
       </c>
       <c r="Y18" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.4">
@@ -7085,7 +7094,7 @@
         <v>0.99097222222222225</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>43</v>
@@ -7122,7 +7131,7 @@
         <v>1</v>
       </c>
       <c r="Y19" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.4">
@@ -7133,7 +7142,7 @@
         <v>0.99652777777777779</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>44</v>
@@ -7172,7 +7181,7 @@
         <v>1</v>
       </c>
       <c r="Y20" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.4">
@@ -7183,7 +7192,7 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>45</v>
@@ -7210,7 +7219,7 @@
         <v>1</v>
       </c>
       <c r="Y21" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.4">
@@ -7221,7 +7230,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>46</v>
@@ -7256,7 +7265,7 @@
         <v>1</v>
       </c>
       <c r="Y22" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.4">
@@ -7267,7 +7276,7 @@
         <v>2.7777777777777779E-3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>47</v>
@@ -7296,7 +7305,7 @@
         <v>1</v>
       </c>
       <c r="Y23" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.4">
@@ -7307,7 +7316,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>49</v>
@@ -7334,7 +7343,7 @@
         <v>1</v>
       </c>
       <c r="Y24" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.4">
@@ -7345,7 +7354,7 @@
         <v>4.8611111111111112E-3</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>50</v>
@@ -7374,7 +7383,7 @@
         <v>1</v>
       </c>
       <c r="Y25" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.4">
@@ -7385,7 +7394,7 @@
         <v>5.5555555555555558E-3</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>51</v>
@@ -7420,7 +7429,7 @@
         <v>1</v>
       </c>
       <c r="Y26" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.4">
@@ -7431,7 +7440,7 @@
         <v>9.0277777777777769E-3</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>52</v>
@@ -7468,7 +7477,7 @@
         <v>1</v>
       </c>
       <c r="Y27" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.4">
@@ -7479,7 +7488,7 @@
         <v>0.73541666666666672</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>53</v>
@@ -7516,7 +7525,7 @@
         <v>1</v>
       </c>
       <c r="Y28" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.4">
@@ -7527,7 +7536,7 @@
         <v>0.74583333333333335</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>55</v>
@@ -7562,7 +7571,7 @@
         <v>1</v>
       </c>
       <c r="Y29" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.4">
@@ -7573,7 +7582,7 @@
         <v>0.75069444444444444</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>56</v>
@@ -7600,7 +7609,7 @@
         <v>1</v>
       </c>
       <c r="Y30" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.4">
@@ -7611,7 +7620,7 @@
         <v>0.75138888888888888</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>57</v>
@@ -7650,7 +7659,7 @@
         <v>1</v>
       </c>
       <c r="Y31" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.4">
@@ -7661,7 +7670,7 @@
         <v>0.75972222222222219</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>58</v>
@@ -7685,7 +7694,7 @@
       <c r="P32" s="21"/>
       <c r="Q32" s="21"/>
       <c r="U32" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="V32" t="s">
         <v>26</v>
@@ -7697,7 +7706,7 @@
         <v>1</v>
       </c>
       <c r="Y32" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.4">
@@ -7708,10 +7717,10 @@
         <v>0.77013888888888893</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>60</v>
+        <v>390</v>
       </c>
       <c r="J33" t="s">
         <v>48</v>
@@ -7745,7 +7754,7 @@
         <v>1</v>
       </c>
       <c r="Y33" t="s">
-        <v>155</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.4">
@@ -7756,13 +7765,13 @@
         <v>0.77361111111111114</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="D34" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J34" t="s">
         <v>61</v>
-      </c>
-      <c r="J34" t="s">
-        <v>62</v>
       </c>
       <c r="K34" s="21">
         <v>1290</v>
@@ -7795,7 +7804,7 @@
         <v>1</v>
       </c>
       <c r="Y34" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.4">
@@ -7806,10 +7815,10 @@
         <v>0.78125</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J35" t="s">
         <v>48</v>
@@ -7837,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="Y35" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.4">
@@ -7848,13 +7857,13 @@
         <v>0.78680555555555554</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>64</v>
+        <v>389</v>
       </c>
       <c r="J36" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K36" s="21">
         <v>1950</v>
@@ -7887,7 +7896,7 @@
         <v>1</v>
       </c>
       <c r="Y36" t="s">
-        <v>158</v>
+        <v>388</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.4">
@@ -7898,10 +7907,10 @@
         <v>0.79236111111111107</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J37" t="s">
         <v>20</v>
@@ -7935,7 +7944,7 @@
         <v>1</v>
       </c>
       <c r="Y37" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.4">
@@ -7946,10 +7955,10 @@
         <v>0.79513888888888884</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J38" t="s">
         <v>35</v>
@@ -7973,7 +7982,7 @@
         <v>1</v>
       </c>
       <c r="Y38" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.4">
@@ -7984,10 +7993,10 @@
         <v>0.79583333333333328</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J39" t="s">
         <v>21</v>
@@ -8011,7 +8020,7 @@
         <v>1</v>
       </c>
       <c r="Y39" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.4">
@@ -8022,13 +8031,13 @@
         <v>0.79722222222222228</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K40" s="21"/>
       <c r="L40" s="21">
@@ -8053,7 +8062,7 @@
         <v>1</v>
       </c>
       <c r="Y40" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.4">
@@ -8064,10 +8073,10 @@
         <v>0.80625000000000002</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J41" t="s">
         <v>35</v>
@@ -8091,7 +8100,7 @@
         <v>1</v>
       </c>
       <c r="Y41" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.4">
@@ -8102,13 +8111,13 @@
         <v>0.81388888888888888</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K42" s="21">
         <v>1290</v>
@@ -8141,7 +8150,7 @@
         <v>1</v>
       </c>
       <c r="Y42" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.4">
@@ -8152,10 +8161,10 @@
         <v>0.82152777777777775</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J43" t="s">
         <v>35</v>
@@ -8179,7 +8188,7 @@
         <v>1</v>
       </c>
       <c r="Y43" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.4">
@@ -8190,10 +8199,10 @@
         <v>0.82222222222222219</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>75</v>
+        <v>385</v>
       </c>
       <c r="J44" t="s">
         <v>24</v>
@@ -8227,7 +8236,7 @@
         <v>1</v>
       </c>
       <c r="Y44" t="s">
-        <v>167</v>
+        <v>384</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.4">
@@ -8238,10 +8247,10 @@
         <v>0.82638888888888884</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>76</v>
+        <v>387</v>
       </c>
       <c r="J45" t="s">
         <v>35</v>
@@ -8265,7 +8274,7 @@
         <v>1</v>
       </c>
       <c r="Y45" t="s">
-        <v>166</v>
+        <v>386</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.4">
@@ -8276,10 +8285,10 @@
         <v>0.82777777777777772</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="J46" t="s">
         <v>35</v>
@@ -8303,7 +8312,7 @@
         <v>1</v>
       </c>
       <c r="Y46" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.4">
@@ -8314,10 +8323,10 @@
         <v>0.84652777777777777</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>78</v>
+        <v>377</v>
       </c>
       <c r="J47" t="s">
         <v>35</v>
@@ -8341,7 +8350,7 @@
         <v>1</v>
       </c>
       <c r="Y47" t="s">
-        <v>169</v>
+        <v>376</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.4">
@@ -8352,10 +8361,10 @@
         <v>0.84930555555555554</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>79</v>
+        <v>378</v>
       </c>
       <c r="J48" t="s">
         <v>35</v>
@@ -8379,7 +8388,7 @@
         <v>1</v>
       </c>
       <c r="Y48" t="s">
-        <v>170</v>
+        <v>379</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.4">
@@ -8390,10 +8399,10 @@
         <v>0.85277777777777775</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J49" t="s">
         <v>48</v>
@@ -8423,7 +8432,7 @@
         <v>1</v>
       </c>
       <c r="Y49" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.4">
@@ -8434,10 +8443,10 @@
         <v>0.85486111111111107</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J50" t="s">
         <v>24</v>
@@ -8469,7 +8478,7 @@
         <v>1</v>
       </c>
       <c r="Y50" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.4">
@@ -8480,10 +8489,10 @@
         <v>0.85763888888888884</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J51" t="s">
         <v>35</v>
@@ -8507,7 +8516,7 @@
         <v>1</v>
       </c>
       <c r="Y51" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.4">
@@ -8518,10 +8527,10 @@
         <v>0.86250000000000004</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J52" t="s">
         <v>20</v>
@@ -8557,7 +8566,7 @@
         <v>1</v>
       </c>
       <c r="Y52" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.4">
@@ -8568,10 +8577,10 @@
         <v>0.86284722222222221</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="J53" t="s">
         <v>21</v>
@@ -8595,7 +8604,7 @@
         <v>1</v>
       </c>
       <c r="Y53" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.4">
@@ -8606,10 +8615,10 @@
         <v>0.86597222222222225</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J54" t="s">
         <v>35</v>
@@ -8633,7 +8642,7 @@
         <v>1</v>
       </c>
       <c r="Y54" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.4">
@@ -8644,10 +8653,10 @@
         <v>0.87013888888888891</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>86</v>
+        <v>374</v>
       </c>
       <c r="J55" t="s">
         <v>24</v>
@@ -8679,7 +8688,7 @@
         <v>1</v>
       </c>
       <c r="Y55" t="s">
-        <v>177</v>
+        <v>375</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.4">
@@ -8690,10 +8699,10 @@
         <v>0.87569444444444444</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J56" t="s">
         <v>24</v>
@@ -8723,7 +8732,7 @@
         <v>1</v>
       </c>
       <c r="Y56" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.4">
@@ -8734,10 +8743,10 @@
         <v>0.88124999999999998</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J57" t="s">
         <v>38</v>
@@ -8773,7 +8782,7 @@
         <v>1</v>
       </c>
       <c r="Y57" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.4">
@@ -8784,10 +8793,10 @@
         <v>0.89027777777777772</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="J58" t="s">
         <v>35</v>
@@ -8811,7 +8820,7 @@
         <v>1</v>
       </c>
       <c r="Y58" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.4">
@@ -8822,10 +8831,10 @@
         <v>0.89097222222222228</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="J59" t="s">
         <v>24</v>
@@ -8857,7 +8866,7 @@
         <v>1</v>
       </c>
       <c r="Y59" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.4">
@@ -8868,10 +8877,10 @@
         <v>0.89513888888888893</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J60" t="s">
         <v>20</v>
@@ -8907,7 +8916,7 @@
         <v>1</v>
       </c>
       <c r="Y60" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.4">
@@ -8918,13 +8927,13 @@
         <v>0.8979166666666667</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="J61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K61" s="21">
         <v>1290</v>
@@ -8957,7 +8966,7 @@
         <v>1</v>
       </c>
       <c r="Y61" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.4">
@@ -8968,10 +8977,10 @@
         <v>0.90416666666666667</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J62" t="s">
         <v>35</v>
@@ -8995,7 +9004,7 @@
         <v>1</v>
       </c>
       <c r="Y62" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.4">
@@ -9006,13 +9015,13 @@
         <v>0.90486111111111112</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="J63" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K63" s="21"/>
       <c r="L63" s="21">
@@ -9037,7 +9046,7 @@
         <v>1</v>
       </c>
       <c r="Y63" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.4">
@@ -9048,13 +9057,13 @@
         <v>0.90694444444444444</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="J64" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K64" s="21"/>
       <c r="L64" s="21"/>
@@ -9075,7 +9084,7 @@
         <v>1</v>
       </c>
       <c r="Y64" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.4">
@@ -9086,10 +9095,10 @@
         <v>0.90729166666666672</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J65" t="s">
         <v>35</v>
@@ -9113,7 +9122,7 @@
         <v>1</v>
       </c>
       <c r="Y65" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.4">
@@ -9124,13 +9133,13 @@
         <v>0.90763888888888888</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="J66" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K66" s="21"/>
       <c r="L66" s="21"/>
@@ -9151,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="Y66" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.4">
@@ -9162,13 +9171,13 @@
         <v>0.90798611111111116</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="J67" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K67" s="21"/>
       <c r="L67" s="21"/>
@@ -9189,7 +9198,7 @@
         <v>1</v>
       </c>
       <c r="Y67" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.4">
@@ -9200,10 +9209,10 @@
         <v>0.90833333333333333</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J68" t="s">
         <v>35</v>
@@ -9227,7 +9236,7 @@
         <v>1</v>
       </c>
       <c r="Y68" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.4">
@@ -9238,10 +9247,10 @@
         <v>0.90902777777777777</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="J69" t="s">
         <v>35</v>
@@ -9265,7 +9274,7 @@
         <v>1</v>
       </c>
       <c r="Y69" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.4">
@@ -9276,10 +9285,10 @@
         <v>0.91041666666666665</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J70" t="s">
         <v>21</v>
@@ -9303,7 +9312,7 @@
         <v>1</v>
       </c>
       <c r="Y70" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.4">
@@ -9314,13 +9323,13 @@
         <v>0.91249999999999998</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="J71" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K71" s="21"/>
       <c r="L71" s="21"/>
@@ -9341,7 +9350,7 @@
         <v>1</v>
       </c>
       <c r="Y71" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.4">
@@ -9352,10 +9361,10 @@
         <v>0.92291666666666672</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="J72" t="s">
         <v>48</v>
@@ -9387,7 +9396,7 @@
         <v>1</v>
       </c>
       <c r="Y72" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.4">
@@ -9398,10 +9407,10 @@
         <v>0.92569444444444449</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="J73" t="s">
         <v>35</v>
@@ -9425,7 +9434,7 @@
         <v>1</v>
       </c>
       <c r="Y73" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.4">
@@ -9436,10 +9445,10 @@
         <v>0.92638888888888893</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="J74" t="s">
         <v>35</v>
@@ -9463,7 +9472,7 @@
         <v>1</v>
       </c>
       <c r="Y74" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.4">
@@ -9474,10 +9483,10 @@
         <v>0.92708333333333337</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>107</v>
+        <v>381</v>
       </c>
       <c r="J75" t="s">
         <v>20</v>
@@ -9513,7 +9522,7 @@
         <v>1</v>
       </c>
       <c r="Y75" t="s">
-        <v>124</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.4">
@@ -9524,10 +9533,10 @@
         <v>0.9291666666666667</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="J76" t="s">
         <v>24</v>
@@ -9561,7 +9570,7 @@
         <v>1</v>
       </c>
       <c r="Y76" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:25" s="15" customFormat="1" x14ac:dyDescent="0.4">
@@ -9571,7 +9580,7 @@
         <v>5</v>
       </c>
       <c r="L77" s="15" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="M77" s="15" t="s">
         <v>6</v>
@@ -9597,10 +9606,10 @@
         <v>0.69861111111111107</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>266</v>
+        <v>383</v>
       </c>
       <c r="J78" t="s">
         <v>35</v>
@@ -9643,7 +9652,7 @@
         <v>2</v>
       </c>
       <c r="Y78" t="s">
-        <v>267</v>
+        <v>382</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.4">
@@ -9654,10 +9663,10 @@
         <v>0.7</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="J79" t="s">
         <v>24</v>
@@ -9700,7 +9709,7 @@
         <v>2</v>
       </c>
       <c r="Y79" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.4">
@@ -9711,10 +9720,10 @@
         <v>0.70277777777777772</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="J80" t="s">
         <v>21</v>
@@ -9757,7 +9766,7 @@
         <v>2</v>
       </c>
       <c r="Y80" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.4">
@@ -9768,13 +9777,13 @@
         <v>0.70972222222222225</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="J81" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K81" s="21">
         <f>IFERROR(solapados_tanda1y2!$P$39*INDEX('z_datos originales'!$C$77:$Q$108,MATCH(limpieza_datos!$C81,'z_datos originales'!$C$77:$C$108,0),MATCH(limpieza_datos!$K$77,'z_datos originales'!$C$77:$Q$77,0)),"")</f>
@@ -9814,7 +9823,7 @@
         <v>2</v>
       </c>
       <c r="Y81" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.4">
@@ -9825,10 +9834,10 @@
         <v>0.71875</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="J82" t="s">
         <v>21</v>
@@ -9871,7 +9880,7 @@
         <v>2</v>
       </c>
       <c r="Y82" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.4">
@@ -9882,10 +9891,10 @@
         <v>0.72152777777777777</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="J83" t="s">
         <v>20</v>
@@ -9928,7 +9937,7 @@
         <v>2</v>
       </c>
       <c r="Y83" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.4">
@@ -9939,10 +9948,10 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="J84" t="s">
         <v>35</v>
@@ -9985,7 +9994,7 @@
         <v>2</v>
       </c>
       <c r="Y84" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.4">
@@ -9996,10 +10005,10 @@
         <v>0.73819444444444449</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="J85" t="s">
         <v>24</v>
@@ -10042,7 +10051,7 @@
         <v>2</v>
       </c>
       <c r="Y85" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.4">
@@ -10053,13 +10062,13 @@
         <v>0.74097222222222225</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="J86" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K86" s="21">
         <f>IFERROR(solapados_tanda1y2!$P$39*INDEX('z_datos originales'!$C$77:$Q$108,MATCH(limpieza_datos!$C86,'z_datos originales'!$C$77:$C$108,0),MATCH(limpieza_datos!$K$77,'z_datos originales'!$C$77:$Q$77,0)),"")</f>
@@ -10099,7 +10108,7 @@
         <v>2</v>
       </c>
       <c r="Y86" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.4">
@@ -10110,10 +10119,10 @@
         <v>0.76111111111111107</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="J87" t="s">
         <v>48</v>
@@ -10156,7 +10165,7 @@
         <v>2</v>
       </c>
       <c r="Y87" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.4">
@@ -10167,10 +10176,10 @@
         <v>0.7631944444444444</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="J88" t="s">
         <v>24</v>
@@ -10213,7 +10222,7 @@
         <v>2</v>
       </c>
       <c r="Y88" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.4">
@@ -10224,10 +10233,10 @@
         <v>0.77986111111111112</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="J89" t="s">
         <v>48</v>
@@ -10270,7 +10279,7 @@
         <v>2</v>
       </c>
       <c r="Y89" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.4">
@@ -10281,10 +10290,10 @@
         <v>0.79027777777777775</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="J90" t="s">
         <v>20</v>
@@ -10327,7 +10336,7 @@
         <v>2</v>
       </c>
       <c r="Y90" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.4">
@@ -10338,10 +10347,10 @@
         <v>0.8</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="J91" t="s">
         <v>48</v>
@@ -10384,7 +10393,7 @@
         <v>2</v>
       </c>
       <c r="Y91" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.4">
@@ -10395,10 +10404,10 @@
         <v>0.80972222222222223</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="J92" t="s">
         <v>24</v>
@@ -10441,7 +10450,7 @@
         <v>2</v>
       </c>
       <c r="Y92" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.4">
@@ -10452,10 +10461,10 @@
         <v>0.81666666666666665</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="J93" t="s">
         <v>24</v>
@@ -10498,7 +10507,7 @@
         <v>2</v>
       </c>
       <c r="Y93" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.4">
@@ -10509,10 +10518,10 @@
         <v>0.82222222222222219</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="J94" t="s">
         <v>21</v>
@@ -10555,7 +10564,7 @@
         <v>2</v>
       </c>
       <c r="Y94" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.4">
@@ -10566,10 +10575,10 @@
         <v>0.82708333333333328</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="J95" t="s">
         <v>24</v>
@@ -10612,7 +10621,7 @@
         <v>2</v>
       </c>
       <c r="Y95" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.4">
@@ -10623,10 +10632,10 @@
         <v>0.83819444444444446</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="J96" t="s">
         <v>35</v>
@@ -10669,7 +10678,7 @@
         <v>2</v>
       </c>
       <c r="Y96" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.4">
@@ -10680,10 +10689,10 @@
         <v>0.84027777777777779</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="J97" t="s">
         <v>48</v>
@@ -10726,7 +10735,7 @@
         <v>2</v>
       </c>
       <c r="Y97" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.4">
@@ -10737,10 +10746,10 @@
         <v>0.85069444444444442</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="J98" t="s">
         <v>38</v>
@@ -10783,7 +10792,7 @@
         <v>2</v>
       </c>
       <c r="Y98" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.4">
@@ -10794,10 +10803,10 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="J99" t="s">
         <v>35</v>
@@ -10840,7 +10849,7 @@
         <v>2</v>
       </c>
       <c r="Y99" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
     </row>
     <row r="100" spans="1:25" s="15" customFormat="1" x14ac:dyDescent="0.4">
@@ -10930,57 +10939,50 @@
     <hyperlink ref="D30" r:id="rId28" xr:uid="{F78689A6-6C5C-4431-9FB9-39B90E431B3F}"/>
     <hyperlink ref="D31" r:id="rId29" xr:uid="{A0271A6D-5583-4AF6-B487-D635FC3E1F97}"/>
     <hyperlink ref="D32" r:id="rId30" xr:uid="{41346792-5663-4496-8547-DD8EC11EB215}"/>
-    <hyperlink ref="D33" r:id="rId31" xr:uid="{F586D756-D125-4641-8245-6A2840619F73}"/>
-    <hyperlink ref="D34" r:id="rId32" xr:uid="{5D205A99-6EA5-4CF8-9E93-0C4CF553647E}"/>
-    <hyperlink ref="D35" r:id="rId33" xr:uid="{C8524AE0-F64A-4C9B-B82C-3152E64E9229}"/>
-    <hyperlink ref="D36" r:id="rId34" xr:uid="{1EDA7FBA-C1EF-4A7D-8BAC-0F9F6409BD69}"/>
-    <hyperlink ref="D37" r:id="rId35" xr:uid="{7866AA3F-31AF-4BA5-AB84-41E18A8D114E}"/>
-    <hyperlink ref="D41" r:id="rId36" xr:uid="{88D7D4E4-50C4-459F-9B72-D938C4767C26}"/>
-    <hyperlink ref="D42" r:id="rId37" xr:uid="{C14E2003-A135-4FA6-B891-F05F48DFFF8A}"/>
-    <hyperlink ref="D43" r:id="rId38" xr:uid="{9D396F29-5908-467F-9E52-D4F86AFD21E3}"/>
-    <hyperlink ref="D44" r:id="rId39" xr:uid="{0E602845-4FC1-4070-9E6B-08AF87A217D3}"/>
-    <hyperlink ref="D45" r:id="rId40" xr:uid="{A30E4C82-8B5C-4670-906F-F330EBBBAF93}"/>
-    <hyperlink ref="D46" r:id="rId41" xr:uid="{B525F21D-40F8-4F31-B161-6DD018CCD835}"/>
-    <hyperlink ref="D47" r:id="rId42" xr:uid="{B2C42940-6C5C-4E8E-9E7A-EBAC71C27E55}"/>
-    <hyperlink ref="D48" r:id="rId43" xr:uid="{64267FC1-FADB-432A-8F4B-7304A6C465D7}"/>
-    <hyperlink ref="D49" r:id="rId44" xr:uid="{DBB53584-B217-4C2F-ABE9-A5BFCC0BFC76}"/>
-    <hyperlink ref="D50" r:id="rId45" xr:uid="{F50ADD64-0003-4284-87EA-ABB204AE1946}"/>
-    <hyperlink ref="D51" r:id="rId46" xr:uid="{42E1DB89-0ED2-4068-9D65-27503BF72FCC}"/>
-    <hyperlink ref="D52" r:id="rId47" xr:uid="{29C7FC7C-2257-474A-9510-324A47A6B130}"/>
-    <hyperlink ref="D53" r:id="rId48" xr:uid="{E9AE8AB7-0F01-4901-ACDD-A76C3912AD5A}"/>
-    <hyperlink ref="D54" r:id="rId49" xr:uid="{AF6EA4C3-5E6C-4C1D-A071-8F6D7A933FCE}"/>
-    <hyperlink ref="D55" r:id="rId50" xr:uid="{295919CC-5ED7-4168-A8AF-F1D2AC9D1508}"/>
-    <hyperlink ref="D56" r:id="rId51" xr:uid="{25D6C098-564B-44AA-B2E3-26C00B7DA62D}"/>
-    <hyperlink ref="D57" r:id="rId52" xr:uid="{3E0AF767-C186-4BB3-9A28-073A3B800775}"/>
-    <hyperlink ref="D58" r:id="rId53" xr:uid="{47909278-84ED-4613-9BE5-C090247B7063}"/>
-    <hyperlink ref="D59" r:id="rId54" xr:uid="{5D8D4885-C525-46A6-8E7E-CA11D107138D}"/>
-    <hyperlink ref="D60" r:id="rId55" xr:uid="{5A6560D7-5958-42EE-AEC4-ED4DC6ADC562}"/>
-    <hyperlink ref="D61" r:id="rId56" xr:uid="{D3ED8DA2-C243-433F-B9B6-D7F4275F1E33}"/>
-    <hyperlink ref="D62" r:id="rId57" xr:uid="{ADAB1EAC-65A2-4AE2-A011-A143950D04FF}"/>
-    <hyperlink ref="D63" r:id="rId58" xr:uid="{52F55D7F-C2F0-432D-BF5D-D7F549EE1CD0}"/>
-    <hyperlink ref="D64" r:id="rId59" xr:uid="{96FAAE5D-6BBE-4AAF-BA5C-8476067A3F93}"/>
-    <hyperlink ref="D65" r:id="rId60" xr:uid="{BCB1AD3D-0D75-4980-9BE0-4A0A0341E34C}"/>
-    <hyperlink ref="D66" r:id="rId61" xr:uid="{5551AF57-0759-4E03-BA87-6FF5D3690D0D}"/>
-    <hyperlink ref="D67" r:id="rId62" xr:uid="{3FA3692B-56EB-4CDC-AF70-CD1AF06E06A3}"/>
-    <hyperlink ref="D68" r:id="rId63" xr:uid="{18650105-8E57-4DAA-8AF4-31637D293D9E}"/>
-    <hyperlink ref="D69" r:id="rId64" xr:uid="{ACBF9558-B4AC-484A-92EC-7F37E0BB67BD}"/>
-    <hyperlink ref="D70" r:id="rId65" xr:uid="{F11D9F59-FF18-4CB3-907D-5AE50C96FDB2}"/>
-    <hyperlink ref="D71" r:id="rId66" xr:uid="{623C8ADB-610E-4CC7-AC21-08E01F32D5DA}"/>
-    <hyperlink ref="D72" r:id="rId67" xr:uid="{562DCECD-F65C-46C7-9C3E-6347ED3DAD54}"/>
-    <hyperlink ref="D73" r:id="rId68" xr:uid="{162B6B80-7EA1-461E-8AE2-AC2D9B72A538}"/>
-    <hyperlink ref="D74" r:id="rId69" xr:uid="{96DA9B5C-70F0-4601-8498-12A5457974EB}"/>
-    <hyperlink ref="D75" r:id="rId70" xr:uid="{D7D4CC28-8322-4C41-AF07-180ACD9B398F}"/>
-    <hyperlink ref="D76" r:id="rId71" xr:uid="{8BC60AB8-DAE9-48F1-975D-25D67D3F6F09}"/>
-    <hyperlink ref="D5" r:id="rId72" xr:uid="{B9BACED9-EFBF-4FE6-BD19-5722EA743AFB}"/>
-    <hyperlink ref="D38" r:id="rId73" xr:uid="{2E6ADDF1-24D1-45A1-BD96-446368A45399}"/>
-    <hyperlink ref="D39" r:id="rId74" xr:uid="{C4123B4B-D9DE-4904-AD82-D1F1CCC6D130}"/>
-    <hyperlink ref="D40" r:id="rId75" xr:uid="{EE523BE3-CCDC-47AE-AD66-151B8BB557ED}"/>
+    <hyperlink ref="D34" r:id="rId31" xr:uid="{5D205A99-6EA5-4CF8-9E93-0C4CF553647E}"/>
+    <hyperlink ref="D35" r:id="rId32" xr:uid="{C8524AE0-F64A-4C9B-B82C-3152E64E9229}"/>
+    <hyperlink ref="D37" r:id="rId33" xr:uid="{7866AA3F-31AF-4BA5-AB84-41E18A8D114E}"/>
+    <hyperlink ref="D41" r:id="rId34" xr:uid="{88D7D4E4-50C4-459F-9B72-D938C4767C26}"/>
+    <hyperlink ref="D42" r:id="rId35" xr:uid="{C14E2003-A135-4FA6-B891-F05F48DFFF8A}"/>
+    <hyperlink ref="D43" r:id="rId36" xr:uid="{9D396F29-5908-467F-9E52-D4F86AFD21E3}"/>
+    <hyperlink ref="D46" r:id="rId37" xr:uid="{B525F21D-40F8-4F31-B161-6DD018CCD835}"/>
+    <hyperlink ref="D48" r:id="rId38" display="https://www.google.com/maps?q=-34.5927619934082,-58.383609771728516&amp;z=17&amp;hl=es" xr:uid="{64267FC1-FADB-432A-8F4B-7304A6C465D7}"/>
+    <hyperlink ref="D49" r:id="rId39" xr:uid="{DBB53584-B217-4C2F-ABE9-A5BFCC0BFC76}"/>
+    <hyperlink ref="D50" r:id="rId40" xr:uid="{F50ADD64-0003-4284-87EA-ABB204AE1946}"/>
+    <hyperlink ref="D51" r:id="rId41" xr:uid="{42E1DB89-0ED2-4068-9D65-27503BF72FCC}"/>
+    <hyperlink ref="D52" r:id="rId42" xr:uid="{29C7FC7C-2257-474A-9510-324A47A6B130}"/>
+    <hyperlink ref="D53" r:id="rId43" xr:uid="{E9AE8AB7-0F01-4901-ACDD-A76C3912AD5A}"/>
+    <hyperlink ref="D54" r:id="rId44" xr:uid="{AF6EA4C3-5E6C-4C1D-A071-8F6D7A933FCE}"/>
+    <hyperlink ref="D56" r:id="rId45" xr:uid="{25D6C098-564B-44AA-B2E3-26C00B7DA62D}"/>
+    <hyperlink ref="D57" r:id="rId46" xr:uid="{3E0AF767-C186-4BB3-9A28-073A3B800775}"/>
+    <hyperlink ref="D58" r:id="rId47" xr:uid="{47909278-84ED-4613-9BE5-C090247B7063}"/>
+    <hyperlink ref="D59" r:id="rId48" xr:uid="{5D8D4885-C525-46A6-8E7E-CA11D107138D}"/>
+    <hyperlink ref="D60" r:id="rId49" xr:uid="{5A6560D7-5958-42EE-AEC4-ED4DC6ADC562}"/>
+    <hyperlink ref="D61" r:id="rId50" xr:uid="{D3ED8DA2-C243-433F-B9B6-D7F4275F1E33}"/>
+    <hyperlink ref="D62" r:id="rId51" xr:uid="{ADAB1EAC-65A2-4AE2-A011-A143950D04FF}"/>
+    <hyperlink ref="D63" r:id="rId52" xr:uid="{52F55D7F-C2F0-432D-BF5D-D7F549EE1CD0}"/>
+    <hyperlink ref="D64" r:id="rId53" xr:uid="{96FAAE5D-6BBE-4AAF-BA5C-8476067A3F93}"/>
+    <hyperlink ref="D65" r:id="rId54" xr:uid="{BCB1AD3D-0D75-4980-9BE0-4A0A0341E34C}"/>
+    <hyperlink ref="D66" r:id="rId55" xr:uid="{5551AF57-0759-4E03-BA87-6FF5D3690D0D}"/>
+    <hyperlink ref="D67" r:id="rId56" xr:uid="{3FA3692B-56EB-4CDC-AF70-CD1AF06E06A3}"/>
+    <hyperlink ref="D68" r:id="rId57" xr:uid="{18650105-8E57-4DAA-8AF4-31637D293D9E}"/>
+    <hyperlink ref="D69" r:id="rId58" xr:uid="{ACBF9558-B4AC-484A-92EC-7F37E0BB67BD}"/>
+    <hyperlink ref="D70" r:id="rId59" xr:uid="{F11D9F59-FF18-4CB3-907D-5AE50C96FDB2}"/>
+    <hyperlink ref="D71" r:id="rId60" xr:uid="{623C8ADB-610E-4CC7-AC21-08E01F32D5DA}"/>
+    <hyperlink ref="D72" r:id="rId61" xr:uid="{562DCECD-F65C-46C7-9C3E-6347ED3DAD54}"/>
+    <hyperlink ref="D73" r:id="rId62" xr:uid="{162B6B80-7EA1-461E-8AE2-AC2D9B72A538}"/>
+    <hyperlink ref="D74" r:id="rId63" xr:uid="{96DA9B5C-70F0-4601-8498-12A5457974EB}"/>
+    <hyperlink ref="D76" r:id="rId64" xr:uid="{8BC60AB8-DAE9-48F1-975D-25D67D3F6F09}"/>
+    <hyperlink ref="D5" r:id="rId65" xr:uid="{B9BACED9-EFBF-4FE6-BD19-5722EA743AFB}"/>
+    <hyperlink ref="D38" r:id="rId66" xr:uid="{2E6ADDF1-24D1-45A1-BD96-446368A45399}"/>
+    <hyperlink ref="D39" r:id="rId67" xr:uid="{C4123B4B-D9DE-4904-AD82-D1F1CCC6D130}"/>
+    <hyperlink ref="D40" r:id="rId68" xr:uid="{EE523BE3-CCDC-47AE-AD66-151B8BB557ED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId76"/>
+  <pageSetup orientation="portrait" r:id="rId69"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DA75701A-79FF-4AB6-8989-70D6FC527FEA}">
           <x14:formula1>
             <xm:f>Hoja2!$A$1:$A$13</xm:f>
@@ -11018,19 +11020,19 @@
   <sheetData>
     <row r="1" spans="1:26" s="4" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>54</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -11051,7 +11053,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
@@ -11081,16 +11083,16 @@
         <v>14</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>16</v>
@@ -11104,7 +11106,7 @@
         <v>0.95277777777777772</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>17</v>
@@ -11141,7 +11143,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.4">
@@ -11152,7 +11154,7 @@
         <v>0.95486111111111116</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>19</v>
@@ -11173,7 +11175,7 @@
         <v>1</v>
       </c>
       <c r="Y3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.4">
@@ -11184,7 +11186,7 @@
         <v>0.95625000000000004</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>22</v>
@@ -11211,7 +11213,7 @@
         <v>1</v>
       </c>
       <c r="Y4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.4">
@@ -11222,7 +11224,7 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>23</v>
@@ -11255,7 +11257,7 @@
         <v>1</v>
       </c>
       <c r="Y5" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.4">
@@ -11266,7 +11268,7 @@
         <v>0.9604166666666667</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>27</v>
@@ -11287,7 +11289,7 @@
         <v>1</v>
       </c>
       <c r="Y6" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.4">
@@ -11298,7 +11300,7 @@
         <v>0.96111111111111114</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -11335,7 +11337,7 @@
         <v>1</v>
       </c>
       <c r="Y7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.4">
@@ -11346,7 +11348,7 @@
         <v>0.96597222222222223</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>30</v>
@@ -11367,7 +11369,7 @@
         <v>1</v>
       </c>
       <c r="Y8" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.4">
@@ -11378,7 +11380,7 @@
         <v>0.96666666666666667</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>31</v>
@@ -11411,7 +11413,7 @@
         <v>1</v>
       </c>
       <c r="Y9" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.4">
@@ -11422,7 +11424,7 @@
         <v>0.96805555555555556</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>32</v>
@@ -11459,7 +11461,7 @@
         <v>1</v>
       </c>
       <c r="Y10" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.4">
@@ -11470,7 +11472,7 @@
         <v>0.97430555555555554</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>33</v>
@@ -11503,7 +11505,7 @@
         <v>1</v>
       </c>
       <c r="Y11" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.4">
@@ -11514,7 +11516,7 @@
         <v>0.97638888888888886</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>34</v>
@@ -11535,7 +11537,7 @@
         <v>1</v>
       </c>
       <c r="Y12" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.4">
@@ -11546,7 +11548,7 @@
         <v>0.97777777777777775</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>36</v>
@@ -11573,7 +11575,7 @@
         <v>1</v>
       </c>
       <c r="Y13" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.4">
@@ -11584,7 +11586,7 @@
         <v>0.97847222222222219</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>37</v>
@@ -11619,7 +11621,7 @@
         <v>1</v>
       </c>
       <c r="Y14" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.4">
@@ -11630,7 +11632,7 @@
         <v>0.98124999999999996</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>39</v>
@@ -11654,7 +11656,7 @@
         <v>1</v>
       </c>
       <c r="Y15" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.4">
@@ -11665,7 +11667,7 @@
         <v>0.98263888888888884</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>40</v>
@@ -11702,7 +11704,7 @@
         <v>1</v>
       </c>
       <c r="Y16" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.4">
@@ -11713,7 +11715,7 @@
         <v>0.98611111111111116</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>41</v>
@@ -11746,7 +11748,7 @@
         <v>1</v>
       </c>
       <c r="Y17" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.4">
@@ -11757,13 +11759,13 @@
         <v>0.99027777777777781</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>42</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N18">
         <v>2200</v>
@@ -11784,7 +11786,7 @@
         <v>1</v>
       </c>
       <c r="Y18" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.4">
@@ -11795,7 +11797,7 @@
         <v>0.99097222222222225</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>43</v>
@@ -11832,7 +11834,7 @@
         <v>1</v>
       </c>
       <c r="Y19" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.4">
@@ -11843,7 +11845,7 @@
         <v>0.99652777777777779</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>44</v>
@@ -11882,7 +11884,7 @@
         <v>1</v>
       </c>
       <c r="Y20" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.4">
@@ -11893,7 +11895,7 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>45</v>
@@ -11914,7 +11916,7 @@
         <v>1</v>
       </c>
       <c r="Y21" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.4">
@@ -11925,7 +11927,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>46</v>
@@ -11960,7 +11962,7 @@
         <v>1</v>
       </c>
       <c r="Y22" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.4">
@@ -11971,7 +11973,7 @@
         <v>2.7777777777777779E-3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>47</v>
@@ -11995,7 +11997,7 @@
         <v>1</v>
       </c>
       <c r="Y23" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.4">
@@ -12006,7 +12008,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>49</v>
@@ -12027,7 +12029,7 @@
         <v>1</v>
       </c>
       <c r="Y24" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.4">
@@ -12038,7 +12040,7 @@
         <v>4.8611111111111112E-3</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>50</v>
@@ -12062,7 +12064,7 @@
         <v>1</v>
       </c>
       <c r="Y25" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.4">
@@ -12073,7 +12075,7 @@
         <v>5.5555555555555558E-3</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>51</v>
@@ -12106,7 +12108,7 @@
         <v>1</v>
       </c>
       <c r="Y26" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.4">
@@ -12117,7 +12119,7 @@
         <v>9.0277777777777769E-3</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>52</v>
@@ -12153,7 +12155,7 @@
         <v>1</v>
       </c>
       <c r="Y27" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.4">
@@ -12164,7 +12166,7 @@
         <v>0.73541666666666672</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>53</v>
@@ -12200,7 +12202,7 @@
         <v>1</v>
       </c>
       <c r="Y28" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.4">
@@ -12211,7 +12213,7 @@
         <v>0.74583333333333335</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>55</v>
@@ -12244,7 +12246,7 @@
         <v>1</v>
       </c>
       <c r="Y29" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.4">
@@ -12255,7 +12257,7 @@
         <v>0.75069444444444444</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>56</v>
@@ -12276,7 +12278,7 @@
         <v>1</v>
       </c>
       <c r="Y30" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.4">
@@ -12287,7 +12289,7 @@
         <v>0.75138888888888888</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>57</v>
@@ -12326,7 +12328,7 @@
         <v>1</v>
       </c>
       <c r="Y31" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.4">
@@ -12337,7 +12339,7 @@
         <v>0.75972222222222219</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>58</v>
@@ -12358,7 +12360,7 @@
         <v>5200</v>
       </c>
       <c r="U32" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="V32" t="s">
         <v>26</v>
@@ -12370,7 +12372,7 @@
         <v>1</v>
       </c>
       <c r="Y32" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.4">
@@ -12381,10 +12383,10 @@
         <v>0.77013888888888893</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>60</v>
+        <v>390</v>
       </c>
       <c r="J33" s="20" t="s">
         <v>48</v>
@@ -12417,7 +12419,7 @@
         <v>1</v>
       </c>
       <c r="Y33" t="s">
-        <v>155</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.4">
@@ -12428,13 +12430,13 @@
         <v>0.77361111111111114</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="D34" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J34" s="20" t="s">
         <v>61</v>
-      </c>
-      <c r="J34" s="20" t="s">
-        <v>62</v>
       </c>
       <c r="K34">
         <v>1290</v>
@@ -12467,7 +12469,7 @@
         <v>1</v>
       </c>
       <c r="Y34" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.4">
@@ -12478,10 +12480,10 @@
         <v>0.78125</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J35" s="20" t="s">
         <v>48</v>
@@ -12505,7 +12507,7 @@
         <v>1</v>
       </c>
       <c r="Y35" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.4">
@@ -12516,13 +12518,13 @@
         <v>0.78680555555555554</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>64</v>
+        <v>389</v>
       </c>
       <c r="J36" s="20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K36">
         <v>1950</v>
@@ -12555,7 +12557,7 @@
         <v>1</v>
       </c>
       <c r="Y36" t="s">
-        <v>158</v>
+        <v>388</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.4">
@@ -12566,10 +12568,10 @@
         <v>0.79236111111111107</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J37" s="20" t="s">
         <v>20</v>
@@ -12602,7 +12604,7 @@
         <v>1</v>
       </c>
       <c r="Y37" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.4">
@@ -12613,10 +12615,10 @@
         <v>0.79513888888888884</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J38" s="20" t="s">
         <v>35</v>
@@ -12634,7 +12636,7 @@
         <v>1</v>
       </c>
       <c r="Y38" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.4">
@@ -12645,10 +12647,10 @@
         <v>0.79583333333333328</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J39" s="20" t="s">
         <v>21</v>
@@ -12666,7 +12668,7 @@
         <v>1</v>
       </c>
       <c r="Y39" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.4">
@@ -12677,13 +12679,13 @@
         <v>0.79722222222222228</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J40" s="20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L40">
         <v>1400</v>
@@ -12704,7 +12706,7 @@
         <v>1</v>
       </c>
       <c r="Y40" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.4">
@@ -12715,10 +12717,10 @@
         <v>0.80625000000000002</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J41" s="20" t="s">
         <v>35</v>
@@ -12736,7 +12738,7 @@
         <v>1</v>
       </c>
       <c r="Y41" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.4">
@@ -12747,13 +12749,13 @@
         <v>0.81388888888888888</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J42" s="20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K42">
         <v>1290</v>
@@ -12786,7 +12788,7 @@
         <v>1</v>
       </c>
       <c r="Y42" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.4">
@@ -12797,10 +12799,10 @@
         <v>0.82152777777777775</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J43" s="20" t="s">
         <v>35</v>
@@ -12818,7 +12820,7 @@
         <v>1</v>
       </c>
       <c r="Y43" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.4">
@@ -12829,10 +12831,10 @@
         <v>0.82222222222222219</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>75</v>
+        <v>385</v>
       </c>
       <c r="J44" s="20" t="s">
         <v>24</v>
@@ -12865,7 +12867,7 @@
         <v>1</v>
       </c>
       <c r="Y44" t="s">
-        <v>167</v>
+        <v>384</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.4">
@@ -12876,10 +12878,10 @@
         <v>0.82638888888888884</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>76</v>
+        <v>387</v>
       </c>
       <c r="J45" s="20" t="s">
         <v>35</v>
@@ -12897,7 +12899,7 @@
         <v>1</v>
       </c>
       <c r="Y45" t="s">
-        <v>166</v>
+        <v>386</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.4">
@@ -12908,10 +12910,10 @@
         <v>0.82777777777777772</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="J46" s="20" t="s">
         <v>35</v>
@@ -12929,7 +12931,7 @@
         <v>1</v>
       </c>
       <c r="Y46" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.4">
@@ -12940,10 +12942,10 @@
         <v>0.84652777777777777</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>78</v>
+        <v>377</v>
       </c>
       <c r="J47" s="20" t="s">
         <v>35</v>
@@ -12961,7 +12963,7 @@
         <v>1</v>
       </c>
       <c r="Y47" t="s">
-        <v>169</v>
+        <v>376</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.4">
@@ -12972,10 +12974,10 @@
         <v>0.84930555555555554</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>79</v>
+        <v>378</v>
       </c>
       <c r="J48" s="20" t="s">
         <v>35</v>
@@ -12993,7 +12995,7 @@
         <v>1</v>
       </c>
       <c r="Y48" t="s">
-        <v>170</v>
+        <v>379</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.4">
@@ -13004,10 +13006,10 @@
         <v>0.85277777777777775</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J49" s="20" t="s">
         <v>48</v>
@@ -13034,7 +13036,7 @@
         <v>1</v>
       </c>
       <c r="Y49" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.4">
@@ -13045,10 +13047,10 @@
         <v>0.85486111111111107</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J50" s="20" t="s">
         <v>24</v>
@@ -13078,7 +13080,7 @@
         <v>1</v>
       </c>
       <c r="Y50" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.4">
@@ -13089,10 +13091,10 @@
         <v>0.85763888888888884</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J51" s="20" t="s">
         <v>35</v>
@@ -13110,7 +13112,7 @@
         <v>1</v>
       </c>
       <c r="Y51" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.4">
@@ -13121,10 +13123,10 @@
         <v>0.86250000000000004</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J52" s="20" t="s">
         <v>20</v>
@@ -13160,7 +13162,7 @@
         <v>1</v>
       </c>
       <c r="Y52" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.4">
@@ -13171,10 +13173,10 @@
         <v>0.86284722222222221</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="J53" s="20" t="s">
         <v>21</v>
@@ -13192,7 +13194,7 @@
         <v>1</v>
       </c>
       <c r="Y53" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.4">
@@ -13203,10 +13205,10 @@
         <v>0.86597222222222225</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J54" s="20" t="s">
         <v>35</v>
@@ -13224,7 +13226,7 @@
         <v>1</v>
       </c>
       <c r="Y54" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.4">
@@ -13235,10 +13237,10 @@
         <v>0.87013888888888891</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>86</v>
+        <v>374</v>
       </c>
       <c r="J55" s="20" t="s">
         <v>24</v>
@@ -13268,7 +13270,7 @@
         <v>1</v>
       </c>
       <c r="Y55" t="s">
-        <v>177</v>
+        <v>375</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.4">
@@ -13279,10 +13281,10 @@
         <v>0.87569444444444444</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J56" s="20" t="s">
         <v>24</v>
@@ -13309,7 +13311,7 @@
         <v>1</v>
       </c>
       <c r="Y56" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.4">
@@ -13320,10 +13322,10 @@
         <v>0.88124999999999998</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J57" s="20" t="s">
         <v>38</v>
@@ -13359,7 +13361,7 @@
         <v>1</v>
       </c>
       <c r="Y57" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.4">
@@ -13370,10 +13372,10 @@
         <v>0.89027777777777772</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="J58" s="20" t="s">
         <v>35</v>
@@ -13391,7 +13393,7 @@
         <v>1</v>
       </c>
       <c r="Y58" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.4">
@@ -13402,10 +13404,10 @@
         <v>0.89097222222222228</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="J59" s="20" t="s">
         <v>24</v>
@@ -13435,7 +13437,7 @@
         <v>1</v>
       </c>
       <c r="Y59" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.4">
@@ -13446,10 +13448,10 @@
         <v>0.89513888888888893</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J60" s="20" t="s">
         <v>20</v>
@@ -13485,7 +13487,7 @@
         <v>1</v>
       </c>
       <c r="Y60" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.4">
@@ -13496,13 +13498,13 @@
         <v>0.8979166666666667</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="J61" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K61">
         <v>1290</v>
@@ -13535,7 +13537,7 @@
         <v>1</v>
       </c>
       <c r="Y61" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.4">
@@ -13546,10 +13548,10 @@
         <v>0.90416666666666667</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J62" s="20" t="s">
         <v>35</v>
@@ -13567,7 +13569,7 @@
         <v>1</v>
       </c>
       <c r="Y62" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.4">
@@ -13578,13 +13580,13 @@
         <v>0.90486111111111112</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="J63" s="20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L63">
         <v>1400</v>
@@ -13605,7 +13607,7 @@
         <v>1</v>
       </c>
       <c r="Y63" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.4">
@@ -13616,13 +13618,13 @@
         <v>0.90694444444444444</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="J64" s="20" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="Q64">
         <v>8500</v>
@@ -13637,7 +13639,7 @@
         <v>1</v>
       </c>
       <c r="Y64" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.4">
@@ -13648,10 +13650,10 @@
         <v>0.90729166666666672</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J65" s="20" t="s">
         <v>35</v>
@@ -13669,7 +13671,7 @@
         <v>1</v>
       </c>
       <c r="Y65" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.4">
@@ -13680,13 +13682,13 @@
         <v>0.90763888888888888</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="J66" s="20" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="Q66">
         <v>17000</v>
@@ -13701,7 +13703,7 @@
         <v>1</v>
       </c>
       <c r="Y66" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.4">
@@ -13712,13 +13714,13 @@
         <v>0.90798611111111116</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="J67" s="20" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="Q67">
         <v>21000</v>
@@ -13733,7 +13735,7 @@
         <v>1</v>
       </c>
       <c r="Y67" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.4">
@@ -13744,10 +13746,10 @@
         <v>0.90833333333333333</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J68" s="20" t="s">
         <v>35</v>
@@ -13765,7 +13767,7 @@
         <v>1</v>
       </c>
       <c r="Y68" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.4">
@@ -13776,10 +13778,10 @@
         <v>0.90902777777777777</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="J69" s="20" t="s">
         <v>35</v>
@@ -13797,7 +13799,7 @@
         <v>1</v>
       </c>
       <c r="Y69" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.4">
@@ -13808,10 +13810,10 @@
         <v>0.91041666666666665</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J70" s="20" t="s">
         <v>21</v>
@@ -13829,7 +13831,7 @@
         <v>1</v>
       </c>
       <c r="Y70" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.4">
@@ -13840,13 +13842,13 @@
         <v>0.91249999999999998</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="J71" s="20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P71">
         <v>725</v>
@@ -13861,7 +13863,7 @@
         <v>1</v>
       </c>
       <c r="Y71" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.4">
@@ -13872,10 +13874,10 @@
         <v>0.92291666666666672</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="J72" s="20" t="s">
         <v>48</v>
@@ -13905,7 +13907,7 @@
         <v>1</v>
       </c>
       <c r="Y72" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.4">
@@ -13916,10 +13918,10 @@
         <v>0.92569444444444449</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="J73" s="20" t="s">
         <v>35</v>
@@ -13937,7 +13939,7 @@
         <v>1</v>
       </c>
       <c r="Y73" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.4">
@@ -13948,10 +13950,10 @@
         <v>0.92638888888888893</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="J74" s="20" t="s">
         <v>35</v>
@@ -13969,7 +13971,7 @@
         <v>1</v>
       </c>
       <c r="Y74" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.4">
@@ -13980,10 +13982,10 @@
         <v>0.92708333333333337</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>107</v>
+        <v>381</v>
       </c>
       <c r="J75" s="20" t="s">
         <v>20</v>
@@ -14019,7 +14021,7 @@
         <v>1</v>
       </c>
       <c r="Y75" t="s">
-        <v>124</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.4">
@@ -14030,10 +14032,10 @@
         <v>0.9291666666666667</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="J76" s="20" t="s">
         <v>24</v>
@@ -14066,7 +14068,7 @@
         <v>1</v>
       </c>
       <c r="Y76" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:25" s="15" customFormat="1" x14ac:dyDescent="0.4">
@@ -14077,7 +14079,7 @@
         <v>5</v>
       </c>
       <c r="L77" s="15" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="M77" s="15" t="s">
         <v>6</v>
@@ -14103,10 +14105,10 @@
         <v>0.69861111111111107</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>266</v>
+        <v>383</v>
       </c>
       <c r="J78" s="20" t="s">
         <v>35</v>
@@ -14124,7 +14126,7 @@
         <v>2</v>
       </c>
       <c r="Y78" t="s">
-        <v>267</v>
+        <v>382</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.4">
@@ -14135,10 +14137,10 @@
         <v>0.7</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="J79" s="20" t="s">
         <v>24</v>
@@ -14168,7 +14170,7 @@
         <v>2</v>
       </c>
       <c r="Y79" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.4">
@@ -14179,10 +14181,10 @@
         <v>0.70277777777777772</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="J80" s="20" t="s">
         <v>21</v>
@@ -14200,7 +14202,7 @@
         <v>2</v>
       </c>
       <c r="Y80" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.4">
@@ -14211,13 +14213,13 @@
         <v>0.70972222222222225</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="J81" s="20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P81">
         <v>3000</v>
@@ -14232,7 +14234,7 @@
         <v>2</v>
       </c>
       <c r="Y81" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.4">
@@ -14243,10 +14245,10 @@
         <v>0.71180555555555558</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="J82" s="20" t="s">
         <v>35</v>
@@ -14264,7 +14266,7 @@
         <v>2</v>
       </c>
       <c r="Y82" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.4">
@@ -14275,10 +14277,10 @@
         <v>0.71319444444444446</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="J83" s="20" t="s">
         <v>35</v>
@@ -14297,7 +14299,7 @@
         <v>2</v>
       </c>
       <c r="Y83" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.4">
@@ -14308,10 +14310,10 @@
         <v>0.71527777777777779</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="J84" s="20" t="s">
         <v>24</v>
@@ -14342,7 +14344,7 @@
         <v>2</v>
       </c>
       <c r="Y84" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.4">
@@ -14353,10 +14355,10 @@
         <v>0.71875</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="J85" s="20" t="s">
         <v>21</v>
@@ -14374,7 +14376,7 @@
         <v>2</v>
       </c>
       <c r="Y85" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.4">
@@ -14385,10 +14387,10 @@
         <v>0.72152777777777777</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="J86" s="20" t="s">
         <v>20</v>
@@ -14425,7 +14427,7 @@
         <v>2</v>
       </c>
       <c r="Y86" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.4">
@@ -14436,10 +14438,10 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="J87" s="20" t="s">
         <v>35</v>
@@ -14457,7 +14459,7 @@
         <v>2</v>
       </c>
       <c r="Y87" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.4">
@@ -14468,10 +14470,10 @@
         <v>0.73819444444444449</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="J88" s="20" t="s">
         <v>24</v>
@@ -14501,7 +14503,7 @@
         <v>2</v>
       </c>
       <c r="Y88" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.4">
@@ -14512,13 +14514,13 @@
         <v>0.74097222222222225</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="J89" s="20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K89">
         <v>1190</v>
@@ -14552,7 +14554,7 @@
         <v>2</v>
       </c>
       <c r="Y89" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.4">
@@ -14563,10 +14565,10 @@
         <v>0.75</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="J90" s="20" t="s">
         <v>48</v>
@@ -14593,7 +14595,7 @@
         <v>2</v>
       </c>
       <c r="Y90" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.4">
@@ -14604,10 +14606,10 @@
         <v>0.76111111111111107</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="J91" s="20" t="s">
         <v>48</v>
@@ -14634,7 +14636,7 @@
         <v>2</v>
       </c>
       <c r="Y91" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.4">
@@ -14645,10 +14647,10 @@
         <v>0.7631944444444444</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="J92" s="20" t="s">
         <v>24</v>
@@ -14681,7 +14683,7 @@
         <v>2</v>
       </c>
       <c r="Y92" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.4">
@@ -14692,10 +14694,10 @@
         <v>0.77638888888888891</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="J93" s="20" t="s">
         <v>24</v>
@@ -14726,7 +14728,7 @@
         <v>2</v>
       </c>
       <c r="Y93" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.4">
@@ -14737,10 +14739,10 @@
         <v>0.77986111111111112</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="J94" s="20" t="s">
         <v>48</v>
@@ -14764,7 +14766,7 @@
         <v>2</v>
       </c>
       <c r="Y94" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.4">
@@ -14775,13 +14777,13 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="J95" s="20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P95">
         <f>1500/2</f>
@@ -14797,7 +14799,7 @@
         <v>2</v>
       </c>
       <c r="Y95" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.4">
@@ -14808,10 +14810,10 @@
         <v>0.78680555555555554</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="J96" s="20" t="s">
         <v>21</v>
@@ -14829,7 +14831,7 @@
         <v>2</v>
       </c>
       <c r="Y96" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.4">
@@ -14840,10 +14842,10 @@
         <v>0.79027777777777775</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="J97" s="20" t="s">
         <v>20</v>
@@ -14880,7 +14882,7 @@
         <v>2</v>
       </c>
       <c r="Y97" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.4">
@@ -14891,10 +14893,10 @@
         <v>0.8</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="J98" s="20" t="s">
         <v>48</v>
@@ -14918,7 +14920,7 @@
         <v>2</v>
       </c>
       <c r="Y98" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.4">
@@ -14929,10 +14931,10 @@
         <v>0.80138888888888893</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="J99" s="20" t="s">
         <v>35</v>
@@ -14950,7 +14952,7 @@
         <v>2</v>
       </c>
       <c r="Y99" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.4">
@@ -14961,10 +14963,10 @@
         <v>0.80972222222222223</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="J100" s="20" t="s">
         <v>24</v>
@@ -14985,7 +14987,7 @@
         <v>2</v>
       </c>
       <c r="Y100" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.4">
@@ -14996,10 +14998,10 @@
         <v>0.81666666666666665</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="J101" s="20" t="s">
         <v>24</v>
@@ -15030,7 +15032,7 @@
         <v>2</v>
       </c>
       <c r="Y101" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.4">
@@ -15041,10 +15043,10 @@
         <v>0.82222222222222219</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="J102" s="20" t="s">
         <v>21</v>
@@ -15062,7 +15064,7 @@
         <v>2</v>
       </c>
       <c r="Y102" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.4">
@@ -15073,10 +15075,10 @@
         <v>0.82708333333333328</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="J103" s="20" t="s">
         <v>24</v>
@@ -15110,7 +15112,7 @@
         <v>2</v>
       </c>
       <c r="Y103" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.4">
@@ -15121,10 +15123,10 @@
         <v>0.83819444444444446</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="J104" s="20" t="s">
         <v>35</v>
@@ -15145,7 +15147,7 @@
         <v>2</v>
       </c>
       <c r="Y104" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.4">
@@ -15156,10 +15158,10 @@
         <v>0.84027777777777779</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="J105" s="20" t="s">
         <v>48</v>
@@ -15189,7 +15191,7 @@
         <v>2</v>
       </c>
       <c r="Y105" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.4">
@@ -15200,10 +15202,10 @@
         <v>0.84375</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="J106" s="20" t="s">
         <v>35</v>
@@ -15221,7 +15223,7 @@
         <v>2</v>
       </c>
       <c r="Y106" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.4">
@@ -15232,10 +15234,10 @@
         <v>0.85069444444444442</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="J107" s="20" t="s">
         <v>38</v>
@@ -15272,7 +15274,7 @@
         <v>2</v>
       </c>
       <c r="Y107" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.4">
@@ -15283,10 +15285,10 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="J108" s="20" t="s">
         <v>35</v>
@@ -15304,7 +15306,7 @@
         <v>2</v>
       </c>
       <c r="Y108" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
     </row>
     <row r="109" spans="1:25" s="15" customFormat="1" x14ac:dyDescent="0.4">
@@ -15393,51 +15395,43 @@
     <hyperlink ref="D30" r:id="rId28" xr:uid="{7FCA1409-2A7F-48D9-B888-FD1AF00A1D54}"/>
     <hyperlink ref="D31" r:id="rId29" xr:uid="{A3E654D2-3C80-4EDF-86EC-AAAC7B01DA30}"/>
     <hyperlink ref="D32" r:id="rId30" xr:uid="{E456A4BD-870B-4F40-8838-ED171E1FF425}"/>
-    <hyperlink ref="D33" r:id="rId31" xr:uid="{CB434C94-2B4A-4CDA-92D3-E2F4ABE385BD}"/>
-    <hyperlink ref="D34" r:id="rId32" xr:uid="{7BD77EF0-8032-461F-9774-7E184E3DBCFB}"/>
-    <hyperlink ref="D35" r:id="rId33" xr:uid="{8E85B2A5-E8FA-4852-A1B2-D33E45EC6B39}"/>
-    <hyperlink ref="D36" r:id="rId34" xr:uid="{41CA6DF9-5BF5-4DA5-93DC-C71E5845CABE}"/>
-    <hyperlink ref="D37" r:id="rId35" xr:uid="{1EE51ECD-69AF-494B-8520-BD6261336C89}"/>
-    <hyperlink ref="D41" r:id="rId36" xr:uid="{CE6ABC30-A360-4542-9DEE-683C8DDB8042}"/>
-    <hyperlink ref="D42" r:id="rId37" xr:uid="{BAE7041E-15D3-4E82-ACB1-FE2CC2921852}"/>
-    <hyperlink ref="D43" r:id="rId38" xr:uid="{79146B76-70C1-4682-9B9F-6016826D45FD}"/>
-    <hyperlink ref="D44" r:id="rId39" xr:uid="{B3B44629-3675-48AB-A896-4F1072B67029}"/>
-    <hyperlink ref="D45" r:id="rId40" xr:uid="{AAA1452F-C087-4087-9A36-47304200A25B}"/>
-    <hyperlink ref="D46" r:id="rId41" xr:uid="{58BA3545-02BC-4641-B982-97D2A73CCD98}"/>
-    <hyperlink ref="D47" r:id="rId42" xr:uid="{312BBE8A-5AA0-4EA5-A3D3-3C46F291B9DC}"/>
-    <hyperlink ref="D48" r:id="rId43" xr:uid="{E78EA705-C4CA-41CE-BB6A-DE06E5C36E30}"/>
-    <hyperlink ref="D49" r:id="rId44" xr:uid="{9AC29BD2-ED28-46F7-9DF7-E7C149BB65EE}"/>
-    <hyperlink ref="D50" r:id="rId45" xr:uid="{EBF959DC-367B-4FA9-AA50-D57F9F44FEB1}"/>
-    <hyperlink ref="D51" r:id="rId46" xr:uid="{42A02AE0-AF1E-4A62-8F38-0FFD796C521C}"/>
-    <hyperlink ref="D52" r:id="rId47" xr:uid="{233C5DFE-BEC5-4DD5-A564-9A42403184CD}"/>
-    <hyperlink ref="D53" r:id="rId48" xr:uid="{998E828F-A35D-47B7-9AFC-8E53F6BA3F1C}"/>
-    <hyperlink ref="D54" r:id="rId49" xr:uid="{AFFED709-8239-4FA3-9121-E2ADCD0F842F}"/>
-    <hyperlink ref="D55" r:id="rId50" xr:uid="{A1AB0FF5-712E-4BCE-BA42-BC46E8B8B3E8}"/>
-    <hyperlink ref="D56" r:id="rId51" xr:uid="{C08F5748-5739-4F5F-B521-43C37C580D00}"/>
-    <hyperlink ref="D57" r:id="rId52" xr:uid="{71554D1B-F9B1-490D-9819-224DB54580DF}"/>
-    <hyperlink ref="D58" r:id="rId53" xr:uid="{9D65CD39-25FB-40D0-8C96-2E9EA3C4E94D}"/>
-    <hyperlink ref="D59" r:id="rId54" xr:uid="{4C0F0048-A8CF-4382-9173-B555B3A2BD17}"/>
-    <hyperlink ref="D60" r:id="rId55" xr:uid="{BFB3DAF1-00FA-40C7-9AFD-504413148B14}"/>
-    <hyperlink ref="D61" r:id="rId56" xr:uid="{3C153DC1-7651-48CC-B70A-BB8F96EBB412}"/>
-    <hyperlink ref="D62" r:id="rId57" xr:uid="{6A01D59A-0361-45B4-B8B7-C1616567C3ED}"/>
-    <hyperlink ref="D63" r:id="rId58" xr:uid="{4AA3E144-4131-432C-8D00-69EDE0E48BD6}"/>
-    <hyperlink ref="D64" r:id="rId59" xr:uid="{595BC966-A242-4E1A-B35E-593FB9F5DB81}"/>
-    <hyperlink ref="D65" r:id="rId60" xr:uid="{8DF8CB04-C5EE-4608-BC08-316B9162FE8B}"/>
-    <hyperlink ref="D66" r:id="rId61" xr:uid="{E320E887-2E4E-4A15-9487-623EF9E36775}"/>
-    <hyperlink ref="D67" r:id="rId62" xr:uid="{2970998B-B166-4E3A-8AC5-295C3A6133E2}"/>
-    <hyperlink ref="D68" r:id="rId63" xr:uid="{99D72668-62E1-414D-A8FD-5BE14E55D238}"/>
-    <hyperlink ref="D69" r:id="rId64" xr:uid="{435035DD-083E-4E25-AC57-BF43FAB00460}"/>
-    <hyperlink ref="D70" r:id="rId65" xr:uid="{86428C06-7AEE-42F5-B729-C598EBED08EF}"/>
-    <hyperlink ref="D71" r:id="rId66" xr:uid="{EBB633DA-3CD1-4421-B9C2-5CB3514A982B}"/>
-    <hyperlink ref="D72" r:id="rId67" xr:uid="{234F2EA6-1990-4DC2-AEA0-4BA7837870FB}"/>
-    <hyperlink ref="D73" r:id="rId68" xr:uid="{732D4B70-FD82-435E-B5AA-CB8078A5C21D}"/>
-    <hyperlink ref="D74" r:id="rId69" xr:uid="{E265A52B-005B-48BB-847F-D4C8925D1768}"/>
-    <hyperlink ref="D75" r:id="rId70" xr:uid="{5BC5894A-BDD1-4763-A26A-8CF62ED3812A}"/>
-    <hyperlink ref="D76" r:id="rId71" xr:uid="{BC6E1B13-50C4-4FD0-B155-CB1484A528AB}"/>
-    <hyperlink ref="D5" r:id="rId72" xr:uid="{2A3CDF9E-BC79-46F9-B457-42B761ACD097}"/>
-    <hyperlink ref="D38" r:id="rId73" xr:uid="{CBEC265E-2E7F-49F7-AFE2-B854546EC169}"/>
-    <hyperlink ref="D39" r:id="rId74" xr:uid="{8989D088-3173-4782-9CBD-DFD3278E91D3}"/>
-    <hyperlink ref="D40" r:id="rId75" xr:uid="{E57FB86E-B967-4E0B-8660-AFEF8245A911}"/>
+    <hyperlink ref="D34" r:id="rId31" xr:uid="{7BD77EF0-8032-461F-9774-7E184E3DBCFB}"/>
+    <hyperlink ref="D35" r:id="rId32" xr:uid="{8E85B2A5-E8FA-4852-A1B2-D33E45EC6B39}"/>
+    <hyperlink ref="D37" r:id="rId33" xr:uid="{1EE51ECD-69AF-494B-8520-BD6261336C89}"/>
+    <hyperlink ref="D41" r:id="rId34" xr:uid="{CE6ABC30-A360-4542-9DEE-683C8DDB8042}"/>
+    <hyperlink ref="D42" r:id="rId35" xr:uid="{BAE7041E-15D3-4E82-ACB1-FE2CC2921852}"/>
+    <hyperlink ref="D43" r:id="rId36" xr:uid="{79146B76-70C1-4682-9B9F-6016826D45FD}"/>
+    <hyperlink ref="D46" r:id="rId37" xr:uid="{58BA3545-02BC-4641-B982-97D2A73CCD98}"/>
+    <hyperlink ref="D49" r:id="rId38" xr:uid="{9AC29BD2-ED28-46F7-9DF7-E7C149BB65EE}"/>
+    <hyperlink ref="D50" r:id="rId39" xr:uid="{EBF959DC-367B-4FA9-AA50-D57F9F44FEB1}"/>
+    <hyperlink ref="D51" r:id="rId40" xr:uid="{42A02AE0-AF1E-4A62-8F38-0FFD796C521C}"/>
+    <hyperlink ref="D52" r:id="rId41" xr:uid="{233C5DFE-BEC5-4DD5-A564-9A42403184CD}"/>
+    <hyperlink ref="D53" r:id="rId42" xr:uid="{998E828F-A35D-47B7-9AFC-8E53F6BA3F1C}"/>
+    <hyperlink ref="D54" r:id="rId43" xr:uid="{AFFED709-8239-4FA3-9121-E2ADCD0F842F}"/>
+    <hyperlink ref="D56" r:id="rId44" xr:uid="{C08F5748-5739-4F5F-B521-43C37C580D00}"/>
+    <hyperlink ref="D57" r:id="rId45" xr:uid="{71554D1B-F9B1-490D-9819-224DB54580DF}"/>
+    <hyperlink ref="D58" r:id="rId46" xr:uid="{9D65CD39-25FB-40D0-8C96-2E9EA3C4E94D}"/>
+    <hyperlink ref="D59" r:id="rId47" xr:uid="{4C0F0048-A8CF-4382-9173-B555B3A2BD17}"/>
+    <hyperlink ref="D60" r:id="rId48" xr:uid="{BFB3DAF1-00FA-40C7-9AFD-504413148B14}"/>
+    <hyperlink ref="D61" r:id="rId49" xr:uid="{3C153DC1-7651-48CC-B70A-BB8F96EBB412}"/>
+    <hyperlink ref="D62" r:id="rId50" xr:uid="{6A01D59A-0361-45B4-B8B7-C1616567C3ED}"/>
+    <hyperlink ref="D63" r:id="rId51" xr:uid="{4AA3E144-4131-432C-8D00-69EDE0E48BD6}"/>
+    <hyperlink ref="D64" r:id="rId52" xr:uid="{595BC966-A242-4E1A-B35E-593FB9F5DB81}"/>
+    <hyperlink ref="D65" r:id="rId53" xr:uid="{8DF8CB04-C5EE-4608-BC08-316B9162FE8B}"/>
+    <hyperlink ref="D66" r:id="rId54" xr:uid="{E320E887-2E4E-4A15-9487-623EF9E36775}"/>
+    <hyperlink ref="D67" r:id="rId55" xr:uid="{2970998B-B166-4E3A-8AC5-295C3A6133E2}"/>
+    <hyperlink ref="D68" r:id="rId56" xr:uid="{99D72668-62E1-414D-A8FD-5BE14E55D238}"/>
+    <hyperlink ref="D69" r:id="rId57" xr:uid="{435035DD-083E-4E25-AC57-BF43FAB00460}"/>
+    <hyperlink ref="D70" r:id="rId58" xr:uid="{86428C06-7AEE-42F5-B729-C598EBED08EF}"/>
+    <hyperlink ref="D71" r:id="rId59" xr:uid="{EBB633DA-3CD1-4421-B9C2-5CB3514A982B}"/>
+    <hyperlink ref="D72" r:id="rId60" xr:uid="{234F2EA6-1990-4DC2-AEA0-4BA7837870FB}"/>
+    <hyperlink ref="D73" r:id="rId61" xr:uid="{732D4B70-FD82-435E-B5AA-CB8078A5C21D}"/>
+    <hyperlink ref="D74" r:id="rId62" xr:uid="{E265A52B-005B-48BB-847F-D4C8925D1768}"/>
+    <hyperlink ref="D76" r:id="rId63" xr:uid="{BC6E1B13-50C4-4FD0-B155-CB1484A528AB}"/>
+    <hyperlink ref="D5" r:id="rId64" xr:uid="{2A3CDF9E-BC79-46F9-B457-42B761ACD097}"/>
+    <hyperlink ref="D38" r:id="rId65" xr:uid="{CBEC265E-2E7F-49F7-AFE2-B854546EC169}"/>
+    <hyperlink ref="D39" r:id="rId66" xr:uid="{8989D088-3173-4782-9CBD-DFD3278E91D3}"/>
+    <hyperlink ref="D40" r:id="rId67" xr:uid="{E57FB86E-B967-4E0B-8660-AFEF8245A911}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -15467,19 +15461,19 @@
   <sheetData>
     <row r="1" spans="1:26" s="4" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>54</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -15500,7 +15494,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
@@ -15530,16 +15524,16 @@
         <v>14</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>16</v>
@@ -15553,7 +15547,7 @@
         <v>0.75069444444444444</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>56</v>
@@ -15574,7 +15568,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.4">
@@ -15585,10 +15579,10 @@
         <v>0.80138888888888893</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="J3" t="s">
         <v>35</v>
@@ -15606,7 +15600,7 @@
         <v>2</v>
       </c>
       <c r="Y3" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -15623,7 +15617,7 @@
         <v>0.74583333333333335</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>55</v>
@@ -15656,7 +15650,7 @@
         <v>1</v>
       </c>
       <c r="Y5" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.4">
@@ -15667,10 +15661,10 @@
         <v>0.77638888888888891</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="J6" t="s">
         <v>24</v>
@@ -15701,7 +15695,7 @@
         <v>2</v>
       </c>
       <c r="Y6" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -15734,13 +15728,13 @@
         <v>0.91249999999999998</v>
       </c>
       <c r="C8" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="J8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P8">
         <v>725</v>
@@ -15755,7 +15749,7 @@
         <v>1</v>
       </c>
       <c r="Y8" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.4">
@@ -15766,13 +15760,13 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="J9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P9">
         <f>1500/2</f>
@@ -15788,7 +15782,7 @@
         <v>2</v>
       </c>
       <c r="Y9" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -15805,7 +15799,7 @@
         <v>0.75972222222222219</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>58</v>
@@ -15826,7 +15820,7 @@
         <v>5200</v>
       </c>
       <c r="U11" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="V11" t="s">
         <v>26</v>
@@ -15838,7 +15832,7 @@
         <v>1</v>
       </c>
       <c r="Y11" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.4">
@@ -15849,10 +15843,10 @@
         <v>0.75</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="J12" t="s">
         <v>48</v>
@@ -15879,7 +15873,7 @@
         <v>2</v>
       </c>
       <c r="Y12" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -15908,10 +15902,10 @@
         <v>0.91041666666666665</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J14" t="s">
         <v>21</v>
@@ -15929,7 +15923,7 @@
         <v>1</v>
       </c>
       <c r="Y14" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.4">
@@ -15940,10 +15934,10 @@
         <v>0.78680555555555554</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="J15" t="s">
         <v>21</v>
@@ -15961,7 +15955,7 @@
         <v>2</v>
       </c>
       <c r="Y15" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -15978,10 +15972,10 @@
         <v>0.92291666666666672</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="J17" t="s">
         <v>48</v>
@@ -16011,7 +16005,7 @@
         <v>1</v>
       </c>
       <c r="Y17" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.4">
@@ -16022,10 +16016,10 @@
         <v>0.71527777777777779</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="J18" t="s">
         <v>24</v>
@@ -16056,7 +16050,7 @@
         <v>2</v>
       </c>
       <c r="Y18" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -16089,10 +16083,10 @@
         <v>0.92569444444444449</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="J20" t="s">
         <v>35</v>
@@ -16110,7 +16104,7 @@
         <v>1</v>
       </c>
       <c r="Y20" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.4">
@@ -16121,10 +16115,10 @@
         <v>0.71319444444444446</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="J21" t="s">
         <v>35</v>
@@ -16143,7 +16137,7 @@
         <v>2</v>
       </c>
       <c r="Y21" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -16160,10 +16154,10 @@
         <v>0.92638888888888893</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="J23" t="s">
         <v>35</v>
@@ -16181,7 +16175,7 @@
         <v>1</v>
       </c>
       <c r="Y23" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.4">
@@ -16192,10 +16186,10 @@
         <v>0.71180555555555558</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="J24" t="s">
         <v>35</v>
@@ -16213,7 +16207,7 @@
         <v>2</v>
       </c>
       <c r="Y24" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -16230,10 +16224,10 @@
         <v>0.84652777777777777</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J26" s="20" t="s">
         <v>35</v>
@@ -16251,7 +16245,7 @@
         <v>1</v>
       </c>
       <c r="Y26" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.4">
@@ -16262,10 +16256,10 @@
         <v>0.84375</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="J27" s="20" t="s">
         <v>35</v>
@@ -16283,7 +16277,7 @@
         <v>2</v>
       </c>
       <c r="Y27" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
@@ -16328,12 +16322,12 @@
     <row r="37" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A38" s="18" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.4">
       <c r="L39" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="P39">
         <f>MEDIAN(Q39:Q57)</f>
@@ -16480,17 +16474,17 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="B3" t="str">
         <f>CONCATENATE("POINT(",RIGHT(A3,10), " ",LEFT(A3,10),")")</f>
@@ -16499,7 +16493,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B31" si="0">CONCATENATE("POINT(",RIGHT(A4,10), " ",LEFT(A4,10),")")</f>
@@ -16508,7 +16502,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="0"/>
@@ -16517,7 +16511,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="0"/>
@@ -16526,7 +16520,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="0"/>
@@ -16535,7 +16529,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="0"/>
@@ -16544,7 +16538,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="0"/>
@@ -16553,7 +16547,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="0"/>
@@ -16562,7 +16556,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
@@ -16571,7 +16565,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="0"/>
@@ -16580,7 +16574,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="0"/>
@@ -16589,7 +16583,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="0"/>
@@ -16598,7 +16592,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="0"/>
@@ -16607,7 +16601,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="0"/>
@@ -16616,7 +16610,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="0"/>
@@ -16625,7 +16619,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="0"/>
@@ -16634,7 +16628,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="0"/>
@@ -16643,7 +16637,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="0"/>
@@ -16652,7 +16646,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="0"/>
@@ -16661,7 +16655,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="0"/>
@@ -16670,7 +16664,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="0"/>
@@ -16679,7 +16673,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="0"/>
@@ -16688,7 +16682,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="0"/>
@@ -16697,7 +16691,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="0"/>
@@ -16706,7 +16700,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="0"/>
@@ -16715,7 +16709,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="0"/>
@@ -16724,7 +16718,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="0"/>
@@ -16733,7 +16727,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="0"/>
@@ -16742,7 +16736,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="0"/>

--- a/data/comercios_territorio_sp.xlsx
+++ b/data/comercios_territorio_sp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\as\Documents\00_TESIS\meu_tesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B99F21D-094A-4959-A234-9EE112C76D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35640A37-CDF8-4797-A2B8-F2ED6477C565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{7FC3CCF3-7BCA-42E8-BEEE-4B41A7F93BBF}"/>
   </bookViews>
@@ -173,9 +173,6 @@
     <t>Verduleria</t>
   </si>
   <si>
-    <t>https://maps.google.com/maps?q=-34.59735870361328%2C-58.3789176940918&amp;z=17&amp;hl=es</t>
-  </si>
-  <si>
     <t>https://maps.google.com/maps?q=-34.59750747680664%2C-58.3781852722168&amp;z=17&amp;hl=es</t>
   </si>
   <si>
@@ -251,9 +248,6 @@
     <t>Supermercado Disco</t>
   </si>
   <si>
-    <t>https://www.google.com/maps?q=-34.5927734375,-58.376285552978516&amp;z=17&amp;hl=es</t>
-  </si>
-  <si>
     <t>Supermercado Jumbo</t>
   </si>
   <si>
@@ -296,9 +290,6 @@
     <t>https://www.google.com/maps?q=-34.59286880493164,-58.37950897216797&amp;z=17&amp;hl=es</t>
   </si>
   <si>
-    <t>https://www.google.com/maps?q=-34.592735290527344,-58.37911605834961&amp;z=17&amp;hl=es</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps?q=-34.595916748046875,-58.37848663330078&amp;z=17&amp;hl=es</t>
   </si>
   <si>
@@ -449,9 +440,6 @@
     <t>POINT(-58.37844212398452 -34.59655767156747)</t>
   </si>
   <si>
-    <t>POINT(-58.37895525466836 -34.5971643780612)</t>
-  </si>
-  <si>
     <t>POINT(-58.378201396997426 -34.597295515245946)</t>
   </si>
   <si>
@@ -509,9 +497,6 @@
     <t>POINT(-58.3784753258331 -34.59167239737799)</t>
   </si>
   <si>
-    <t>POINT(-58.37626951049113 -34.592587899421325)</t>
-  </si>
-  <si>
     <t>POINT(-58.38104853932667 -34.59403893884416)</t>
   </si>
   <si>
@@ -545,9 +530,6 @@
     <t>POINT(-58.37947145282013 -34.592665635486746)</t>
   </si>
   <si>
-    <t>POINT(-58.37910001049114 -34.59254979933628)</t>
-  </si>
-  <si>
     <t>POINT(-58.378459781655636 -34.59576653342594)</t>
   </si>
   <si>
@@ -1239,6 +1221,24 @@
   </si>
   <si>
     <t>POINT(-58.37935967209949 -34.59165991469645)</t>
+  </si>
+  <si>
+    <t>POINT(-58.37905910670746 -34.5927824431818)</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Juncal+833,+C1062ABE+Cdad.+Aut%C3%B3noma+de+Buenos+Aires/@-34.5928161,-58.3791828,21z/data=!4m6!3m5!1s0x95bccab6c10e43a7:0x9da6744281d0fbdb!8m2!3d-34.5927941!4d-58.3790592!16s%2Fg%2F11dfh48dx7?hl=es&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>POINT(-58.376197216356985 -34.5928172847864)</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/@-34.5928267,-58.3763974,21z?hl=es&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>POINT(-58.37869881477214 -34.5976081096709)</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/34%C2%B035'50.5%22S+58%C2%B022'44.1%22W/@-34.5975982,-58.3788232,21z/data=!4m4!3m3!8m2!3d-34.5973587!4d-58.3789177?hl=es&amp;entry=ttu&amp;g_ep=EgoyMDI2MDMxMS4wIKXMDSoASAFQAw%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -1775,19 +1775,19 @@
   <sheetData>
     <row r="1" spans="1:26" s="4" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
@@ -1838,16 +1838,16 @@
         <v>14</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>16</v>
@@ -1861,7 +1861,7 @@
         <v>0.95277777777777772</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>17</v>
@@ -1898,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.4">
@@ -1909,7 +1909,7 @@
         <v>0.95486111111111116</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>19</v>
@@ -1936,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="Y3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.4">
@@ -1947,13 +1947,13 @@
         <v>0.95625000000000004</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>22</v>
       </c>
       <c r="J4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
@@ -1978,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="Y4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.4">
@@ -1989,7 +1989,7 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>23</v>
@@ -2024,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="Y5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.4">
@@ -2035,7 +2035,7 @@
         <v>0.9604166666666667</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>27</v>
@@ -2062,7 +2062,7 @@
         <v>1</v>
       </c>
       <c r="Y6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.4">
@@ -2073,7 +2073,7 @@
         <v>0.96111111111111114</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2110,7 +2110,7 @@
         <v>1</v>
       </c>
       <c r="Y7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.4">
@@ -2121,7 +2121,7 @@
         <v>0.96597222222222223</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>30</v>
@@ -2148,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="Y8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.4">
@@ -2159,13 +2159,13 @@
         <v>0.96666666666666667</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="J9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K9" s="21">
         <v>2400</v>
@@ -2194,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="Y9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.4">
@@ -2205,7 +2205,7 @@
         <v>0.96805555555555556</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>32</v>
@@ -2242,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="Y10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.4">
@@ -2253,7 +2253,7 @@
         <v>0.97430555555555554</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>33</v>
@@ -2288,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="Y11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.4">
@@ -2299,7 +2299,7 @@
         <v>0.97638888888888886</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>34</v>
@@ -2326,7 +2326,7 @@
         <v>1</v>
       </c>
       <c r="Y12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.4">
@@ -2337,13 +2337,13 @@
         <v>0.97777777777777775</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>36</v>
+        <v>391</v>
       </c>
       <c r="J13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K13" s="21"/>
       <c r="L13" s="21">
@@ -2368,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="Y13" t="s">
-        <v>128</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.4">
@@ -2379,13 +2379,13 @@
         <v>0.97847222222222219</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" t="s">
         <v>37</v>
-      </c>
-      <c r="J14" t="s">
-        <v>38</v>
       </c>
       <c r="K14" s="21">
         <v>1740</v>
@@ -2414,7 +2414,7 @@
         <v>1</v>
       </c>
       <c r="Y14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.4">
@@ -2425,13 +2425,13 @@
         <v>0.98124999999999996</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K15" s="21"/>
       <c r="L15" s="21"/>
@@ -2454,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="Y15" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.4">
@@ -2465,10 +2465,10 @@
         <v>0.98263888888888884</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J16" t="s">
         <v>20</v>
@@ -2502,7 +2502,7 @@
         <v>1</v>
       </c>
       <c r="Y16" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.4">
@@ -2513,13 +2513,13 @@
         <v>0.98611111111111116</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K17" s="21">
         <v>1900</v>
@@ -2548,7 +2548,7 @@
         <v>1</v>
       </c>
       <c r="Y17" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.4">
@@ -2559,13 +2559,13 @@
         <v>0.99027777777777781</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K18" s="21"/>
       <c r="L18" s="21"/>
@@ -2590,7 +2590,7 @@
         <v>1</v>
       </c>
       <c r="Y18" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.4">
@@ -2601,10 +2601,10 @@
         <v>0.99097222222222225</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J19" t="s">
         <v>20</v>
@@ -2638,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="Y19" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.4">
@@ -2649,10 +2649,10 @@
         <v>0.99652777777777779</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J20" t="s">
         <v>24</v>
@@ -2688,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="Y20" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.4">
@@ -2699,10 +2699,10 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J21" t="s">
         <v>35</v>
@@ -2726,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="Y21" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.4">
@@ -2737,13 +2737,13 @@
         <v>0</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K22" s="21">
         <v>1390</v>
@@ -2772,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="Y22" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.4">
@@ -2783,13 +2783,13 @@
         <v>2.7777777777777779E-3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" t="s">
         <v>47</v>
-      </c>
-      <c r="J23" t="s">
-        <v>48</v>
       </c>
       <c r="K23" s="21"/>
       <c r="L23" s="21"/>
@@ -2812,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="Y23" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.4">
@@ -2823,10 +2823,10 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J24" t="s">
         <v>35</v>
@@ -2850,7 +2850,7 @@
         <v>1</v>
       </c>
       <c r="Y24" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.4">
@@ -2861,13 +2861,13 @@
         <v>4.8611111111111112E-3</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K25" s="21"/>
       <c r="L25" s="21">
@@ -2890,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="Y25" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.4">
@@ -2901,13 +2901,13 @@
         <v>5.5555555555555558E-3</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K26" s="21"/>
       <c r="L26" s="21"/>
@@ -2936,7 +2936,7 @@
         <v>1</v>
       </c>
       <c r="Y26" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.4">
@@ -2947,10 +2947,10 @@
         <v>9.0277777777777769E-3</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J27" t="s">
         <v>24</v>
@@ -2984,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="Y27" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.4">
@@ -2995,10 +2995,10 @@
         <v>0.73541666666666672</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J28" t="s">
         <v>24</v>
@@ -3032,7 +3032,7 @@
         <v>1</v>
       </c>
       <c r="Y28" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.4">
@@ -3043,10 +3043,10 @@
         <v>0.74583333333333335</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J29" t="s">
         <v>24</v>
@@ -3078,7 +3078,7 @@
         <v>1</v>
       </c>
       <c r="Y29" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.4">
@@ -3089,10 +3089,10 @@
         <v>0.75069444444444444</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J30" t="s">
         <v>35</v>
@@ -3116,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="Y30" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.4">
@@ -3127,10 +3127,10 @@
         <v>0.75138888888888888</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J31" t="s">
         <v>20</v>
@@ -3166,7 +3166,7 @@
         <v>1</v>
       </c>
       <c r="Y31" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.4">
@@ -3177,13 +3177,13 @@
         <v>0.75972222222222219</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D32" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J32" t="s">
         <v>58</v>
-      </c>
-      <c r="J32" t="s">
-        <v>59</v>
       </c>
       <c r="K32" s="21">
         <v>2100</v>
@@ -3201,7 +3201,7 @@
       <c r="P32" s="21"/>
       <c r="Q32" s="21"/>
       <c r="U32" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="V32" t="s">
         <v>26</v>
@@ -3213,7 +3213,7 @@
         <v>1</v>
       </c>
       <c r="Y32" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.4">
@@ -3224,13 +3224,13 @@
         <v>0.77013888888888893</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="J33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K33" s="21">
         <v>1485</v>
@@ -3261,7 +3261,7 @@
         <v>1</v>
       </c>
       <c r="Y33" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.4">
@@ -3272,13 +3272,13 @@
         <v>0.77361111111111114</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D34" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J34" t="s">
         <v>60</v>
-      </c>
-      <c r="J34" t="s">
-        <v>61</v>
       </c>
       <c r="K34" s="21">
         <v>1290</v>
@@ -3311,7 +3311,7 @@
         <v>1</v>
       </c>
       <c r="Y34" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.4">
@@ -3322,13 +3322,13 @@
         <v>0.78125</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>62</v>
+        <v>389</v>
       </c>
       <c r="J35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K35" s="21"/>
       <c r="L35" s="21">
@@ -3353,7 +3353,7 @@
         <v>1</v>
       </c>
       <c r="Y35" t="s">
-        <v>148</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.4">
@@ -3364,13 +3364,13 @@
         <v>0.78680555555555554</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="J36" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K36" s="21">
         <v>1950</v>
@@ -3403,7 +3403,7 @@
         <v>1</v>
       </c>
       <c r="Y36" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.4">
@@ -3414,10 +3414,10 @@
         <v>0.79236111111111107</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J37" t="s">
         <v>20</v>
@@ -3451,7 +3451,7 @@
         <v>1</v>
       </c>
       <c r="Y37" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.4">
@@ -3462,10 +3462,10 @@
         <v>0.79513888888888884</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J38" t="s">
         <v>35</v>
@@ -3489,7 +3489,7 @@
         <v>1</v>
       </c>
       <c r="Y38" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.4">
@@ -3500,10 +3500,10 @@
         <v>0.79583333333333328</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J39" t="s">
         <v>21</v>
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="Y39" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.4">
@@ -3538,13 +3538,13 @@
         <v>0.79722222222222228</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K40" s="21"/>
       <c r="L40" s="21">
@@ -3569,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="Y40" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.4">
@@ -3580,10 +3580,10 @@
         <v>0.80625000000000002</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J41" t="s">
         <v>35</v>
@@ -3607,7 +3607,7 @@
         <v>1</v>
       </c>
       <c r="Y41" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.4">
@@ -3618,13 +3618,13 @@
         <v>0.81388888888888888</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J42" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K42" s="21">
         <v>1290</v>
@@ -3657,7 +3657,7 @@
         <v>1</v>
       </c>
       <c r="Y42" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.4">
@@ -3668,10 +3668,10 @@
         <v>0.82152777777777775</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J43" t="s">
         <v>35</v>
@@ -3695,7 +3695,7 @@
         <v>1</v>
       </c>
       <c r="Y43" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.4">
@@ -3706,10 +3706,10 @@
         <v>0.82222222222222219</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="J44" t="s">
         <v>24</v>
@@ -3743,7 +3743,7 @@
         <v>1</v>
       </c>
       <c r="Y44" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.4">
@@ -3754,10 +3754,10 @@
         <v>0.82638888888888884</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="J45" t="s">
         <v>35</v>
@@ -3781,7 +3781,7 @@
         <v>1</v>
       </c>
       <c r="Y45" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.4">
@@ -3792,10 +3792,10 @@
         <v>0.82777777777777772</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J46" t="s">
         <v>35</v>
@@ -3819,7 +3819,7 @@
         <v>1</v>
       </c>
       <c r="Y46" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.4">
@@ -3830,10 +3830,10 @@
         <v>0.84652777777777777</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="J47" t="s">
         <v>35</v>
@@ -3857,7 +3857,7 @@
         <v>1</v>
       </c>
       <c r="Y47" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.4">
@@ -3868,10 +3868,10 @@
         <v>0.84930555555555554</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="J48" t="s">
         <v>35</v>
@@ -3895,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="Y48" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.4">
@@ -3906,13 +3906,13 @@
         <v>0.85277777777777775</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K49" s="21"/>
       <c r="L49" s="21">
@@ -3939,7 +3939,7 @@
         <v>1</v>
       </c>
       <c r="Y49" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.4">
@@ -3950,10 +3950,10 @@
         <v>0.85486111111111107</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J50" t="s">
         <v>24</v>
@@ -3985,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="Y50" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.4">
@@ -3996,10 +3996,10 @@
         <v>0.85763888888888884</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>77</v>
+        <v>387</v>
       </c>
       <c r="J51" t="s">
         <v>35</v>
@@ -4023,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="Y51" t="s">
-        <v>160</v>
+        <v>386</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.4">
@@ -4034,10 +4034,10 @@
         <v>0.86250000000000004</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J52" t="s">
         <v>20</v>
@@ -4073,7 +4073,7 @@
         <v>1</v>
       </c>
       <c r="Y52" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.4">
@@ -4084,10 +4084,10 @@
         <v>0.86284722222222221</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J53" t="s">
         <v>21</v>
@@ -4111,7 +4111,7 @@
         <v>1</v>
       </c>
       <c r="Y53" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.4">
@@ -4122,10 +4122,10 @@
         <v>0.86597222222222225</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J54" t="s">
         <v>35</v>
@@ -4149,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="Y54" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.4">
@@ -4160,10 +4160,10 @@
         <v>0.87013888888888891</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="J55" t="s">
         <v>24</v>
@@ -4195,7 +4195,7 @@
         <v>1</v>
       </c>
       <c r="Y55" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.4">
@@ -4206,10 +4206,10 @@
         <v>0.87569444444444444</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J56" t="s">
         <v>24</v>
@@ -4239,7 +4239,7 @@
         <v>1</v>
       </c>
       <c r="Y56" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.4">
@@ -4250,13 +4250,13 @@
         <v>0.88124999999999998</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K57" s="21">
         <v>1430</v>
@@ -4289,7 +4289,7 @@
         <v>1</v>
       </c>
       <c r="Y57" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.4">
@@ -4300,10 +4300,10 @@
         <v>0.89027777777777772</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J58" t="s">
         <v>35</v>
@@ -4327,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="Y58" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.4">
@@ -4338,10 +4338,10 @@
         <v>0.89097222222222228</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J59" t="s">
         <v>24</v>
@@ -4373,7 +4373,7 @@
         <v>1</v>
       </c>
       <c r="Y59" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.4">
@@ -4384,10 +4384,10 @@
         <v>0.89513888888888893</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="J60" t="s">
         <v>20</v>
@@ -4423,7 +4423,7 @@
         <v>1</v>
       </c>
       <c r="Y60" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.4">
@@ -4434,13 +4434,13 @@
         <v>0.8979166666666667</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K61" s="21">
         <v>1290</v>
@@ -4473,7 +4473,7 @@
         <v>1</v>
       </c>
       <c r="Y61" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.4">
@@ -4484,10 +4484,10 @@
         <v>0.90416666666666667</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J62" t="s">
         <v>35</v>
@@ -4511,7 +4511,7 @@
         <v>1</v>
       </c>
       <c r="Y62" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.4">
@@ -4522,13 +4522,13 @@
         <v>0.90486111111111112</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J63" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K63" s="21"/>
       <c r="L63" s="21">
@@ -4553,7 +4553,7 @@
         <v>1</v>
       </c>
       <c r="Y63" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.4">
@@ -4564,13 +4564,13 @@
         <v>0.90694444444444444</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J64" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K64" s="21"/>
       <c r="L64" s="21"/>
@@ -4591,7 +4591,7 @@
         <v>1</v>
       </c>
       <c r="Y64" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.4">
@@ -4602,10 +4602,10 @@
         <v>0.90729166666666672</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J65" t="s">
         <v>35</v>
@@ -4629,7 +4629,7 @@
         <v>1</v>
       </c>
       <c r="Y65" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.4">
@@ -4640,13 +4640,13 @@
         <v>0.90763888888888888</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J66" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K66" s="21"/>
       <c r="L66" s="21"/>
@@ -4667,7 +4667,7 @@
         <v>1</v>
       </c>
       <c r="Y66" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.4">
@@ -4678,13 +4678,13 @@
         <v>0.90798611111111116</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J67" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K67" s="21"/>
       <c r="L67" s="21"/>
@@ -4705,7 +4705,7 @@
         <v>1</v>
       </c>
       <c r="Y67" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.4">
@@ -4716,10 +4716,10 @@
         <v>0.90833333333333333</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J68" t="s">
         <v>35</v>
@@ -4743,7 +4743,7 @@
         <v>1</v>
       </c>
       <c r="Y68" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.4">
@@ -4754,10 +4754,10 @@
         <v>0.90902777777777777</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J69" t="s">
         <v>35</v>
@@ -4781,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="Y69" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.4">
@@ -4792,10 +4792,10 @@
         <v>0.91041666666666665</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J70" t="s">
         <v>21</v>
@@ -4819,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="Y70" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.4">
@@ -4830,13 +4830,13 @@
         <v>0.91249999999999998</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J71" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K71" s="21"/>
       <c r="L71" s="21"/>
@@ -4857,7 +4857,7 @@
         <v>1</v>
       </c>
       <c r="Y71" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.4">
@@ -4868,13 +4868,13 @@
         <v>0.92291666666666672</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J72" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K72" s="21">
         <v>1600</v>
@@ -4903,7 +4903,7 @@
         <v>1</v>
       </c>
       <c r="Y72" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.4">
@@ -4914,10 +4914,10 @@
         <v>0.92569444444444449</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J73" t="s">
         <v>35</v>
@@ -4941,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="Y73" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.4">
@@ -4952,10 +4952,10 @@
         <v>0.92638888888888893</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J74" t="s">
         <v>35</v>
@@ -4979,7 +4979,7 @@
         <v>1</v>
       </c>
       <c r="Y74" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.4">
@@ -4990,10 +4990,10 @@
         <v>0.92708333333333337</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="J75" t="s">
         <v>20</v>
@@ -5029,7 +5029,7 @@
         <v>1</v>
       </c>
       <c r="Y75" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.4">
@@ -5040,10 +5040,10 @@
         <v>0.9291666666666667</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J76" t="s">
         <v>24</v>
@@ -5077,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="Y76" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" spans="1:25" s="15" customFormat="1" x14ac:dyDescent="0.4">
@@ -5092,10 +5092,10 @@
         <v>0.69861111111111107</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="J78" t="s">
         <v>35</v>
@@ -5131,7 +5131,7 @@
         <v>2</v>
       </c>
       <c r="Y78" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.4">
@@ -5142,10 +5142,10 @@
         <v>0.7</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J79" t="s">
         <v>24</v>
@@ -5181,7 +5181,7 @@
         <v>2</v>
       </c>
       <c r="Y79" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.4">
@@ -5192,10 +5192,10 @@
         <v>0.70277777777777772</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="J80" t="s">
         <v>21</v>
@@ -5231,7 +5231,7 @@
         <v>2</v>
       </c>
       <c r="Y80" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.4">
@@ -5242,13 +5242,13 @@
         <v>0.70972222222222225</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="J81" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K81" s="21">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         <v>2</v>
       </c>
       <c r="Y81" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.4">
@@ -5292,10 +5292,10 @@
         <v>0.71875</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="J82" t="s">
         <v>21</v>
@@ -5331,7 +5331,7 @@
         <v>2</v>
       </c>
       <c r="Y82" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.4">
@@ -5342,10 +5342,10 @@
         <v>0.72152777777777777</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J83" t="s">
         <v>20</v>
@@ -5381,7 +5381,7 @@
         <v>2</v>
       </c>
       <c r="Y83" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.4">
@@ -5392,10 +5392,10 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="J84" t="s">
         <v>35</v>
@@ -5431,7 +5431,7 @@
         <v>2</v>
       </c>
       <c r="Y84" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.4">
@@ -5442,10 +5442,10 @@
         <v>0.73819444444444449</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="J85" t="s">
         <v>24</v>
@@ -5481,7 +5481,7 @@
         <v>2</v>
       </c>
       <c r="Y85" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.4">
@@ -5492,13 +5492,13 @@
         <v>0.74097222222222225</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J86" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K86" s="21">
         <v>1098.4615384615386</v>
@@ -5531,7 +5531,7 @@
         <v>2</v>
       </c>
       <c r="Y86" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.4">
@@ -5542,13 +5542,13 @@
         <v>0.76111111111111107</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="J87" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K87" s="21">
         <v>2030.7692307692309</v>
@@ -5581,7 +5581,7 @@
         <v>2</v>
       </c>
       <c r="Y87" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.4">
@@ -5592,10 +5592,10 @@
         <v>0.7631944444444444</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="J88" t="s">
         <v>24</v>
@@ -5631,7 +5631,7 @@
         <v>2</v>
       </c>
       <c r="Y88" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.4">
@@ -5642,13 +5642,13 @@
         <v>0.77986111111111112</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="J89" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K89" s="21">
         <v>0</v>
@@ -5681,7 +5681,7 @@
         <v>2</v>
       </c>
       <c r="Y89" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.4">
@@ -5692,10 +5692,10 @@
         <v>0.79027777777777775</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="J90" t="s">
         <v>20</v>
@@ -5731,7 +5731,7 @@
         <v>2</v>
       </c>
       <c r="Y90" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.4">
@@ -5742,13 +5742,13 @@
         <v>0.8</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="J91" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K91" s="21">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>2</v>
       </c>
       <c r="Y91" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.4">
@@ -5792,10 +5792,10 @@
         <v>0.80972222222222223</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="J92" t="s">
         <v>24</v>
@@ -5831,7 +5831,7 @@
         <v>2</v>
       </c>
       <c r="Y92" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.4">
@@ -5842,10 +5842,10 @@
         <v>0.81666666666666665</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="J93" t="s">
         <v>24</v>
@@ -5881,7 +5881,7 @@
         <v>2</v>
       </c>
       <c r="Y93" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.4">
@@ -5892,10 +5892,10 @@
         <v>0.82222222222222219</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="J94" t="s">
         <v>21</v>
@@ -5931,7 +5931,7 @@
         <v>2</v>
       </c>
       <c r="Y94" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.4">
@@ -5942,10 +5942,10 @@
         <v>0.82708333333333328</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="J95" t="s">
         <v>24</v>
@@ -5981,7 +5981,7 @@
         <v>2</v>
       </c>
       <c r="Y95" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.4">
@@ -5992,10 +5992,10 @@
         <v>0.83819444444444446</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="J96" t="s">
         <v>35</v>
@@ -6031,7 +6031,7 @@
         <v>2</v>
       </c>
       <c r="Y96" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.4">
@@ -6042,13 +6042,13 @@
         <v>0.84027777777777779</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="J97" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K97" s="21">
         <v>2030.7692307692309</v>
@@ -6081,7 +6081,7 @@
         <v>2</v>
       </c>
       <c r="Y97" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.4">
@@ -6092,13 +6092,13 @@
         <v>0.85069444444444442</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="J98" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K98" s="21">
         <v>1190.7692307692309</v>
@@ -6131,7 +6131,7 @@
         <v>2</v>
       </c>
       <c r="Y98" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.4">
@@ -6142,10 +6142,10 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="J99" t="s">
         <v>35</v>
@@ -6181,7 +6181,7 @@
         <v>2</v>
       </c>
       <c r="Y99" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="100" spans="1:25" s="15" customFormat="1" x14ac:dyDescent="0.4">
@@ -6268,19 +6268,19 @@
   <sheetData>
     <row r="1" spans="1:26" s="4" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -6301,7 +6301,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
@@ -6331,16 +6331,16 @@
         <v>14</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>16</v>
@@ -6354,7 +6354,7 @@
         <v>0.95277777777777772</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>17</v>
@@ -6391,7 +6391,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.4">
@@ -6402,7 +6402,7 @@
         <v>0.95486111111111116</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>19</v>
@@ -6429,7 +6429,7 @@
         <v>1</v>
       </c>
       <c r="Y3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.4">
@@ -6440,13 +6440,13 @@
         <v>0.95625000000000004</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>22</v>
       </c>
       <c r="J4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
@@ -6471,7 +6471,7 @@
         <v>1</v>
       </c>
       <c r="Y4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.4">
@@ -6482,7 +6482,7 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>23</v>
@@ -6517,7 +6517,7 @@
         <v>1</v>
       </c>
       <c r="Y5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.4">
@@ -6528,7 +6528,7 @@
         <v>0.9604166666666667</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>27</v>
@@ -6555,7 +6555,7 @@
         <v>1</v>
       </c>
       <c r="Y6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.4">
@@ -6566,7 +6566,7 @@
         <v>0.96111111111111114</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -6603,7 +6603,7 @@
         <v>1</v>
       </c>
       <c r="Y7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.4">
@@ -6614,7 +6614,7 @@
         <v>0.96597222222222223</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>30</v>
@@ -6641,7 +6641,7 @@
         <v>1</v>
       </c>
       <c r="Y8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.4">
@@ -6652,13 +6652,13 @@
         <v>0.96666666666666667</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="J9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K9" s="21">
         <v>2400</v>
@@ -6687,7 +6687,7 @@
         <v>1</v>
       </c>
       <c r="Y9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.4">
@@ -6698,7 +6698,7 @@
         <v>0.96805555555555556</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>32</v>
@@ -6735,7 +6735,7 @@
         <v>1</v>
       </c>
       <c r="Y10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.4">
@@ -6746,7 +6746,7 @@
         <v>0.97430555555555554</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>33</v>
@@ -6781,7 +6781,7 @@
         <v>1</v>
       </c>
       <c r="Y11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.4">
@@ -6792,7 +6792,7 @@
         <v>0.97638888888888886</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>34</v>
@@ -6819,7 +6819,7 @@
         <v>1</v>
       </c>
       <c r="Y12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.4">
@@ -6830,13 +6830,13 @@
         <v>0.97777777777777775</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>36</v>
+        <v>391</v>
       </c>
       <c r="J13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K13" s="21"/>
       <c r="L13" s="21">
@@ -6861,7 +6861,7 @@
         <v>1</v>
       </c>
       <c r="Y13" t="s">
-        <v>128</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.4">
@@ -6872,13 +6872,13 @@
         <v>0.97847222222222219</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" t="s">
         <v>37</v>
-      </c>
-      <c r="J14" t="s">
-        <v>38</v>
       </c>
       <c r="K14" s="21">
         <v>1740</v>
@@ -6907,7 +6907,7 @@
         <v>1</v>
       </c>
       <c r="Y14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.4">
@@ -6918,13 +6918,13 @@
         <v>0.98124999999999996</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K15" s="21"/>
       <c r="L15" s="21"/>
@@ -6947,7 +6947,7 @@
         <v>1</v>
       </c>
       <c r="Y15" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.4">
@@ -6958,10 +6958,10 @@
         <v>0.98263888888888884</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J16" t="s">
         <v>20</v>
@@ -6995,7 +6995,7 @@
         <v>1</v>
       </c>
       <c r="Y16" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.4">
@@ -7006,13 +7006,13 @@
         <v>0.98611111111111116</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K17" s="21">
         <v>1900</v>
@@ -7041,7 +7041,7 @@
         <v>1</v>
       </c>
       <c r="Y17" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.4">
@@ -7052,13 +7052,13 @@
         <v>0.99027777777777781</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K18" s="21"/>
       <c r="L18" s="21"/>
@@ -7083,7 +7083,7 @@
         <v>1</v>
       </c>
       <c r="Y18" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.4">
@@ -7094,10 +7094,10 @@
         <v>0.99097222222222225</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J19" t="s">
         <v>20</v>
@@ -7131,7 +7131,7 @@
         <v>1</v>
       </c>
       <c r="Y19" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.4">
@@ -7142,10 +7142,10 @@
         <v>0.99652777777777779</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J20" t="s">
         <v>24</v>
@@ -7181,7 +7181,7 @@
         <v>1</v>
       </c>
       <c r="Y20" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.4">
@@ -7192,10 +7192,10 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J21" t="s">
         <v>35</v>
@@ -7219,7 +7219,7 @@
         <v>1</v>
       </c>
       <c r="Y21" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.4">
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K22" s="21">
         <v>1390</v>
@@ -7265,7 +7265,7 @@
         <v>1</v>
       </c>
       <c r="Y22" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.4">
@@ -7276,13 +7276,13 @@
         <v>2.7777777777777779E-3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" t="s">
         <v>47</v>
-      </c>
-      <c r="J23" t="s">
-        <v>48</v>
       </c>
       <c r="K23" s="21"/>
       <c r="L23" s="21"/>
@@ -7305,7 +7305,7 @@
         <v>1</v>
       </c>
       <c r="Y23" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.4">
@@ -7316,10 +7316,10 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J24" t="s">
         <v>35</v>
@@ -7343,7 +7343,7 @@
         <v>1</v>
       </c>
       <c r="Y24" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.4">
@@ -7354,13 +7354,13 @@
         <v>4.8611111111111112E-3</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K25" s="21"/>
       <c r="L25" s="21">
@@ -7383,7 +7383,7 @@
         <v>1</v>
       </c>
       <c r="Y25" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.4">
@@ -7394,13 +7394,13 @@
         <v>5.5555555555555558E-3</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K26" s="21"/>
       <c r="L26" s="21"/>
@@ -7429,7 +7429,7 @@
         <v>1</v>
       </c>
       <c r="Y26" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.4">
@@ -7440,10 +7440,10 @@
         <v>9.0277777777777769E-3</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J27" t="s">
         <v>24</v>
@@ -7477,7 +7477,7 @@
         <v>1</v>
       </c>
       <c r="Y27" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.4">
@@ -7488,10 +7488,10 @@
         <v>0.73541666666666672</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J28" t="s">
         <v>24</v>
@@ -7525,7 +7525,7 @@
         <v>1</v>
       </c>
       <c r="Y28" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.4">
@@ -7536,10 +7536,10 @@
         <v>0.74583333333333335</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J29" t="s">
         <v>24</v>
@@ -7571,7 +7571,7 @@
         <v>1</v>
       </c>
       <c r="Y29" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.4">
@@ -7582,10 +7582,10 @@
         <v>0.75069444444444444</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J30" t="s">
         <v>35</v>
@@ -7609,7 +7609,7 @@
         <v>1</v>
       </c>
       <c r="Y30" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.4">
@@ -7620,10 +7620,10 @@
         <v>0.75138888888888888</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J31" t="s">
         <v>20</v>
@@ -7659,7 +7659,7 @@
         <v>1</v>
       </c>
       <c r="Y31" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.4">
@@ -7670,13 +7670,13 @@
         <v>0.75972222222222219</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D32" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J32" t="s">
         <v>58</v>
-      </c>
-      <c r="J32" t="s">
-        <v>59</v>
       </c>
       <c r="K32" s="21">
         <v>2100</v>
@@ -7694,7 +7694,7 @@
       <c r="P32" s="21"/>
       <c r="Q32" s="21"/>
       <c r="U32" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="V32" t="s">
         <v>26</v>
@@ -7706,7 +7706,7 @@
         <v>1</v>
       </c>
       <c r="Y32" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.4">
@@ -7717,13 +7717,13 @@
         <v>0.77013888888888893</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="J33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K33" s="21">
         <v>1485</v>
@@ -7754,7 +7754,7 @@
         <v>1</v>
       </c>
       <c r="Y33" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.4">
@@ -7765,13 +7765,13 @@
         <v>0.77361111111111114</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D34" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J34" t="s">
         <v>60</v>
-      </c>
-      <c r="J34" t="s">
-        <v>61</v>
       </c>
       <c r="K34" s="21">
         <v>1290</v>
@@ -7804,7 +7804,7 @@
         <v>1</v>
       </c>
       <c r="Y34" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.4">
@@ -7815,13 +7815,13 @@
         <v>0.78125</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>62</v>
+        <v>389</v>
       </c>
       <c r="J35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K35" s="21"/>
       <c r="L35" s="21">
@@ -7846,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="Y35" t="s">
-        <v>148</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.4">
@@ -7857,13 +7857,13 @@
         <v>0.78680555555555554</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="J36" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K36" s="21">
         <v>1950</v>
@@ -7896,7 +7896,7 @@
         <v>1</v>
       </c>
       <c r="Y36" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.4">
@@ -7907,10 +7907,10 @@
         <v>0.79236111111111107</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J37" t="s">
         <v>20</v>
@@ -7944,7 +7944,7 @@
         <v>1</v>
       </c>
       <c r="Y37" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.4">
@@ -7955,10 +7955,10 @@
         <v>0.79513888888888884</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J38" t="s">
         <v>35</v>
@@ -7982,7 +7982,7 @@
         <v>1</v>
       </c>
       <c r="Y38" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.4">
@@ -7993,10 +7993,10 @@
         <v>0.79583333333333328</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J39" t="s">
         <v>21</v>
@@ -8020,7 +8020,7 @@
         <v>1</v>
       </c>
       <c r="Y39" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.4">
@@ -8031,13 +8031,13 @@
         <v>0.79722222222222228</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K40" s="21"/>
       <c r="L40" s="21">
@@ -8062,7 +8062,7 @@
         <v>1</v>
       </c>
       <c r="Y40" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.4">
@@ -8073,10 +8073,10 @@
         <v>0.80625000000000002</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J41" t="s">
         <v>35</v>
@@ -8100,7 +8100,7 @@
         <v>1</v>
       </c>
       <c r="Y41" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.4">
@@ -8111,13 +8111,13 @@
         <v>0.81388888888888888</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J42" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K42" s="21">
         <v>1290</v>
@@ -8150,7 +8150,7 @@
         <v>1</v>
       </c>
       <c r="Y42" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.4">
@@ -8161,10 +8161,10 @@
         <v>0.82152777777777775</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J43" t="s">
         <v>35</v>
@@ -8188,7 +8188,7 @@
         <v>1</v>
       </c>
       <c r="Y43" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.4">
@@ -8199,10 +8199,10 @@
         <v>0.82222222222222219</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="J44" t="s">
         <v>24</v>
@@ -8236,7 +8236,7 @@
         <v>1</v>
       </c>
       <c r="Y44" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.4">
@@ -8247,10 +8247,10 @@
         <v>0.82638888888888884</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="J45" t="s">
         <v>35</v>
@@ -8274,7 +8274,7 @@
         <v>1</v>
       </c>
       <c r="Y45" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.4">
@@ -8285,10 +8285,10 @@
         <v>0.82777777777777772</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J46" t="s">
         <v>35</v>
@@ -8312,7 +8312,7 @@
         <v>1</v>
       </c>
       <c r="Y46" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.4">
@@ -8323,10 +8323,10 @@
         <v>0.84652777777777777</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="J47" t="s">
         <v>35</v>
@@ -8350,7 +8350,7 @@
         <v>1</v>
       </c>
       <c r="Y47" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.4">
@@ -8361,10 +8361,10 @@
         <v>0.84930555555555554</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="J48" t="s">
         <v>35</v>
@@ -8388,7 +8388,7 @@
         <v>1</v>
       </c>
       <c r="Y48" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.4">
@@ -8399,13 +8399,13 @@
         <v>0.85277777777777775</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K49" s="21"/>
       <c r="L49" s="21">
@@ -8432,7 +8432,7 @@
         <v>1</v>
       </c>
       <c r="Y49" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.4">
@@ -8443,10 +8443,10 @@
         <v>0.85486111111111107</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J50" t="s">
         <v>24</v>
@@ -8478,7 +8478,7 @@
         <v>1</v>
       </c>
       <c r="Y50" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.4">
@@ -8489,10 +8489,10 @@
         <v>0.85763888888888884</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>77</v>
+        <v>387</v>
       </c>
       <c r="J51" t="s">
         <v>35</v>
@@ -8516,7 +8516,7 @@
         <v>1</v>
       </c>
       <c r="Y51" t="s">
-        <v>160</v>
+        <v>386</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.4">
@@ -8527,10 +8527,10 @@
         <v>0.86250000000000004</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J52" t="s">
         <v>20</v>
@@ -8566,7 +8566,7 @@
         <v>1</v>
       </c>
       <c r="Y52" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.4">
@@ -8577,10 +8577,10 @@
         <v>0.86284722222222221</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J53" t="s">
         <v>21</v>
@@ -8604,7 +8604,7 @@
         <v>1</v>
       </c>
       <c r="Y53" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.4">
@@ -8615,10 +8615,10 @@
         <v>0.86597222222222225</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J54" t="s">
         <v>35</v>
@@ -8642,7 +8642,7 @@
         <v>1</v>
       </c>
       <c r="Y54" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.4">
@@ -8653,10 +8653,10 @@
         <v>0.87013888888888891</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="J55" t="s">
         <v>24</v>
@@ -8688,7 +8688,7 @@
         <v>1</v>
       </c>
       <c r="Y55" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.4">
@@ -8699,10 +8699,10 @@
         <v>0.87569444444444444</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J56" t="s">
         <v>24</v>
@@ -8732,7 +8732,7 @@
         <v>1</v>
       </c>
       <c r="Y56" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.4">
@@ -8743,13 +8743,13 @@
         <v>0.88124999999999998</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K57" s="21">
         <v>1430</v>
@@ -8782,7 +8782,7 @@
         <v>1</v>
       </c>
       <c r="Y57" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.4">
@@ -8793,10 +8793,10 @@
         <v>0.89027777777777772</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J58" t="s">
         <v>35</v>
@@ -8820,7 +8820,7 @@
         <v>1</v>
       </c>
       <c r="Y58" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.4">
@@ -8831,10 +8831,10 @@
         <v>0.89097222222222228</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J59" t="s">
         <v>24</v>
@@ -8866,7 +8866,7 @@
         <v>1</v>
       </c>
       <c r="Y59" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.4">
@@ -8877,10 +8877,10 @@
         <v>0.89513888888888893</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="J60" t="s">
         <v>20</v>
@@ -8916,7 +8916,7 @@
         <v>1</v>
       </c>
       <c r="Y60" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.4">
@@ -8927,13 +8927,13 @@
         <v>0.8979166666666667</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K61" s="21">
         <v>1290</v>
@@ -8966,7 +8966,7 @@
         <v>1</v>
       </c>
       <c r="Y61" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.4">
@@ -8977,10 +8977,10 @@
         <v>0.90416666666666667</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J62" t="s">
         <v>35</v>
@@ -9004,7 +9004,7 @@
         <v>1</v>
       </c>
       <c r="Y62" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.4">
@@ -9015,13 +9015,13 @@
         <v>0.90486111111111112</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J63" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K63" s="21"/>
       <c r="L63" s="21">
@@ -9046,7 +9046,7 @@
         <v>1</v>
       </c>
       <c r="Y63" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.4">
@@ -9057,13 +9057,13 @@
         <v>0.90694444444444444</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J64" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K64" s="21"/>
       <c r="L64" s="21"/>
@@ -9084,7 +9084,7 @@
         <v>1</v>
       </c>
       <c r="Y64" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.4">
@@ -9095,10 +9095,10 @@
         <v>0.90729166666666672</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J65" t="s">
         <v>35</v>
@@ -9122,7 +9122,7 @@
         <v>1</v>
       </c>
       <c r="Y65" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.4">
@@ -9133,13 +9133,13 @@
         <v>0.90763888888888888</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J66" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K66" s="21"/>
       <c r="L66" s="21"/>
@@ -9160,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="Y66" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.4">
@@ -9171,13 +9171,13 @@
         <v>0.90798611111111116</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J67" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K67" s="21"/>
       <c r="L67" s="21"/>
@@ -9198,7 +9198,7 @@
         <v>1</v>
       </c>
       <c r="Y67" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.4">
@@ -9209,10 +9209,10 @@
         <v>0.90833333333333333</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J68" t="s">
         <v>35</v>
@@ -9236,7 +9236,7 @@
         <v>1</v>
       </c>
       <c r="Y68" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.4">
@@ -9247,10 +9247,10 @@
         <v>0.90902777777777777</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J69" t="s">
         <v>35</v>
@@ -9274,7 +9274,7 @@
         <v>1</v>
       </c>
       <c r="Y69" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.4">
@@ -9285,10 +9285,10 @@
         <v>0.91041666666666665</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J70" t="s">
         <v>21</v>
@@ -9312,7 +9312,7 @@
         <v>1</v>
       </c>
       <c r="Y70" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.4">
@@ -9323,13 +9323,13 @@
         <v>0.91249999999999998</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J71" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K71" s="21"/>
       <c r="L71" s="21"/>
@@ -9350,7 +9350,7 @@
         <v>1</v>
       </c>
       <c r="Y71" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.4">
@@ -9361,13 +9361,13 @@
         <v>0.92291666666666672</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J72" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K72" s="21">
         <v>1600</v>
@@ -9396,7 +9396,7 @@
         <v>1</v>
       </c>
       <c r="Y72" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.4">
@@ -9407,10 +9407,10 @@
         <v>0.92569444444444449</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J73" t="s">
         <v>35</v>
@@ -9434,7 +9434,7 @@
         <v>1</v>
       </c>
       <c r="Y73" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.4">
@@ -9445,10 +9445,10 @@
         <v>0.92638888888888893</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J74" t="s">
         <v>35</v>
@@ -9472,7 +9472,7 @@
         <v>1</v>
       </c>
       <c r="Y74" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.4">
@@ -9483,10 +9483,10 @@
         <v>0.92708333333333337</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="J75" t="s">
         <v>20</v>
@@ -9522,7 +9522,7 @@
         <v>1</v>
       </c>
       <c r="Y75" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.4">
@@ -9533,10 +9533,10 @@
         <v>0.9291666666666667</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J76" t="s">
         <v>24</v>
@@ -9570,7 +9570,7 @@
         <v>1</v>
       </c>
       <c r="Y76" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" spans="1:25" s="15" customFormat="1" x14ac:dyDescent="0.4">
@@ -9580,7 +9580,7 @@
         <v>5</v>
       </c>
       <c r="L77" s="15" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M77" s="15" t="s">
         <v>6</v>
@@ -9606,10 +9606,10 @@
         <v>0.69861111111111107</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="J78" t="s">
         <v>35</v>
@@ -9652,7 +9652,7 @@
         <v>2</v>
       </c>
       <c r="Y78" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.4">
@@ -9663,10 +9663,10 @@
         <v>0.7</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J79" t="s">
         <v>24</v>
@@ -9709,7 +9709,7 @@
         <v>2</v>
       </c>
       <c r="Y79" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.4">
@@ -9720,10 +9720,10 @@
         <v>0.70277777777777772</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="J80" t="s">
         <v>21</v>
@@ -9766,7 +9766,7 @@
         <v>2</v>
       </c>
       <c r="Y80" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.4">
@@ -9777,13 +9777,13 @@
         <v>0.70972222222222225</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="J81" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K81" s="21">
         <f>IFERROR(solapados_tanda1y2!$P$39*INDEX('z_datos originales'!$C$77:$Q$108,MATCH(limpieza_datos!$C81,'z_datos originales'!$C$77:$C$108,0),MATCH(limpieza_datos!$K$77,'z_datos originales'!$C$77:$Q$77,0)),"")</f>
@@ -9823,7 +9823,7 @@
         <v>2</v>
       </c>
       <c r="Y81" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.4">
@@ -9834,10 +9834,10 @@
         <v>0.71875</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="J82" t="s">
         <v>21</v>
@@ -9880,7 +9880,7 @@
         <v>2</v>
       </c>
       <c r="Y82" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.4">
@@ -9891,10 +9891,10 @@
         <v>0.72152777777777777</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J83" t="s">
         <v>20</v>
@@ -9937,7 +9937,7 @@
         <v>2</v>
       </c>
       <c r="Y83" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.4">
@@ -9948,10 +9948,10 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="J84" t="s">
         <v>35</v>
@@ -9994,7 +9994,7 @@
         <v>2</v>
       </c>
       <c r="Y84" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.4">
@@ -10005,10 +10005,10 @@
         <v>0.73819444444444449</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="J85" t="s">
         <v>24</v>
@@ -10051,7 +10051,7 @@
         <v>2</v>
       </c>
       <c r="Y85" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.4">
@@ -10062,13 +10062,13 @@
         <v>0.74097222222222225</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J86" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K86" s="21">
         <f>IFERROR(solapados_tanda1y2!$P$39*INDEX('z_datos originales'!$C$77:$Q$108,MATCH(limpieza_datos!$C86,'z_datos originales'!$C$77:$C$108,0),MATCH(limpieza_datos!$K$77,'z_datos originales'!$C$77:$Q$77,0)),"")</f>
@@ -10108,7 +10108,7 @@
         <v>2</v>
       </c>
       <c r="Y86" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.4">
@@ -10119,13 +10119,13 @@
         <v>0.76111111111111107</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="J87" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K87" s="21">
         <f>IFERROR(solapados_tanda1y2!$P$39*INDEX('z_datos originales'!$C$77:$Q$108,MATCH(limpieza_datos!$C87,'z_datos originales'!$C$77:$C$108,0),MATCH(limpieza_datos!$K$77,'z_datos originales'!$C$77:$Q$77,0)),"")</f>
@@ -10165,7 +10165,7 @@
         <v>2</v>
       </c>
       <c r="Y87" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.4">
@@ -10176,10 +10176,10 @@
         <v>0.7631944444444444</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="J88" t="s">
         <v>24</v>
@@ -10222,7 +10222,7 @@
         <v>2</v>
       </c>
       <c r="Y88" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.4">
@@ -10233,13 +10233,13 @@
         <v>0.77986111111111112</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="J89" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K89" s="21">
         <f>IFERROR(solapados_tanda1y2!$P$39*INDEX('z_datos originales'!$C$77:$Q$108,MATCH(limpieza_datos!$C89,'z_datos originales'!$C$77:$C$108,0),MATCH(limpieza_datos!$K$77,'z_datos originales'!$C$77:$Q$77,0)),"")</f>
@@ -10279,7 +10279,7 @@
         <v>2</v>
       </c>
       <c r="Y89" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.4">
@@ -10290,10 +10290,10 @@
         <v>0.79027777777777775</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="J90" t="s">
         <v>20</v>
@@ -10336,7 +10336,7 @@
         <v>2</v>
       </c>
       <c r="Y90" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.4">
@@ -10347,13 +10347,13 @@
         <v>0.8</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="J91" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K91" s="21">
         <f>IFERROR(solapados_tanda1y2!$P$39*INDEX('z_datos originales'!$C$77:$Q$108,MATCH(limpieza_datos!$C91,'z_datos originales'!$C$77:$C$108,0),MATCH(limpieza_datos!$K$77,'z_datos originales'!$C$77:$Q$77,0)),"")</f>
@@ -10393,7 +10393,7 @@
         <v>2</v>
       </c>
       <c r="Y91" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.4">
@@ -10404,10 +10404,10 @@
         <v>0.80972222222222223</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="J92" t="s">
         <v>24</v>
@@ -10450,7 +10450,7 @@
         <v>2</v>
       </c>
       <c r="Y92" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.4">
@@ -10461,10 +10461,10 @@
         <v>0.81666666666666665</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="J93" t="s">
         <v>24</v>
@@ -10507,7 +10507,7 @@
         <v>2</v>
       </c>
       <c r="Y93" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.4">
@@ -10518,10 +10518,10 @@
         <v>0.82222222222222219</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="J94" t="s">
         <v>21</v>
@@ -10564,7 +10564,7 @@
         <v>2</v>
       </c>
       <c r="Y94" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.4">
@@ -10575,10 +10575,10 @@
         <v>0.82708333333333328</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="J95" t="s">
         <v>24</v>
@@ -10621,7 +10621,7 @@
         <v>2</v>
       </c>
       <c r="Y95" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.4">
@@ -10632,10 +10632,10 @@
         <v>0.83819444444444446</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="J96" t="s">
         <v>35</v>
@@ -10678,7 +10678,7 @@
         <v>2</v>
       </c>
       <c r="Y96" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.4">
@@ -10689,13 +10689,13 @@
         <v>0.84027777777777779</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="J97" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K97" s="21">
         <f>IFERROR(solapados_tanda1y2!$P$39*INDEX('z_datos originales'!$C$77:$Q$108,MATCH(limpieza_datos!$C97,'z_datos originales'!$C$77:$C$108,0),MATCH(limpieza_datos!$K$77,'z_datos originales'!$C$77:$Q$77,0)),"")</f>
@@ -10735,7 +10735,7 @@
         <v>2</v>
       </c>
       <c r="Y97" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.4">
@@ -10746,13 +10746,13 @@
         <v>0.85069444444444442</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="J98" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K98" s="21">
         <f>IFERROR(solapados_tanda1y2!$P$39*INDEX('z_datos originales'!$C$77:$Q$108,MATCH(limpieza_datos!$C98,'z_datos originales'!$C$77:$C$108,0),MATCH(limpieza_datos!$K$77,'z_datos originales'!$C$77:$Q$77,0)),"")</f>
@@ -10792,7 +10792,7 @@
         <v>2</v>
       </c>
       <c r="Y98" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.4">
@@ -10803,10 +10803,10 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="J99" t="s">
         <v>35</v>
@@ -10849,7 +10849,7 @@
         <v>2</v>
       </c>
       <c r="Y99" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="100" spans="1:25" s="15" customFormat="1" x14ac:dyDescent="0.4">
@@ -10919,67 +10919,65 @@
     <hyperlink ref="D10" r:id="rId8" xr:uid="{22B09F3D-D035-41D1-840F-6F57ADA7A1B3}"/>
     <hyperlink ref="D11" r:id="rId9" xr:uid="{BBA507A8-E763-4809-9E49-3723D71F5EC7}"/>
     <hyperlink ref="D12" r:id="rId10" xr:uid="{E8A1EC9E-B5B4-4FE3-9D99-DB6BADF641C5}"/>
-    <hyperlink ref="D13" r:id="rId11" xr:uid="{EEC2A981-0238-479F-A937-5E1FBD2D9C1E}"/>
-    <hyperlink ref="D14" r:id="rId12" xr:uid="{F453FF3C-B34E-41FD-A65F-33F58391904A}"/>
-    <hyperlink ref="D15" r:id="rId13" xr:uid="{420782D8-FE47-4264-8D56-97F5895E2ED5}"/>
-    <hyperlink ref="D16" r:id="rId14" xr:uid="{9B3F01EC-02F2-4876-8D64-3BBC145AC523}"/>
-    <hyperlink ref="D17" r:id="rId15" xr:uid="{B02084DC-1454-46DC-959E-5FEF50FEB772}"/>
-    <hyperlink ref="D18" r:id="rId16" xr:uid="{8182AD81-B104-4CB8-8272-63287EB9C2F4}"/>
-    <hyperlink ref="D19" r:id="rId17" xr:uid="{91840029-A2D8-4EFB-A58D-E6165DE3F501}"/>
-    <hyperlink ref="D20" r:id="rId18" xr:uid="{C1BEECED-4448-43A4-A10F-88DBAC99BF15}"/>
-    <hyperlink ref="D21" r:id="rId19" xr:uid="{DBDA89C5-DC3A-4374-8917-72BBA9ECB1E3}"/>
-    <hyperlink ref="D22" r:id="rId20" xr:uid="{1D364EF1-FA01-4ADA-B445-2DD1FDFD9E63}"/>
-    <hyperlink ref="D23" r:id="rId21" xr:uid="{65A301B4-C3CE-4E95-BD61-E159FD1E2090}"/>
-    <hyperlink ref="D24" r:id="rId22" xr:uid="{2B251CE2-D744-48B7-BE95-99866FA30C10}"/>
-    <hyperlink ref="D25" r:id="rId23" xr:uid="{042AAF7A-4190-4A14-AA61-D0B75DEDF6BB}"/>
-    <hyperlink ref="D26" r:id="rId24" xr:uid="{6B515C46-7D3F-4851-B3F2-E6F222A21410}"/>
-    <hyperlink ref="D27" r:id="rId25" xr:uid="{2AB2CBC6-8BF2-4E9E-962D-CFB7A8A25E8F}"/>
-    <hyperlink ref="D28" r:id="rId26" xr:uid="{7C583A4D-81CE-49A2-916C-235D3DCAB232}"/>
-    <hyperlink ref="D29" r:id="rId27" xr:uid="{986BE7FB-19E4-447A-B394-C9796DACF9B6}"/>
-    <hyperlink ref="D30" r:id="rId28" xr:uid="{F78689A6-6C5C-4431-9FB9-39B90E431B3F}"/>
-    <hyperlink ref="D31" r:id="rId29" xr:uid="{A0271A6D-5583-4AF6-B487-D635FC3E1F97}"/>
-    <hyperlink ref="D32" r:id="rId30" xr:uid="{41346792-5663-4496-8547-DD8EC11EB215}"/>
-    <hyperlink ref="D34" r:id="rId31" xr:uid="{5D205A99-6EA5-4CF8-9E93-0C4CF553647E}"/>
-    <hyperlink ref="D35" r:id="rId32" xr:uid="{C8524AE0-F64A-4C9B-B82C-3152E64E9229}"/>
-    <hyperlink ref="D37" r:id="rId33" xr:uid="{7866AA3F-31AF-4BA5-AB84-41E18A8D114E}"/>
-    <hyperlink ref="D41" r:id="rId34" xr:uid="{88D7D4E4-50C4-459F-9B72-D938C4767C26}"/>
-    <hyperlink ref="D42" r:id="rId35" xr:uid="{C14E2003-A135-4FA6-B891-F05F48DFFF8A}"/>
-    <hyperlink ref="D43" r:id="rId36" xr:uid="{9D396F29-5908-467F-9E52-D4F86AFD21E3}"/>
-    <hyperlink ref="D46" r:id="rId37" xr:uid="{B525F21D-40F8-4F31-B161-6DD018CCD835}"/>
-    <hyperlink ref="D48" r:id="rId38" display="https://www.google.com/maps?q=-34.5927619934082,-58.383609771728516&amp;z=17&amp;hl=es" xr:uid="{64267FC1-FADB-432A-8F4B-7304A6C465D7}"/>
-    <hyperlink ref="D49" r:id="rId39" xr:uid="{DBB53584-B217-4C2F-ABE9-A5BFCC0BFC76}"/>
-    <hyperlink ref="D50" r:id="rId40" xr:uid="{F50ADD64-0003-4284-87EA-ABB204AE1946}"/>
-    <hyperlink ref="D51" r:id="rId41" xr:uid="{42E1DB89-0ED2-4068-9D65-27503BF72FCC}"/>
-    <hyperlink ref="D52" r:id="rId42" xr:uid="{29C7FC7C-2257-474A-9510-324A47A6B130}"/>
-    <hyperlink ref="D53" r:id="rId43" xr:uid="{E9AE8AB7-0F01-4901-ACDD-A76C3912AD5A}"/>
-    <hyperlink ref="D54" r:id="rId44" xr:uid="{AF6EA4C3-5E6C-4C1D-A071-8F6D7A933FCE}"/>
-    <hyperlink ref="D56" r:id="rId45" xr:uid="{25D6C098-564B-44AA-B2E3-26C00B7DA62D}"/>
-    <hyperlink ref="D57" r:id="rId46" xr:uid="{3E0AF767-C186-4BB3-9A28-073A3B800775}"/>
-    <hyperlink ref="D58" r:id="rId47" xr:uid="{47909278-84ED-4613-9BE5-C090247B7063}"/>
-    <hyperlink ref="D59" r:id="rId48" xr:uid="{5D8D4885-C525-46A6-8E7E-CA11D107138D}"/>
-    <hyperlink ref="D60" r:id="rId49" xr:uid="{5A6560D7-5958-42EE-AEC4-ED4DC6ADC562}"/>
-    <hyperlink ref="D61" r:id="rId50" xr:uid="{D3ED8DA2-C243-433F-B9B6-D7F4275F1E33}"/>
-    <hyperlink ref="D62" r:id="rId51" xr:uid="{ADAB1EAC-65A2-4AE2-A011-A143950D04FF}"/>
-    <hyperlink ref="D63" r:id="rId52" xr:uid="{52F55D7F-C2F0-432D-BF5D-D7F549EE1CD0}"/>
-    <hyperlink ref="D64" r:id="rId53" xr:uid="{96FAAE5D-6BBE-4AAF-BA5C-8476067A3F93}"/>
-    <hyperlink ref="D65" r:id="rId54" xr:uid="{BCB1AD3D-0D75-4980-9BE0-4A0A0341E34C}"/>
-    <hyperlink ref="D66" r:id="rId55" xr:uid="{5551AF57-0759-4E03-BA87-6FF5D3690D0D}"/>
-    <hyperlink ref="D67" r:id="rId56" xr:uid="{3FA3692B-56EB-4CDC-AF70-CD1AF06E06A3}"/>
-    <hyperlink ref="D68" r:id="rId57" xr:uid="{18650105-8E57-4DAA-8AF4-31637D293D9E}"/>
-    <hyperlink ref="D69" r:id="rId58" xr:uid="{ACBF9558-B4AC-484A-92EC-7F37E0BB67BD}"/>
-    <hyperlink ref="D70" r:id="rId59" xr:uid="{F11D9F59-FF18-4CB3-907D-5AE50C96FDB2}"/>
-    <hyperlink ref="D71" r:id="rId60" xr:uid="{623C8ADB-610E-4CC7-AC21-08E01F32D5DA}"/>
-    <hyperlink ref="D72" r:id="rId61" xr:uid="{562DCECD-F65C-46C7-9C3E-6347ED3DAD54}"/>
-    <hyperlink ref="D73" r:id="rId62" xr:uid="{162B6B80-7EA1-461E-8AE2-AC2D9B72A538}"/>
-    <hyperlink ref="D74" r:id="rId63" xr:uid="{96DA9B5C-70F0-4601-8498-12A5457974EB}"/>
-    <hyperlink ref="D76" r:id="rId64" xr:uid="{8BC60AB8-DAE9-48F1-975D-25D67D3F6F09}"/>
-    <hyperlink ref="D5" r:id="rId65" xr:uid="{B9BACED9-EFBF-4FE6-BD19-5722EA743AFB}"/>
-    <hyperlink ref="D38" r:id="rId66" xr:uid="{2E6ADDF1-24D1-45A1-BD96-446368A45399}"/>
-    <hyperlink ref="D39" r:id="rId67" xr:uid="{C4123B4B-D9DE-4904-AD82-D1F1CCC6D130}"/>
-    <hyperlink ref="D40" r:id="rId68" xr:uid="{EE523BE3-CCDC-47AE-AD66-151B8BB557ED}"/>
+    <hyperlink ref="D14" r:id="rId11" xr:uid="{F453FF3C-B34E-41FD-A65F-33F58391904A}"/>
+    <hyperlink ref="D15" r:id="rId12" xr:uid="{420782D8-FE47-4264-8D56-97F5895E2ED5}"/>
+    <hyperlink ref="D16" r:id="rId13" xr:uid="{9B3F01EC-02F2-4876-8D64-3BBC145AC523}"/>
+    <hyperlink ref="D17" r:id="rId14" xr:uid="{B02084DC-1454-46DC-959E-5FEF50FEB772}"/>
+    <hyperlink ref="D18" r:id="rId15" xr:uid="{8182AD81-B104-4CB8-8272-63287EB9C2F4}"/>
+    <hyperlink ref="D19" r:id="rId16" xr:uid="{91840029-A2D8-4EFB-A58D-E6165DE3F501}"/>
+    <hyperlink ref="D20" r:id="rId17" xr:uid="{C1BEECED-4448-43A4-A10F-88DBAC99BF15}"/>
+    <hyperlink ref="D21" r:id="rId18" xr:uid="{DBDA89C5-DC3A-4374-8917-72BBA9ECB1E3}"/>
+    <hyperlink ref="D22" r:id="rId19" xr:uid="{1D364EF1-FA01-4ADA-B445-2DD1FDFD9E63}"/>
+    <hyperlink ref="D23" r:id="rId20" xr:uid="{65A301B4-C3CE-4E95-BD61-E159FD1E2090}"/>
+    <hyperlink ref="D24" r:id="rId21" xr:uid="{2B251CE2-D744-48B7-BE95-99866FA30C10}"/>
+    <hyperlink ref="D25" r:id="rId22" xr:uid="{042AAF7A-4190-4A14-AA61-D0B75DEDF6BB}"/>
+    <hyperlink ref="D26" r:id="rId23" xr:uid="{6B515C46-7D3F-4851-B3F2-E6F222A21410}"/>
+    <hyperlink ref="D27" r:id="rId24" xr:uid="{2AB2CBC6-8BF2-4E9E-962D-CFB7A8A25E8F}"/>
+    <hyperlink ref="D28" r:id="rId25" xr:uid="{7C583A4D-81CE-49A2-916C-235D3DCAB232}"/>
+    <hyperlink ref="D29" r:id="rId26" xr:uid="{986BE7FB-19E4-447A-B394-C9796DACF9B6}"/>
+    <hyperlink ref="D30" r:id="rId27" xr:uid="{F78689A6-6C5C-4431-9FB9-39B90E431B3F}"/>
+    <hyperlink ref="D31" r:id="rId28" xr:uid="{A0271A6D-5583-4AF6-B487-D635FC3E1F97}"/>
+    <hyperlink ref="D32" r:id="rId29" xr:uid="{41346792-5663-4496-8547-DD8EC11EB215}"/>
+    <hyperlink ref="D34" r:id="rId30" xr:uid="{5D205A99-6EA5-4CF8-9E93-0C4CF553647E}"/>
+    <hyperlink ref="D37" r:id="rId31" xr:uid="{7866AA3F-31AF-4BA5-AB84-41E18A8D114E}"/>
+    <hyperlink ref="D41" r:id="rId32" xr:uid="{88D7D4E4-50C4-459F-9B72-D938C4767C26}"/>
+    <hyperlink ref="D42" r:id="rId33" xr:uid="{C14E2003-A135-4FA6-B891-F05F48DFFF8A}"/>
+    <hyperlink ref="D43" r:id="rId34" xr:uid="{9D396F29-5908-467F-9E52-D4F86AFD21E3}"/>
+    <hyperlink ref="D46" r:id="rId35" xr:uid="{B525F21D-40F8-4F31-B161-6DD018CCD835}"/>
+    <hyperlink ref="D48" r:id="rId36" display="https://www.google.com/maps?q=-34.5927619934082,-58.383609771728516&amp;z=17&amp;hl=es" xr:uid="{64267FC1-FADB-432A-8F4B-7304A6C465D7}"/>
+    <hyperlink ref="D49" r:id="rId37" xr:uid="{DBB53584-B217-4C2F-ABE9-A5BFCC0BFC76}"/>
+    <hyperlink ref="D50" r:id="rId38" xr:uid="{F50ADD64-0003-4284-87EA-ABB204AE1946}"/>
+    <hyperlink ref="D51" r:id="rId39" display="https://www.google.com/maps?q=-34.592735290527344,-58.37911605834961&amp;z=17&amp;hl=es" xr:uid="{42E1DB89-0ED2-4068-9D65-27503BF72FCC}"/>
+    <hyperlink ref="D52" r:id="rId40" xr:uid="{29C7FC7C-2257-474A-9510-324A47A6B130}"/>
+    <hyperlink ref="D53" r:id="rId41" xr:uid="{E9AE8AB7-0F01-4901-ACDD-A76C3912AD5A}"/>
+    <hyperlink ref="D54" r:id="rId42" xr:uid="{AF6EA4C3-5E6C-4C1D-A071-8F6D7A933FCE}"/>
+    <hyperlink ref="D56" r:id="rId43" xr:uid="{25D6C098-564B-44AA-B2E3-26C00B7DA62D}"/>
+    <hyperlink ref="D57" r:id="rId44" xr:uid="{3E0AF767-C186-4BB3-9A28-073A3B800775}"/>
+    <hyperlink ref="D58" r:id="rId45" xr:uid="{47909278-84ED-4613-9BE5-C090247B7063}"/>
+    <hyperlink ref="D59" r:id="rId46" xr:uid="{5D8D4885-C525-46A6-8E7E-CA11D107138D}"/>
+    <hyperlink ref="D60" r:id="rId47" xr:uid="{5A6560D7-5958-42EE-AEC4-ED4DC6ADC562}"/>
+    <hyperlink ref="D61" r:id="rId48" xr:uid="{D3ED8DA2-C243-433F-B9B6-D7F4275F1E33}"/>
+    <hyperlink ref="D62" r:id="rId49" xr:uid="{ADAB1EAC-65A2-4AE2-A011-A143950D04FF}"/>
+    <hyperlink ref="D63" r:id="rId50" xr:uid="{52F55D7F-C2F0-432D-BF5D-D7F549EE1CD0}"/>
+    <hyperlink ref="D64" r:id="rId51" xr:uid="{96FAAE5D-6BBE-4AAF-BA5C-8476067A3F93}"/>
+    <hyperlink ref="D65" r:id="rId52" xr:uid="{BCB1AD3D-0D75-4980-9BE0-4A0A0341E34C}"/>
+    <hyperlink ref="D66" r:id="rId53" xr:uid="{5551AF57-0759-4E03-BA87-6FF5D3690D0D}"/>
+    <hyperlink ref="D67" r:id="rId54" xr:uid="{3FA3692B-56EB-4CDC-AF70-CD1AF06E06A3}"/>
+    <hyperlink ref="D68" r:id="rId55" xr:uid="{18650105-8E57-4DAA-8AF4-31637D293D9E}"/>
+    <hyperlink ref="D69" r:id="rId56" xr:uid="{ACBF9558-B4AC-484A-92EC-7F37E0BB67BD}"/>
+    <hyperlink ref="D70" r:id="rId57" xr:uid="{F11D9F59-FF18-4CB3-907D-5AE50C96FDB2}"/>
+    <hyperlink ref="D71" r:id="rId58" xr:uid="{623C8ADB-610E-4CC7-AC21-08E01F32D5DA}"/>
+    <hyperlink ref="D72" r:id="rId59" xr:uid="{562DCECD-F65C-46C7-9C3E-6347ED3DAD54}"/>
+    <hyperlink ref="D73" r:id="rId60" xr:uid="{162B6B80-7EA1-461E-8AE2-AC2D9B72A538}"/>
+    <hyperlink ref="D74" r:id="rId61" xr:uid="{96DA9B5C-70F0-4601-8498-12A5457974EB}"/>
+    <hyperlink ref="D76" r:id="rId62" xr:uid="{8BC60AB8-DAE9-48F1-975D-25D67D3F6F09}"/>
+    <hyperlink ref="D5" r:id="rId63" xr:uid="{B9BACED9-EFBF-4FE6-BD19-5722EA743AFB}"/>
+    <hyperlink ref="D38" r:id="rId64" xr:uid="{2E6ADDF1-24D1-45A1-BD96-446368A45399}"/>
+    <hyperlink ref="D39" r:id="rId65" xr:uid="{C4123B4B-D9DE-4904-AD82-D1F1CCC6D130}"/>
+    <hyperlink ref="D40" r:id="rId66" xr:uid="{EE523BE3-CCDC-47AE-AD66-151B8BB557ED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId69"/>
+  <pageSetup orientation="portrait" r:id="rId67"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -11020,19 +11018,19 @@
   <sheetData>
     <row r="1" spans="1:26" s="4" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -11053,7 +11051,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
@@ -11083,16 +11081,16 @@
         <v>14</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>16</v>
@@ -11106,7 +11104,7 @@
         <v>0.95277777777777772</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>17</v>
@@ -11143,7 +11141,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.4">
@@ -11154,7 +11152,7 @@
         <v>0.95486111111111116</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>19</v>
@@ -11175,7 +11173,7 @@
         <v>1</v>
       </c>
       <c r="Y3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.4">
@@ -11186,13 +11184,13 @@
         <v>0.95625000000000004</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>22</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N4">
         <v>1800</v>
@@ -11213,7 +11211,7 @@
         <v>1</v>
       </c>
       <c r="Y4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.4">
@@ -11224,7 +11222,7 @@
         <v>0.95833333333333337</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>23</v>
@@ -11257,7 +11255,7 @@
         <v>1</v>
       </c>
       <c r="Y5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.4">
@@ -11268,7 +11266,7 @@
         <v>0.9604166666666667</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>27</v>
@@ -11289,7 +11287,7 @@
         <v>1</v>
       </c>
       <c r="Y6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.4">
@@ -11300,7 +11298,7 @@
         <v>0.96111111111111114</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -11337,7 +11335,7 @@
         <v>1</v>
       </c>
       <c r="Y7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.4">
@@ -11348,7 +11346,7 @@
         <v>0.96597222222222223</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>30</v>
@@ -11369,7 +11367,7 @@
         <v>1</v>
       </c>
       <c r="Y8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.4">
@@ -11380,13 +11378,13 @@
         <v>0.96666666666666667</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K9">
         <v>2400</v>
@@ -11413,7 +11411,7 @@
         <v>1</v>
       </c>
       <c r="Y9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.4">
@@ -11424,7 +11422,7 @@
         <v>0.96805555555555556</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>32</v>
@@ -11461,7 +11459,7 @@
         <v>1</v>
       </c>
       <c r="Y10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.4">
@@ -11472,7 +11470,7 @@
         <v>0.97430555555555554</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>33</v>
@@ -11505,7 +11503,7 @@
         <v>1</v>
       </c>
       <c r="Y11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.4">
@@ -11516,7 +11514,7 @@
         <v>0.97638888888888886</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>34</v>
@@ -11537,7 +11535,7 @@
         <v>1</v>
       </c>
       <c r="Y12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.4">
@@ -11548,13 +11546,13 @@
         <v>0.97777777777777775</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>36</v>
+        <v>391</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L13">
         <v>1800</v>
@@ -11575,7 +11573,7 @@
         <v>1</v>
       </c>
       <c r="Y13" t="s">
-        <v>128</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.4">
@@ -11586,13 +11584,13 @@
         <v>0.97847222222222219</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" s="20" t="s">
         <v>37</v>
-      </c>
-      <c r="J14" s="20" t="s">
-        <v>38</v>
       </c>
       <c r="K14">
         <v>1740</v>
@@ -11621,7 +11619,7 @@
         <v>1</v>
       </c>
       <c r="Y14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.4">
@@ -11632,13 +11630,13 @@
         <v>0.98124999999999996</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N15">
         <v>1800</v>
@@ -11656,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="Y15" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.4">
@@ -11667,10 +11665,10 @@
         <v>0.98263888888888884</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J16" s="20" t="s">
         <v>20</v>
@@ -11704,7 +11702,7 @@
         <v>1</v>
       </c>
       <c r="Y16" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.4">
@@ -11715,13 +11713,13 @@
         <v>0.98611111111111116</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K17">
         <v>1900</v>
@@ -11748,7 +11746,7 @@
         <v>1</v>
       </c>
       <c r="Y17" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.4">
@@ -11759,13 +11757,13 @@
         <v>0.99027777777777781</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N18">
         <v>2200</v>
@@ -11786,7 +11784,7 @@
         <v>1</v>
       </c>
       <c r="Y18" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.4">
@@ -11797,10 +11795,10 @@
         <v>0.99097222222222225</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J19" s="20" t="s">
         <v>20</v>
@@ -11834,7 +11832,7 @@
         <v>1</v>
       </c>
       <c r="Y19" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.4">
@@ -11845,10 +11843,10 @@
         <v>0.99652777777777779</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J20" s="20" t="s">
         <v>24</v>
@@ -11884,7 +11882,7 @@
         <v>1</v>
       </c>
       <c r="Y20" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.4">
@@ -11895,10 +11893,10 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J21" s="20" t="s">
         <v>35</v>
@@ -11916,7 +11914,7 @@
         <v>1</v>
       </c>
       <c r="Y21" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.4">
@@ -11927,13 +11925,13 @@
         <v>0</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J22" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K22">
         <v>1390</v>
@@ -11962,7 +11960,7 @@
         <v>1</v>
       </c>
       <c r="Y22" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.4">
@@ -11973,13 +11971,13 @@
         <v>2.7777777777777779E-3</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" s="20" t="s">
         <v>47</v>
-      </c>
-      <c r="J23" s="20" t="s">
-        <v>48</v>
       </c>
       <c r="M23">
         <v>1500</v>
@@ -11997,7 +11995,7 @@
         <v>1</v>
       </c>
       <c r="Y23" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.4">
@@ -12008,10 +12006,10 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J24" s="20" t="s">
         <v>35</v>
@@ -12029,7 +12027,7 @@
         <v>1</v>
       </c>
       <c r="Y24" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.4">
@@ -12040,13 +12038,13 @@
         <v>4.8611111111111112E-3</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L25">
         <v>2500</v>
@@ -12064,7 +12062,7 @@
         <v>1</v>
       </c>
       <c r="Y25" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.4">
@@ -12075,13 +12073,13 @@
         <v>5.5555555555555558E-3</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M26">
         <v>1100</v>
@@ -12108,7 +12106,7 @@
         <v>1</v>
       </c>
       <c r="Y26" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.4">
@@ -12119,10 +12117,10 @@
         <v>9.0277777777777769E-3</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J27" s="20" t="s">
         <v>24</v>
@@ -12155,7 +12153,7 @@
         <v>1</v>
       </c>
       <c r="Y27" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.4">
@@ -12166,10 +12164,10 @@
         <v>0.73541666666666672</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J28" s="20" t="s">
         <v>24</v>
@@ -12202,7 +12200,7 @@
         <v>1</v>
       </c>
       <c r="Y28" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.4">
@@ -12213,10 +12211,10 @@
         <v>0.74583333333333335</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J29" s="20" t="s">
         <v>24</v>
@@ -12246,7 +12244,7 @@
         <v>1</v>
       </c>
       <c r="Y29" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.4">
@@ -12257,10 +12255,10 @@
         <v>0.75069444444444444</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J30" s="20" t="s">
         <v>35</v>
@@ -12278,7 +12276,7 @@
         <v>1</v>
       </c>
       <c r="Y30" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.4">
@@ -12289,10 +12287,10 @@
         <v>0.75138888888888888</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J31" s="20" t="s">
         <v>20</v>
@@ -12328,7 +12326,7 @@
         <v>1</v>
       </c>
       <c r="Y31" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.4">
@@ -12339,13 +12337,13 @@
         <v>0.75972222222222219</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D32" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J32" s="20" t="s">
         <v>58</v>
-      </c>
-      <c r="J32" s="20" t="s">
-        <v>59</v>
       </c>
       <c r="K32">
         <v>2100</v>
@@ -12360,7 +12358,7 @@
         <v>5200</v>
       </c>
       <c r="U32" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="V32" t="s">
         <v>26</v>
@@ -12372,7 +12370,7 @@
         <v>1</v>
       </c>
       <c r="Y32" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.4">
@@ -12383,13 +12381,13 @@
         <v>0.77013888888888893</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K33">
         <v>1485</v>
@@ -12419,7 +12417,7 @@
         <v>1</v>
       </c>
       <c r="Y33" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.4">
@@ -12430,13 +12428,13 @@
         <v>0.77361111111111114</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D34" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J34" s="20" t="s">
         <v>60</v>
-      </c>
-      <c r="J34" s="20" t="s">
-        <v>61</v>
       </c>
       <c r="K34">
         <v>1290</v>
@@ -12469,7 +12467,7 @@
         <v>1</v>
       </c>
       <c r="Y34" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.4">
@@ -12480,13 +12478,13 @@
         <v>0.78125</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>62</v>
+        <v>389</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L35">
         <v>1000</v>
@@ -12507,7 +12505,7 @@
         <v>1</v>
       </c>
       <c r="Y35" t="s">
-        <v>148</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.4">
@@ -12518,13 +12516,13 @@
         <v>0.78680555555555554</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="J36" s="20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K36">
         <v>1950</v>
@@ -12557,7 +12555,7 @@
         <v>1</v>
       </c>
       <c r="Y36" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.4">
@@ -12568,10 +12566,10 @@
         <v>0.79236111111111107</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J37" s="20" t="s">
         <v>20</v>
@@ -12604,7 +12602,7 @@
         <v>1</v>
       </c>
       <c r="Y37" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.4">
@@ -12615,10 +12613,10 @@
         <v>0.79513888888888884</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J38" s="20" t="s">
         <v>35</v>
@@ -12636,7 +12634,7 @@
         <v>1</v>
       </c>
       <c r="Y38" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.4">
@@ -12647,10 +12645,10 @@
         <v>0.79583333333333328</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J39" s="20" t="s">
         <v>21</v>
@@ -12668,7 +12666,7 @@
         <v>1</v>
       </c>
       <c r="Y39" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.4">
@@ -12679,13 +12677,13 @@
         <v>0.79722222222222228</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J40" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L40">
         <v>1400</v>
@@ -12706,7 +12704,7 @@
         <v>1</v>
       </c>
       <c r="Y40" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.4">
@@ -12717,10 +12715,10 @@
         <v>0.80625000000000002</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J41" s="20" t="s">
         <v>35</v>
@@ -12738,7 +12736,7 @@
         <v>1</v>
       </c>
       <c r="Y41" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.4">
@@ -12749,13 +12747,13 @@
         <v>0.81388888888888888</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J42" s="20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K42">
         <v>1290</v>
@@ -12788,7 +12786,7 @@
         <v>1</v>
       </c>
       <c r="Y42" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.4">
@@ -12799,10 +12797,10 @@
         <v>0.82152777777777775</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J43" s="20" t="s">
         <v>35</v>
@@ -12820,7 +12818,7 @@
         <v>1</v>
       </c>
       <c r="Y43" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.4">
@@ -12831,10 +12829,10 @@
         <v>0.82222222222222219</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="J44" s="20" t="s">
         <v>24</v>
@@ -12867,7 +12865,7 @@
         <v>1</v>
       </c>
       <c r="Y44" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.4">
@@ -12878,10 +12876,10 @@
         <v>0.82638888888888884</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="J45" s="20" t="s">
         <v>35</v>
@@ -12899,7 +12897,7 @@
         <v>1</v>
       </c>
       <c r="Y45" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.4">
@@ -12910,10 +12908,10 @@
         <v>0.82777777777777772</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J46" s="20" t="s">
         <v>35</v>
@@ -12931,7 +12929,7 @@
         <v>1</v>
       </c>
       <c r="Y46" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.4">
@@ -12942,10 +12940,10 @@
         <v>0.84652777777777777</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="J47" s="20" t="s">
         <v>35</v>
@@ -12963,7 +12961,7 @@
         <v>1</v>
       </c>
       <c r="Y47" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.4">
@@ -12974,10 +12972,10 @@
         <v>0.84930555555555554</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="J48" s="20" t="s">
         <v>35</v>
@@ -12995,7 +12993,7 @@
         <v>1</v>
       </c>
       <c r="Y48" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.4">
@@ -13006,13 +13004,13 @@
         <v>0.85277777777777775</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J49" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L49">
         <v>1200</v>
@@ -13036,7 +13034,7 @@
         <v>1</v>
       </c>
       <c r="Y49" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.4">
@@ -13047,10 +13045,10 @@
         <v>0.85486111111111107</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J50" s="20" t="s">
         <v>24</v>
@@ -13080,7 +13078,7 @@
         <v>1</v>
       </c>
       <c r="Y50" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.4">
@@ -13091,10 +13089,10 @@
         <v>0.85763888888888884</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>77</v>
+        <v>387</v>
       </c>
       <c r="J51" s="20" t="s">
         <v>35</v>
@@ -13112,7 +13110,7 @@
         <v>1</v>
       </c>
       <c r="Y51" t="s">
-        <v>160</v>
+        <v>386</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.4">
@@ -13123,10 +13121,10 @@
         <v>0.86250000000000004</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J52" s="20" t="s">
         <v>20</v>
@@ -13162,7 +13160,7 @@
         <v>1</v>
       </c>
       <c r="Y52" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.4">
@@ -13173,10 +13171,10 @@
         <v>0.86284722222222221</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J53" s="20" t="s">
         <v>21</v>
@@ -13194,7 +13192,7 @@
         <v>1</v>
       </c>
       <c r="Y53" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.4">
@@ -13205,10 +13203,10 @@
         <v>0.86597222222222225</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J54" s="20" t="s">
         <v>35</v>
@@ -13226,7 +13224,7 @@
         <v>1</v>
       </c>
       <c r="Y54" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.4">
@@ -13237,10 +13235,10 @@
         <v>0.87013888888888891</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="J55" s="20" t="s">
         <v>24</v>
@@ -13270,7 +13268,7 @@
         <v>1</v>
       </c>
       <c r="Y55" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.4">
@@ -13281,10 +13279,10 @@
         <v>0.87569444444444444</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J56" s="20" t="s">
         <v>24</v>
@@ -13311,7 +13309,7 @@
         <v>1</v>
       </c>
       <c r="Y56" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.4">
@@ -13322,13 +13320,13 @@
         <v>0.88124999999999998</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J57" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K57">
         <v>1430</v>
@@ -13361,7 +13359,7 @@
         <v>1</v>
       </c>
       <c r="Y57" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.4">
@@ -13372,10 +13370,10 @@
         <v>0.89027777777777772</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J58" s="20" t="s">
         <v>35</v>
@@ -13393,7 +13391,7 @@
         <v>1</v>
       </c>
       <c r="Y58" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.4">
@@ -13404,10 +13402,10 @@
         <v>0.89097222222222228</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J59" s="20" t="s">
         <v>24</v>
@@ -13437,7 +13435,7 @@
         <v>1</v>
       </c>
       <c r="Y59" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.4">
@@ -13448,10 +13446,10 @@
         <v>0.89513888888888893</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="J60" s="20" t="s">
         <v>20</v>
@@ -13487,7 +13485,7 @@
         <v>1</v>
       </c>
       <c r="Y60" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.4">
@@ -13498,13 +13496,13 @@
         <v>0.8979166666666667</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J61" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K61">
         <v>1290</v>
@@ -13537,7 +13535,7 @@
         <v>1</v>
       </c>
       <c r="Y61" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.4">
@@ -13548,10 +13546,10 @@
         <v>0.90416666666666667</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J62" s="20" t="s">
         <v>35</v>
@@ -13569,7 +13567,7 @@
         <v>1</v>
       </c>
       <c r="Y62" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.4">
@@ -13580,13 +13578,13 @@
         <v>0.90486111111111112</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J63" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L63">
         <v>1400</v>
@@ -13607,7 +13605,7 @@
         <v>1</v>
       </c>
       <c r="Y63" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.4">
@@ -13618,13 +13616,13 @@
         <v>0.90694444444444444</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J64" s="20" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q64">
         <v>8500</v>
@@ -13639,7 +13637,7 @@
         <v>1</v>
       </c>
       <c r="Y64" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.4">
@@ -13650,10 +13648,10 @@
         <v>0.90729166666666672</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J65" s="20" t="s">
         <v>35</v>
@@ -13671,7 +13669,7 @@
         <v>1</v>
       </c>
       <c r="Y65" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.4">
@@ -13682,13 +13680,13 @@
         <v>0.90763888888888888</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J66" s="20" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q66">
         <v>17000</v>
@@ -13703,7 +13701,7 @@
         <v>1</v>
       </c>
       <c r="Y66" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.4">
@@ -13714,13 +13712,13 @@
         <v>0.90798611111111116</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J67" s="20" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q67">
         <v>21000</v>
@@ -13735,7 +13733,7 @@
         <v>1</v>
       </c>
       <c r="Y67" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.4">
@@ -13746,10 +13744,10 @@
         <v>0.90833333333333333</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J68" s="20" t="s">
         <v>35</v>
@@ -13767,7 +13765,7 @@
         <v>1</v>
       </c>
       <c r="Y68" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.4">
@@ -13778,10 +13776,10 @@
         <v>0.90902777777777777</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J69" s="20" t="s">
         <v>35</v>
@@ -13799,7 +13797,7 @@
         <v>1</v>
       </c>
       <c r="Y69" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.4">
@@ -13810,10 +13808,10 @@
         <v>0.91041666666666665</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J70" s="20" t="s">
         <v>21</v>
@@ -13831,7 +13829,7 @@
         <v>1</v>
       </c>
       <c r="Y70" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.4">
@@ -13842,13 +13840,13 @@
         <v>0.91249999999999998</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J71" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P71">
         <v>725</v>
@@ -13863,7 +13861,7 @@
         <v>1</v>
       </c>
       <c r="Y71" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.4">
@@ -13874,13 +13872,13 @@
         <v>0.92291666666666672</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J72" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K72">
         <v>1600</v>
@@ -13907,7 +13905,7 @@
         <v>1</v>
       </c>
       <c r="Y72" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.4">
@@ -13918,10 +13916,10 @@
         <v>0.92569444444444449</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J73" s="20" t="s">
         <v>35</v>
@@ -13939,7 +13937,7 @@
         <v>1</v>
       </c>
       <c r="Y73" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.4">
@@ -13950,10 +13948,10 @@
         <v>0.92638888888888893</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J74" s="20" t="s">
         <v>35</v>
@@ -13971,7 +13969,7 @@
         <v>1</v>
       </c>
       <c r="Y74" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.4">
@@ -13982,10 +13980,10 @@
         <v>0.92708333333333337</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="J75" s="20" t="s">
         <v>20</v>
@@ -14021,7 +14019,7 @@
         <v>1</v>
       </c>
       <c r="Y75" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.4">
@@ -14032,10 +14030,10 @@
         <v>0.9291666666666667</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J76" s="20" t="s">
         <v>24</v>
@@ -14068,7 +14066,7 @@
         <v>1</v>
       </c>
       <c r="Y76" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" spans="1:25" s="15" customFormat="1" x14ac:dyDescent="0.4">
@@ -14079,7 +14077,7 @@
         <v>5</v>
       </c>
       <c r="L77" s="15" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M77" s="15" t="s">
         <v>6</v>
@@ -14105,10 +14103,10 @@
         <v>0.69861111111111107</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="J78" s="20" t="s">
         <v>35</v>
@@ -14126,7 +14124,7 @@
         <v>2</v>
       </c>
       <c r="Y78" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.4">
@@ -14137,10 +14135,10 @@
         <v>0.7</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J79" s="20" t="s">
         <v>24</v>
@@ -14170,7 +14168,7 @@
         <v>2</v>
       </c>
       <c r="Y79" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.4">
@@ -14181,10 +14179,10 @@
         <v>0.70277777777777772</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="J80" s="20" t="s">
         <v>21</v>
@@ -14202,7 +14200,7 @@
         <v>2</v>
       </c>
       <c r="Y80" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.4">
@@ -14213,13 +14211,13 @@
         <v>0.70972222222222225</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="J81" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P81">
         <v>3000</v>
@@ -14234,7 +14232,7 @@
         <v>2</v>
       </c>
       <c r="Y81" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.4">
@@ -14245,10 +14243,10 @@
         <v>0.71180555555555558</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="J82" s="20" t="s">
         <v>35</v>
@@ -14266,7 +14264,7 @@
         <v>2</v>
       </c>
       <c r="Y82" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.4">
@@ -14277,10 +14275,10 @@
         <v>0.71319444444444446</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="J83" s="20" t="s">
         <v>35</v>
@@ -14299,7 +14297,7 @@
         <v>2</v>
       </c>
       <c r="Y83" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.4">
@@ -14310,10 +14308,10 @@
         <v>0.71527777777777779</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J84" s="20" t="s">
         <v>24</v>
@@ -14344,7 +14342,7 @@
         <v>2</v>
       </c>
       <c r="Y84" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.4">
@@ -14355,10 +14353,10 @@
         <v>0.71875</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="J85" s="20" t="s">
         <v>21</v>
@@ -14376,7 +14374,7 @@
         <v>2</v>
       </c>
       <c r="Y85" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.4">
@@ -14387,10 +14385,10 @@
         <v>0.72152777777777777</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J86" s="20" t="s">
         <v>20</v>
@@ -14427,7 +14425,7 @@
         <v>2</v>
       </c>
       <c r="Y86" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.4">
@@ -14438,10 +14436,10 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="J87" s="20" t="s">
         <v>35</v>
@@ -14459,7 +14457,7 @@
         <v>2</v>
       </c>
       <c r="Y87" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.4">
@@ -14470,10 +14468,10 @@
         <v>0.73819444444444449</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="J88" s="20" t="s">
         <v>24</v>
@@ -14503,7 +14501,7 @@
         <v>2</v>
       </c>
       <c r="Y88" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.4">
@@ -14514,13 +14512,13 @@
         <v>0.74097222222222225</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J89" s="20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K89">
         <v>1190</v>
@@ -14554,7 +14552,7 @@
         <v>2</v>
       </c>
       <c r="Y89" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.4">
@@ -14565,13 +14563,13 @@
         <v>0.75</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="J90" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K90">
         <v>2900</v>
@@ -14595,7 +14593,7 @@
         <v>2</v>
       </c>
       <c r="Y90" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.4">
@@ -14606,13 +14604,13 @@
         <v>0.76111111111111107</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="J91" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K91">
         <v>2200</v>
@@ -14636,7 +14634,7 @@
         <v>2</v>
       </c>
       <c r="Y91" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.4">
@@ -14647,10 +14645,10 @@
         <v>0.7631944444444444</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="J92" s="20" t="s">
         <v>24</v>
@@ -14683,7 +14681,7 @@
         <v>2</v>
       </c>
       <c r="Y92" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.4">
@@ -14694,10 +14692,10 @@
         <v>0.77638888888888891</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="J93" s="20" t="s">
         <v>24</v>
@@ -14728,7 +14726,7 @@
         <v>2</v>
       </c>
       <c r="Y93" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.4">
@@ -14739,13 +14737,13 @@
         <v>0.77986111111111112</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="J94" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M94">
         <v>1600</v>
@@ -14766,7 +14764,7 @@
         <v>2</v>
       </c>
       <c r="Y94" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.4">
@@ -14777,13 +14775,13 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="J95" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P95">
         <f>1500/2</f>
@@ -14799,7 +14797,7 @@
         <v>2</v>
       </c>
       <c r="Y95" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.4">
@@ -14810,10 +14808,10 @@
         <v>0.78680555555555554</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="J96" s="20" t="s">
         <v>21</v>
@@ -14831,7 +14829,7 @@
         <v>2</v>
       </c>
       <c r="Y96" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.4">
@@ -14842,10 +14840,10 @@
         <v>0.79027777777777775</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="J97" s="20" t="s">
         <v>20</v>
@@ -14882,7 +14880,7 @@
         <v>2</v>
       </c>
       <c r="Y97" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.4">
@@ -14893,13 +14891,13 @@
         <v>0.8</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="J98" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L98">
         <v>900</v>
@@ -14920,7 +14918,7 @@
         <v>2</v>
       </c>
       <c r="Y98" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.4">
@@ -14931,10 +14929,10 @@
         <v>0.80138888888888893</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="J99" s="20" t="s">
         <v>35</v>
@@ -14952,7 +14950,7 @@
         <v>2</v>
       </c>
       <c r="Y99" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.4">
@@ -14963,10 +14961,10 @@
         <v>0.80972222222222223</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="J100" s="20" t="s">
         <v>24</v>
@@ -14987,7 +14985,7 @@
         <v>2</v>
       </c>
       <c r="Y100" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.4">
@@ -14998,10 +14996,10 @@
         <v>0.81666666666666665</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="J101" s="20" t="s">
         <v>24</v>
@@ -15032,7 +15030,7 @@
         <v>2</v>
       </c>
       <c r="Y101" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.4">
@@ -15043,10 +15041,10 @@
         <v>0.82222222222222219</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="J102" s="20" t="s">
         <v>21</v>
@@ -15064,7 +15062,7 @@
         <v>2</v>
       </c>
       <c r="Y102" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.4">
@@ -15075,10 +15073,10 @@
         <v>0.82708333333333328</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="J103" s="20" t="s">
         <v>24</v>
@@ -15112,7 +15110,7 @@
         <v>2</v>
       </c>
       <c r="Y103" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.4">
@@ -15123,10 +15121,10 @@
         <v>0.83819444444444446</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="J104" s="20" t="s">
         <v>35</v>
@@ -15147,7 +15145,7 @@
         <v>2</v>
       </c>
       <c r="Y104" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.4">
@@ -15158,13 +15156,13 @@
         <v>0.84027777777777779</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="J105" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K105">
         <v>2200</v>
@@ -15191,7 +15189,7 @@
         <v>2</v>
       </c>
       <c r="Y105" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.4">
@@ -15202,10 +15200,10 @@
         <v>0.84375</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="J106" s="20" t="s">
         <v>35</v>
@@ -15223,7 +15221,7 @@
         <v>2</v>
       </c>
       <c r="Y106" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.4">
@@ -15234,13 +15232,13 @@
         <v>0.85069444444444442</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="J107" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K107">
         <v>1290</v>
@@ -15274,7 +15272,7 @@
         <v>2</v>
       </c>
       <c r="Y107" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.4">
@@ -15285,10 +15283,10 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="J108" s="20" t="s">
         <v>35</v>
@@ -15306,7 +15304,7 @@
         <v>2</v>
       </c>
       <c r="Y108" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="109" spans="1:25" s="15" customFormat="1" x14ac:dyDescent="0.4">
@@ -15375,63 +15373,60 @@
     <hyperlink ref="D10" r:id="rId8" xr:uid="{3383D294-A08B-44D0-8231-2B1B470D1819}"/>
     <hyperlink ref="D11" r:id="rId9" xr:uid="{78EB432A-CAF2-42F1-A19A-DFDF0FC674FF}"/>
     <hyperlink ref="D12" r:id="rId10" xr:uid="{38BAB723-547E-4775-8E05-1455DDB50C13}"/>
-    <hyperlink ref="D13" r:id="rId11" xr:uid="{CF3C8BF2-0586-4C9B-9119-9A1A6A4E4623}"/>
-    <hyperlink ref="D14" r:id="rId12" xr:uid="{1604CFEE-3E60-45F4-B4F9-EC8B8486BDF4}"/>
-    <hyperlink ref="D15" r:id="rId13" xr:uid="{C8DE7F22-28D7-4602-95AC-801F4E941FB7}"/>
-    <hyperlink ref="D16" r:id="rId14" xr:uid="{F2D9FE1C-6398-44A6-9491-C044DD46A65C}"/>
-    <hyperlink ref="D17" r:id="rId15" xr:uid="{DCCF0236-2107-404F-A3E5-CD3E57714E88}"/>
-    <hyperlink ref="D18" r:id="rId16" xr:uid="{8769EE86-B3E7-42BB-95A2-18EC2708EB65}"/>
-    <hyperlink ref="D19" r:id="rId17" xr:uid="{1964888D-BB19-40EE-A00B-1BF8C31402B1}"/>
-    <hyperlink ref="D20" r:id="rId18" xr:uid="{2EF06C4F-F999-4751-9923-E85F89354A63}"/>
-    <hyperlink ref="D21" r:id="rId19" xr:uid="{203FA3FE-B7F3-484A-BCBA-BEC3B565D6B5}"/>
-    <hyperlink ref="D22" r:id="rId20" xr:uid="{4D958BAB-35F7-4887-97A9-DFFA19977D71}"/>
-    <hyperlink ref="D23" r:id="rId21" xr:uid="{6AB16552-E7D3-4185-9396-1F036B3B2CB9}"/>
-    <hyperlink ref="D24" r:id="rId22" xr:uid="{C0FE893A-6758-4A3A-B34D-E85BBC304FEB}"/>
-    <hyperlink ref="D25" r:id="rId23" xr:uid="{370D3FAC-EC09-4DD2-B9A9-2ABA305E87E7}"/>
-    <hyperlink ref="D26" r:id="rId24" xr:uid="{A70BD821-904A-4307-8694-92C33BB216EC}"/>
-    <hyperlink ref="D27" r:id="rId25" xr:uid="{D32D196B-EB3F-46A8-AECA-1F0CA8ED5A4B}"/>
-    <hyperlink ref="D28" r:id="rId26" xr:uid="{39C55308-8296-48BD-9799-32E3D30F8876}"/>
-    <hyperlink ref="D29" r:id="rId27" xr:uid="{95AEF57E-B47B-4ECA-B3EE-3548217A76B5}"/>
-    <hyperlink ref="D30" r:id="rId28" xr:uid="{7FCA1409-2A7F-48D9-B888-FD1AF00A1D54}"/>
-    <hyperlink ref="D31" r:id="rId29" xr:uid="{A3E654D2-3C80-4EDF-86EC-AAAC7B01DA30}"/>
-    <hyperlink ref="D32" r:id="rId30" xr:uid="{E456A4BD-870B-4F40-8838-ED171E1FF425}"/>
-    <hyperlink ref="D34" r:id="rId31" xr:uid="{7BD77EF0-8032-461F-9774-7E184E3DBCFB}"/>
-    <hyperlink ref="D35" r:id="rId32" xr:uid="{8E85B2A5-E8FA-4852-A1B2-D33E45EC6B39}"/>
-    <hyperlink ref="D37" r:id="rId33" xr:uid="{1EE51ECD-69AF-494B-8520-BD6261336C89}"/>
-    <hyperlink ref="D41" r:id="rId34" xr:uid="{CE6ABC30-A360-4542-9DEE-683C8DDB8042}"/>
-    <hyperlink ref="D42" r:id="rId35" xr:uid="{BAE7041E-15D3-4E82-ACB1-FE2CC2921852}"/>
-    <hyperlink ref="D43" r:id="rId36" xr:uid="{79146B76-70C1-4682-9B9F-6016826D45FD}"/>
-    <hyperlink ref="D46" r:id="rId37" xr:uid="{58BA3545-02BC-4641-B982-97D2A73CCD98}"/>
-    <hyperlink ref="D49" r:id="rId38" xr:uid="{9AC29BD2-ED28-46F7-9DF7-E7C149BB65EE}"/>
-    <hyperlink ref="D50" r:id="rId39" xr:uid="{EBF959DC-367B-4FA9-AA50-D57F9F44FEB1}"/>
-    <hyperlink ref="D51" r:id="rId40" xr:uid="{42A02AE0-AF1E-4A62-8F38-0FFD796C521C}"/>
-    <hyperlink ref="D52" r:id="rId41" xr:uid="{233C5DFE-BEC5-4DD5-A564-9A42403184CD}"/>
-    <hyperlink ref="D53" r:id="rId42" xr:uid="{998E828F-A35D-47B7-9AFC-8E53F6BA3F1C}"/>
-    <hyperlink ref="D54" r:id="rId43" xr:uid="{AFFED709-8239-4FA3-9121-E2ADCD0F842F}"/>
-    <hyperlink ref="D56" r:id="rId44" xr:uid="{C08F5748-5739-4F5F-B521-43C37C580D00}"/>
-    <hyperlink ref="D57" r:id="rId45" xr:uid="{71554D1B-F9B1-490D-9819-224DB54580DF}"/>
-    <hyperlink ref="D58" r:id="rId46" xr:uid="{9D65CD39-25FB-40D0-8C96-2E9EA3C4E94D}"/>
-    <hyperlink ref="D59" r:id="rId47" xr:uid="{4C0F0048-A8CF-4382-9173-B555B3A2BD17}"/>
-    <hyperlink ref="D60" r:id="rId48" xr:uid="{BFB3DAF1-00FA-40C7-9AFD-504413148B14}"/>
-    <hyperlink ref="D61" r:id="rId49" xr:uid="{3C153DC1-7651-48CC-B70A-BB8F96EBB412}"/>
-    <hyperlink ref="D62" r:id="rId50" xr:uid="{6A01D59A-0361-45B4-B8B7-C1616567C3ED}"/>
-    <hyperlink ref="D63" r:id="rId51" xr:uid="{4AA3E144-4131-432C-8D00-69EDE0E48BD6}"/>
-    <hyperlink ref="D64" r:id="rId52" xr:uid="{595BC966-A242-4E1A-B35E-593FB9F5DB81}"/>
-    <hyperlink ref="D65" r:id="rId53" xr:uid="{8DF8CB04-C5EE-4608-BC08-316B9162FE8B}"/>
-    <hyperlink ref="D66" r:id="rId54" xr:uid="{E320E887-2E4E-4A15-9487-623EF9E36775}"/>
-    <hyperlink ref="D67" r:id="rId55" xr:uid="{2970998B-B166-4E3A-8AC5-295C3A6133E2}"/>
-    <hyperlink ref="D68" r:id="rId56" xr:uid="{99D72668-62E1-414D-A8FD-5BE14E55D238}"/>
-    <hyperlink ref="D69" r:id="rId57" xr:uid="{435035DD-083E-4E25-AC57-BF43FAB00460}"/>
-    <hyperlink ref="D70" r:id="rId58" xr:uid="{86428C06-7AEE-42F5-B729-C598EBED08EF}"/>
-    <hyperlink ref="D71" r:id="rId59" xr:uid="{EBB633DA-3CD1-4421-B9C2-5CB3514A982B}"/>
-    <hyperlink ref="D72" r:id="rId60" xr:uid="{234F2EA6-1990-4DC2-AEA0-4BA7837870FB}"/>
-    <hyperlink ref="D73" r:id="rId61" xr:uid="{732D4B70-FD82-435E-B5AA-CB8078A5C21D}"/>
-    <hyperlink ref="D74" r:id="rId62" xr:uid="{E265A52B-005B-48BB-847F-D4C8925D1768}"/>
-    <hyperlink ref="D76" r:id="rId63" xr:uid="{BC6E1B13-50C4-4FD0-B155-CB1484A528AB}"/>
-    <hyperlink ref="D5" r:id="rId64" xr:uid="{2A3CDF9E-BC79-46F9-B457-42B761ACD097}"/>
-    <hyperlink ref="D38" r:id="rId65" xr:uid="{CBEC265E-2E7F-49F7-AFE2-B854546EC169}"/>
-    <hyperlink ref="D39" r:id="rId66" xr:uid="{8989D088-3173-4782-9CBD-DFD3278E91D3}"/>
-    <hyperlink ref="D40" r:id="rId67" xr:uid="{E57FB86E-B967-4E0B-8660-AFEF8245A911}"/>
+    <hyperlink ref="D14" r:id="rId11" xr:uid="{1604CFEE-3E60-45F4-B4F9-EC8B8486BDF4}"/>
+    <hyperlink ref="D15" r:id="rId12" xr:uid="{C8DE7F22-28D7-4602-95AC-801F4E941FB7}"/>
+    <hyperlink ref="D16" r:id="rId13" xr:uid="{F2D9FE1C-6398-44A6-9491-C044DD46A65C}"/>
+    <hyperlink ref="D17" r:id="rId14" xr:uid="{DCCF0236-2107-404F-A3E5-CD3E57714E88}"/>
+    <hyperlink ref="D18" r:id="rId15" xr:uid="{8769EE86-B3E7-42BB-95A2-18EC2708EB65}"/>
+    <hyperlink ref="D19" r:id="rId16" xr:uid="{1964888D-BB19-40EE-A00B-1BF8C31402B1}"/>
+    <hyperlink ref="D20" r:id="rId17" xr:uid="{2EF06C4F-F999-4751-9923-E85F89354A63}"/>
+    <hyperlink ref="D21" r:id="rId18" xr:uid="{203FA3FE-B7F3-484A-BCBA-BEC3B565D6B5}"/>
+    <hyperlink ref="D22" r:id="rId19" xr:uid="{4D958BAB-35F7-4887-97A9-DFFA19977D71}"/>
+    <hyperlink ref="D23" r:id="rId20" xr:uid="{6AB16552-E7D3-4185-9396-1F036B3B2CB9}"/>
+    <hyperlink ref="D24" r:id="rId21" xr:uid="{C0FE893A-6758-4A3A-B34D-E85BBC304FEB}"/>
+    <hyperlink ref="D25" r:id="rId22" xr:uid="{370D3FAC-EC09-4DD2-B9A9-2ABA305E87E7}"/>
+    <hyperlink ref="D26" r:id="rId23" xr:uid="{A70BD821-904A-4307-8694-92C33BB216EC}"/>
+    <hyperlink ref="D27" r:id="rId24" xr:uid="{D32D196B-EB3F-46A8-AECA-1F0CA8ED5A4B}"/>
+    <hyperlink ref="D28" r:id="rId25" xr:uid="{39C55308-8296-48BD-9799-32E3D30F8876}"/>
+    <hyperlink ref="D29" r:id="rId26" xr:uid="{95AEF57E-B47B-4ECA-B3EE-3548217A76B5}"/>
+    <hyperlink ref="D30" r:id="rId27" xr:uid="{7FCA1409-2A7F-48D9-B888-FD1AF00A1D54}"/>
+    <hyperlink ref="D31" r:id="rId28" xr:uid="{A3E654D2-3C80-4EDF-86EC-AAAC7B01DA30}"/>
+    <hyperlink ref="D32" r:id="rId29" xr:uid="{E456A4BD-870B-4F40-8838-ED171E1FF425}"/>
+    <hyperlink ref="D34" r:id="rId30" xr:uid="{7BD77EF0-8032-461F-9774-7E184E3DBCFB}"/>
+    <hyperlink ref="D37" r:id="rId31" xr:uid="{1EE51ECD-69AF-494B-8520-BD6261336C89}"/>
+    <hyperlink ref="D41" r:id="rId32" xr:uid="{CE6ABC30-A360-4542-9DEE-683C8DDB8042}"/>
+    <hyperlink ref="D42" r:id="rId33" xr:uid="{BAE7041E-15D3-4E82-ACB1-FE2CC2921852}"/>
+    <hyperlink ref="D43" r:id="rId34" xr:uid="{79146B76-70C1-4682-9B9F-6016826D45FD}"/>
+    <hyperlink ref="D46" r:id="rId35" xr:uid="{58BA3545-02BC-4641-B982-97D2A73CCD98}"/>
+    <hyperlink ref="D49" r:id="rId36" xr:uid="{9AC29BD2-ED28-46F7-9DF7-E7C149BB65EE}"/>
+    <hyperlink ref="D50" r:id="rId37" xr:uid="{EBF959DC-367B-4FA9-AA50-D57F9F44FEB1}"/>
+    <hyperlink ref="D52" r:id="rId38" xr:uid="{233C5DFE-BEC5-4DD5-A564-9A42403184CD}"/>
+    <hyperlink ref="D53" r:id="rId39" xr:uid="{998E828F-A35D-47B7-9AFC-8E53F6BA3F1C}"/>
+    <hyperlink ref="D54" r:id="rId40" xr:uid="{AFFED709-8239-4FA3-9121-E2ADCD0F842F}"/>
+    <hyperlink ref="D56" r:id="rId41" xr:uid="{C08F5748-5739-4F5F-B521-43C37C580D00}"/>
+    <hyperlink ref="D57" r:id="rId42" xr:uid="{71554D1B-F9B1-490D-9819-224DB54580DF}"/>
+    <hyperlink ref="D58" r:id="rId43" xr:uid="{9D65CD39-25FB-40D0-8C96-2E9EA3C4E94D}"/>
+    <hyperlink ref="D59" r:id="rId44" xr:uid="{4C0F0048-A8CF-4382-9173-B555B3A2BD17}"/>
+    <hyperlink ref="D60" r:id="rId45" xr:uid="{BFB3DAF1-00FA-40C7-9AFD-504413148B14}"/>
+    <hyperlink ref="D61" r:id="rId46" xr:uid="{3C153DC1-7651-48CC-B70A-BB8F96EBB412}"/>
+    <hyperlink ref="D62" r:id="rId47" xr:uid="{6A01D59A-0361-45B4-B8B7-C1616567C3ED}"/>
+    <hyperlink ref="D63" r:id="rId48" xr:uid="{4AA3E144-4131-432C-8D00-69EDE0E48BD6}"/>
+    <hyperlink ref="D64" r:id="rId49" xr:uid="{595BC966-A242-4E1A-B35E-593FB9F5DB81}"/>
+    <hyperlink ref="D65" r:id="rId50" xr:uid="{8DF8CB04-C5EE-4608-BC08-316B9162FE8B}"/>
+    <hyperlink ref="D66" r:id="rId51" xr:uid="{E320E887-2E4E-4A15-9487-623EF9E36775}"/>
+    <hyperlink ref="D67" r:id="rId52" xr:uid="{2970998B-B166-4E3A-8AC5-295C3A6133E2}"/>
+    <hyperlink ref="D68" r:id="rId53" xr:uid="{99D72668-62E1-414D-A8FD-5BE14E55D238}"/>
+    <hyperlink ref="D69" r:id="rId54" xr:uid="{435035DD-083E-4E25-AC57-BF43FAB00460}"/>
+    <hyperlink ref="D70" r:id="rId55" xr:uid="{86428C06-7AEE-42F5-B729-C598EBED08EF}"/>
+    <hyperlink ref="D71" r:id="rId56" xr:uid="{EBB633DA-3CD1-4421-B9C2-5CB3514A982B}"/>
+    <hyperlink ref="D72" r:id="rId57" xr:uid="{234F2EA6-1990-4DC2-AEA0-4BA7837870FB}"/>
+    <hyperlink ref="D73" r:id="rId58" xr:uid="{732D4B70-FD82-435E-B5AA-CB8078A5C21D}"/>
+    <hyperlink ref="D74" r:id="rId59" xr:uid="{E265A52B-005B-48BB-847F-D4C8925D1768}"/>
+    <hyperlink ref="D76" r:id="rId60" xr:uid="{BC6E1B13-50C4-4FD0-B155-CB1484A528AB}"/>
+    <hyperlink ref="D5" r:id="rId61" xr:uid="{2A3CDF9E-BC79-46F9-B457-42B761ACD097}"/>
+    <hyperlink ref="D38" r:id="rId62" xr:uid="{CBEC265E-2E7F-49F7-AFE2-B854546EC169}"/>
+    <hyperlink ref="D39" r:id="rId63" xr:uid="{8989D088-3173-4782-9CBD-DFD3278E91D3}"/>
+    <hyperlink ref="D40" r:id="rId64" xr:uid="{E57FB86E-B967-4E0B-8660-AFEF8245A911}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -15461,19 +15456,19 @@
   <sheetData>
     <row r="1" spans="1:26" s="4" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -15494,7 +15489,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
@@ -15524,16 +15519,16 @@
         <v>14</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Z1" s="3" t="s">
         <v>16</v>
@@ -15547,10 +15542,10 @@
         <v>0.75069444444444444</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J2" t="s">
         <v>35</v>
@@ -15568,7 +15563,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.4">
@@ -15579,10 +15574,10 @@
         <v>0.80138888888888893</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="J3" t="s">
         <v>35</v>
@@ -15600,7 +15595,7 @@
         <v>2</v>
       </c>
       <c r="Y3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -15617,10 +15612,10 @@
         <v>0.74583333333333335</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J5" t="s">
         <v>24</v>
@@ -15650,7 +15645,7 @@
         <v>1</v>
       </c>
       <c r="Y5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.4">
@@ -15661,10 +15656,10 @@
         <v>0.77638888888888891</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="J6" t="s">
         <v>24</v>
@@ -15695,7 +15690,7 @@
         <v>2</v>
       </c>
       <c r="Y6" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -15728,13 +15723,13 @@
         <v>0.91249999999999998</v>
       </c>
       <c r="C8" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P8">
         <v>725</v>
@@ -15749,7 +15744,7 @@
         <v>1</v>
       </c>
       <c r="Y8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.4">
@@ -15760,13 +15755,13 @@
         <v>0.78472222222222221</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="J9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P9">
         <f>1500/2</f>
@@ -15782,7 +15777,7 @@
         <v>2</v>
       </c>
       <c r="Y9" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -15799,13 +15794,13 @@
         <v>0.75972222222222219</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" t="s">
         <v>58</v>
-      </c>
-      <c r="J11" t="s">
-        <v>59</v>
       </c>
       <c r="K11">
         <v>2100</v>
@@ -15820,7 +15815,7 @@
         <v>5200</v>
       </c>
       <c r="U11" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="V11" t="s">
         <v>26</v>
@@ -15832,7 +15827,7 @@
         <v>1</v>
       </c>
       <c r="Y11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.4">
@@ -15843,13 +15838,13 @@
         <v>0.75</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="J12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K12">
         <v>2900</v>
@@ -15873,7 +15868,7 @@
         <v>2</v>
       </c>
       <c r="Y12" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -15902,10 +15897,10 @@
         <v>0.91041666666666665</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J14" t="s">
         <v>21</v>
@@ -15923,7 +15918,7 @@
         <v>1</v>
       </c>
       <c r="Y14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.4">
@@ -15934,10 +15929,10 @@
         <v>0.78680555555555554</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="J15" t="s">
         <v>21</v>
@@ -15955,7 +15950,7 @@
         <v>2</v>
       </c>
       <c r="Y15" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -15972,13 +15967,13 @@
         <v>0.92291666666666672</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K17">
         <v>1600</v>
@@ -16005,7 +16000,7 @@
         <v>1</v>
       </c>
       <c r="Y17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.4">
@@ -16016,10 +16011,10 @@
         <v>0.71527777777777779</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J18" t="s">
         <v>24</v>
@@ -16050,7 +16045,7 @@
         <v>2</v>
       </c>
       <c r="Y18" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -16083,10 +16078,10 @@
         <v>0.92569444444444449</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J20" t="s">
         <v>35</v>
@@ -16104,7 +16099,7 @@
         <v>1</v>
       </c>
       <c r="Y20" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.4">
@@ -16115,10 +16110,10 @@
         <v>0.71319444444444446</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="J21" t="s">
         <v>35</v>
@@ -16137,7 +16132,7 @@
         <v>2</v>
       </c>
       <c r="Y21" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -16154,10 +16149,10 @@
         <v>0.92638888888888893</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J23" t="s">
         <v>35</v>
@@ -16175,7 +16170,7 @@
         <v>1</v>
       </c>
       <c r="Y23" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.4">
@@ -16186,10 +16181,10 @@
         <v>0.71180555555555558</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="J24" t="s">
         <v>35</v>
@@ -16207,7 +16202,7 @@
         <v>2</v>
       </c>
       <c r="Y24" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.4">
@@ -16224,10 +16219,10 @@
         <v>0.84652777777777777</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J26" s="20" t="s">
         <v>35</v>
@@ -16245,7 +16240,7 @@
         <v>1</v>
       </c>
       <c r="Y26" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.4">
@@ -16256,10 +16251,10 @@
         <v>0.84375</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="J27" s="20" t="s">
         <v>35</v>
@@ -16277,7 +16272,7 @@
         <v>2</v>
       </c>
       <c r="Y27" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
@@ -16322,12 +16317,12 @@
     <row r="37" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
     <row r="38" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A38" s="18" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.4">
       <c r="L39" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="P39">
         <f>MEDIAN(Q39:Q57)</f>
@@ -16474,17 +16469,17 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B3" t="str">
         <f>CONCATENATE("POINT(",RIGHT(A3,10), " ",LEFT(A3,10),")")</f>
@@ -16493,7 +16488,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B31" si="0">CONCATENATE("POINT(",RIGHT(A4,10), " ",LEFT(A4,10),")")</f>
@@ -16502,7 +16497,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="0"/>
@@ -16511,7 +16506,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="0"/>
@@ -16520,7 +16515,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="0"/>
@@ -16529,7 +16524,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="0"/>
@@ -16538,7 +16533,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="0"/>
@@ -16547,7 +16542,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="0"/>
@@ -16556,7 +16551,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
@@ -16565,7 +16560,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="0"/>
@@ -16574,7 +16569,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="0"/>
@@ -16583,7 +16578,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="0"/>
@@ -16592,7 +16587,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="0"/>
@@ -16601,7 +16596,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="0"/>
@@ -16610,7 +16605,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="0"/>
@@ -16619,7 +16614,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="0"/>
@@ -16628,7 +16623,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="0"/>
@@ -16637,7 +16632,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="0"/>
@@ -16646,7 +16641,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="0"/>
@@ -16655,7 +16650,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="0"/>
@@ -16664,7 +16659,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="0"/>
@@ -16673,7 +16668,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="0"/>
@@ -16682,7 +16677,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="0"/>
@@ -16691,7 +16686,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="0"/>
@@ -16700,7 +16695,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="0"/>
@@ -16709,7 +16704,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="0"/>
@@ -16718,7 +16713,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="0"/>
@@ -16727,7 +16722,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="0"/>
@@ -16736,7 +16731,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="0"/>

--- a/data/comercios_territorio_sp.xlsx
+++ b/data/comercios_territorio_sp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\as\Documents\00_TESIS\meu_tesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908E9323-74C0-4ADD-8F51-70F272A4DD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0FB5A6-5091-4DBB-98CA-0F1A71830E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{7FC3CCF3-7BCA-42E8-BEEE-4B41A7F93BBF}"/>
   </bookViews>
@@ -2637,7 +2637,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2680,8 +2680,6 @@
     <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -3545,7 +3543,7 @@
         <v>1000</v>
       </c>
       <c r="O11" s="21"/>
-      <c r="P11" s="22">
+      <c r="P11" s="21">
         <v>1000</v>
       </c>
       <c r="Q11" s="21"/>
@@ -3585,7 +3583,7 @@
       <c r="O12" s="21">
         <v>1000</v>
       </c>
-      <c r="P12" s="22"/>
+      <c r="P12" s="21"/>
       <c r="Q12" s="21"/>
       <c r="V12" t="s">
         <v>26</v>
@@ -3625,7 +3623,7 @@
       </c>
       <c r="N13" s="21"/>
       <c r="O13" s="21"/>
-      <c r="P13" s="22">
+      <c r="P13" s="21">
         <v>1300</v>
       </c>
       <c r="Q13" s="21"/>
@@ -3673,7 +3671,7 @@
       <c r="O14" s="21">
         <v>590</v>
       </c>
-      <c r="P14" s="22">
+      <c r="P14" s="21">
         <v>2410</v>
       </c>
       <c r="Q14" s="21">
@@ -3717,7 +3715,7 @@
       <c r="O15" s="21">
         <v>1000</v>
       </c>
-      <c r="P15" s="22"/>
+      <c r="P15" s="21"/>
       <c r="Q15" s="21"/>
       <c r="V15" t="s">
         <v>26</v>
@@ -3763,7 +3761,7 @@
       <c r="O16" s="21">
         <v>1490</v>
       </c>
-      <c r="P16" s="22">
+      <c r="P16" s="21">
         <v>1785</v>
       </c>
       <c r="Q16" s="21">
@@ -3811,7 +3809,7 @@
         <v>2600</v>
       </c>
       <c r="O17" s="21"/>
-      <c r="P17" s="22">
+      <c r="P17" s="21">
         <v>1035</v>
       </c>
       <c r="Q17" s="21"/>
@@ -3853,7 +3851,7 @@
       <c r="O18" s="21">
         <v>900</v>
       </c>
-      <c r="P18" s="22">
+      <c r="P18" s="21">
         <v>1742</v>
       </c>
       <c r="Q18" s="21"/>
@@ -3901,7 +3899,7 @@
       <c r="O19" s="21">
         <v>1490</v>
       </c>
-      <c r="P19" s="22">
+      <c r="P19" s="21">
         <v>1785</v>
       </c>
       <c r="Q19" s="21">
@@ -3951,7 +3949,7 @@
       <c r="O20" s="21">
         <v>1000</v>
       </c>
-      <c r="P20" s="22">
+      <c r="P20" s="21">
         <v>1600</v>
       </c>
       <c r="Q20" s="21">
@@ -3993,7 +3991,7 @@
       <c r="O21" s="21">
         <v>1000</v>
       </c>
-      <c r="P21" s="22"/>
+      <c r="P21" s="21"/>
       <c r="Q21" s="21"/>
       <c r="V21" t="s">
         <v>26</v>
@@ -4039,7 +4037,7 @@
       <c r="O22" s="21">
         <v>590</v>
       </c>
-      <c r="P22" s="22">
+      <c r="P22" s="21">
         <v>2145</v>
       </c>
       <c r="Q22" s="21">
@@ -4083,7 +4081,7 @@
         <v>1800</v>
       </c>
       <c r="O23" s="21"/>
-      <c r="P23" s="22"/>
+      <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
       <c r="V23" t="s">
         <v>26</v>
@@ -4121,7 +4119,7 @@
       <c r="O24" s="21">
         <v>800</v>
       </c>
-      <c r="P24" s="22"/>
+      <c r="P24" s="21"/>
       <c r="Q24" s="21"/>
       <c r="V24" t="s">
         <v>26</v>
@@ -4161,7 +4159,7 @@
         <v>2000</v>
       </c>
       <c r="O25" s="21"/>
-      <c r="P25" s="22"/>
+      <c r="P25" s="21"/>
       <c r="Q25" s="21"/>
       <c r="V25" t="s">
         <v>26</v>
@@ -4255,7 +4253,7 @@
         <v>1500</v>
       </c>
       <c r="Q27" s="21">
-        <v>900</v>
+        <v>9000</v>
       </c>
       <c r="V27" t="s">
         <v>26</v>
@@ -6984,7 +6982,7 @@
       </c>
       <c r="N91" s="21"/>
       <c r="O91" s="21"/>
-      <c r="P91" s="22">
+      <c r="P91" s="21">
         <v>1300</v>
       </c>
       <c r="Q91" s="21"/>
@@ -7254,7 +7252,7 @@
       <c r="O97" s="21">
         <v>1000</v>
       </c>
-      <c r="P97" s="22"/>
+      <c r="P97" s="21"/>
       <c r="Q97" s="21"/>
       <c r="V97" t="s">
         <v>26</v>
@@ -7374,7 +7372,7 @@
       <c r="D101" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="J101" s="23" t="s">
+      <c r="J101" t="s">
         <v>58</v>
       </c>
       <c r="K101" s="21">
@@ -7420,7 +7418,7 @@
       <c r="D102" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="J102" s="23" t="s">
+      <c r="J102" t="s">
         <v>21</v>
       </c>
       <c r="K102" s="21"/>
@@ -7458,7 +7456,7 @@
       <c r="D103" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="J103" s="23" t="s">
+      <c r="J103" t="s">
         <v>87</v>
       </c>
       <c r="K103" s="21"/>
@@ -7496,7 +7494,7 @@
       <c r="D104" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="J104" s="23" t="s">
+      <c r="J104" t="s">
         <v>37</v>
       </c>
       <c r="K104" s="21">
@@ -7546,7 +7544,7 @@
       <c r="D105" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="J105" s="23" t="s">
+      <c r="J105" t="s">
         <v>35</v>
       </c>
       <c r="K105" s="21"/>
@@ -7584,7 +7582,7 @@
       <c r="D106" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="J106" s="23" t="s">
+      <c r="J106" t="s">
         <v>21</v>
       </c>
       <c r="K106" s="21"/>
@@ -7622,7 +7620,7 @@
       <c r="D107" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="J107" s="23" t="s">
+      <c r="J107" t="s">
         <v>47</v>
       </c>
       <c r="K107" s="21">
@@ -7672,7 +7670,7 @@
       <c r="D108" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="J108" s="23" t="s">
+      <c r="J108" t="s">
         <v>35</v>
       </c>
       <c r="K108" s="21"/>
@@ -7710,7 +7708,7 @@
       <c r="D109" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="J109" s="23" t="s">
+      <c r="J109" t="s">
         <v>20</v>
       </c>
       <c r="K109" s="21">
@@ -7760,7 +7758,7 @@
       <c r="D110" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="J110" s="23" t="s">
+      <c r="J110" t="s">
         <v>47</v>
       </c>
       <c r="K110" s="21">
@@ -7810,7 +7808,7 @@
       <c r="D111" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="J111" s="23" t="s">
+      <c r="J111" t="s">
         <v>47</v>
       </c>
       <c r="K111" s="21">
@@ -7860,7 +7858,7 @@
       <c r="D112" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="J112" s="23" t="s">
+      <c r="J112" t="s">
         <v>20</v>
       </c>
       <c r="K112" s="21">
@@ -7910,7 +7908,7 @@
       <c r="D113" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="J113" s="23" t="s">
+      <c r="J113" t="s">
         <v>47</v>
       </c>
       <c r="K113" s="21">
@@ -7960,7 +7958,7 @@
       <c r="D114" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="J114" s="23" t="s">
+      <c r="J114" t="s">
         <v>87</v>
       </c>
       <c r="K114" s="21"/>
@@ -7998,7 +7996,7 @@
       <c r="D115" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="J115" s="23" t="s">
+      <c r="J115" t="s">
         <v>21</v>
       </c>
       <c r="K115" s="21"/>
@@ -8036,7 +8034,7 @@
       <c r="D116" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="J116" s="23" t="s">
+      <c r="J116" t="s">
         <v>35</v>
       </c>
       <c r="K116" s="21"/>
@@ -8074,7 +8072,7 @@
       <c r="D117" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="J117" s="23" t="s">
+      <c r="J117" t="s">
         <v>21</v>
       </c>
       <c r="K117" s="21"/>
@@ -8112,7 +8110,7 @@
       <c r="D118" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="J118" s="23" t="s">
+      <c r="J118" t="s">
         <v>20</v>
       </c>
       <c r="K118" s="21">
@@ -8162,7 +8160,7 @@
       <c r="D119" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="J119" s="23" t="s">
+      <c r="J119" t="s">
         <v>87</v>
       </c>
       <c r="K119" s="21"/>
@@ -8200,7 +8198,7 @@
       <c r="D120" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="J120" s="23" t="s">
+      <c r="J120" t="s">
         <v>35</v>
       </c>
       <c r="K120" s="21"/>
@@ -8242,7 +8240,7 @@
       <c r="D122" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="J122" s="23" t="s">
+      <c r="J122" t="s">
         <v>20</v>
       </c>
       <c r="K122" s="21">
@@ -8292,7 +8290,7 @@
       <c r="D123" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="J123" s="23" t="s">
+      <c r="J123" t="s">
         <v>47</v>
       </c>
       <c r="K123" s="21"/>
@@ -8334,7 +8332,7 @@
       <c r="D124" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="J124" s="23" t="s">
+      <c r="J124" t="s">
         <v>47</v>
       </c>
       <c r="K124" s="21">
@@ -8380,7 +8378,7 @@
       <c r="D125" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="J125" s="23" t="s">
+      <c r="J125" t="s">
         <v>20</v>
       </c>
       <c r="K125" s="21">
@@ -8430,7 +8428,7 @@
       <c r="D126" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="J126" s="23" t="s">
+      <c r="J126" t="s">
         <v>35</v>
       </c>
       <c r="O126" s="21">
@@ -8456,7 +8454,7 @@
       <c r="D127" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="J127" s="23" t="s">
+      <c r="J127" t="s">
         <v>502</v>
       </c>
       <c r="K127" s="21">
@@ -8506,7 +8504,7 @@
       <c r="D128" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="J128" s="23" t="s">
+      <c r="J128" t="s">
         <v>47</v>
       </c>
       <c r="K128" s="21">
@@ -8522,7 +8520,7 @@
         <v>1000</v>
       </c>
       <c r="O128" s="21"/>
-      <c r="P128" s="22">
+      <c r="P128" s="21">
         <v>1000</v>
       </c>
       <c r="Q128" s="21"/>
@@ -8552,7 +8550,7 @@
       <c r="D129" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="J129" s="23" t="s">
+      <c r="J129" t="s">
         <v>47</v>
       </c>
       <c r="K129" s="21">
@@ -8570,7 +8568,7 @@
       <c r="O129" s="21">
         <v>1000</v>
       </c>
-      <c r="P129" s="22">
+      <c r="P129" s="21">
         <v>1600</v>
       </c>
       <c r="Q129" s="21">
@@ -8602,7 +8600,7 @@
       <c r="D130" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="J130" s="23" t="s">
+      <c r="J130" t="s">
         <v>47</v>
       </c>
       <c r="K130" s="21"/>
@@ -8622,7 +8620,7 @@
         <v>1500</v>
       </c>
       <c r="Q130" s="21">
-        <v>900</v>
+        <v>9000</v>
       </c>
       <c r="V130" t="s">
         <v>26</v>
@@ -8650,7 +8648,7 @@
       <c r="D131" s="8" t="s">
         <v>510</v>
       </c>
-      <c r="J131" s="23" t="s">
+      <c r="J131" t="s">
         <v>20</v>
       </c>
       <c r="K131" s="21">
@@ -8700,7 +8698,7 @@
       <c r="D132" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="J132" s="23" t="s">
+      <c r="J132" t="s">
         <v>47</v>
       </c>
       <c r="K132" s="21">
@@ -8748,7 +8746,7 @@
       <c r="D133" s="8" t="s">
         <v>514</v>
       </c>
-      <c r="J133" s="23" t="s">
+      <c r="J133" t="s">
         <v>20</v>
       </c>
       <c r="K133" s="21">
@@ -8798,7 +8796,7 @@
       <c r="D134" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="J134" s="23" t="s">
+      <c r="J134" t="s">
         <v>20</v>
       </c>
       <c r="K134" s="21">
@@ -8848,7 +8846,7 @@
       <c r="D135" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="J135" s="23" t="s">
+      <c r="J135" t="s">
         <v>47</v>
       </c>
       <c r="K135" s="21">
@@ -8894,7 +8892,7 @@
       <c r="D136" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="J136" s="23" t="s">
+      <c r="J136" t="s">
         <v>58</v>
       </c>
       <c r="K136" s="21">
@@ -8939,7 +8937,7 @@
       <c r="D137" s="8" t="s">
         <v>528</v>
       </c>
-      <c r="J137" s="23" t="s">
+      <c r="J137" t="s">
         <v>20</v>
       </c>
       <c r="K137" s="21">
@@ -8989,7 +8987,7 @@
       <c r="D138" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="J138" s="23" t="s">
+      <c r="J138" t="s">
         <v>37</v>
       </c>
       <c r="K138" s="21">
@@ -9007,7 +9005,7 @@
       <c r="O138" s="21">
         <v>590</v>
       </c>
-      <c r="P138" s="22">
+      <c r="P138" s="21">
         <v>2145</v>
       </c>
       <c r="Q138" s="21">
@@ -9039,7 +9037,7 @@
       <c r="D139" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J139" s="23" t="s">
+      <c r="J139" t="s">
         <v>47</v>
       </c>
       <c r="K139" s="21">
@@ -9085,7 +9083,7 @@
       <c r="D140" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="J140" s="23" t="s">
+      <c r="J140" t="s">
         <v>47</v>
       </c>
       <c r="K140" s="21">
@@ -9133,7 +9131,7 @@
       <c r="D141" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="J141" s="23" t="s">
+      <c r="J141" t="s">
         <v>35</v>
       </c>
       <c r="O141" s="21">
@@ -9159,7 +9157,7 @@
       <c r="D142" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="J142" s="23" t="s">
+      <c r="J142" t="s">
         <v>20</v>
       </c>
       <c r="K142" s="21">
@@ -9209,7 +9207,7 @@
       <c r="D143" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="J143" s="23" t="s">
+      <c r="J143" t="s">
         <v>35</v>
       </c>
       <c r="O143" s="21">
@@ -9235,7 +9233,7 @@
       <c r="D144" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="J144" s="23" t="s">
+      <c r="J144" t="s">
         <v>20</v>
       </c>
       <c r="K144" s="21">
@@ -9285,7 +9283,7 @@
       <c r="D145" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="J145" s="23" t="s">
+      <c r="J145" t="s">
         <v>37</v>
       </c>
       <c r="K145" s="21">
@@ -9303,7 +9301,7 @@
       <c r="O145" s="21">
         <v>590</v>
       </c>
-      <c r="P145" s="22">
+      <c r="P145" s="21">
         <v>2145</v>
       </c>
       <c r="Q145" s="21">
@@ -9335,7 +9333,7 @@
       <c r="D146" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="J146" s="23" t="s">
+      <c r="J146" t="s">
         <v>47</v>
       </c>
       <c r="K146" s="21"/>
@@ -9347,7 +9345,7 @@
       </c>
       <c r="N146" s="21"/>
       <c r="O146" s="21"/>
-      <c r="P146" s="22">
+      <c r="P146" s="21">
         <v>1300</v>
       </c>
       <c r="Q146" s="21"/>
@@ -9377,7 +9375,7 @@
       <c r="D147" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="J147" s="23" t="s">
+      <c r="J147" t="s">
         <v>35</v>
       </c>
       <c r="O147" s="21">
@@ -9403,7 +9401,7 @@
       <c r="D148" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="J148" s="23" t="s">
+      <c r="J148" t="s">
         <v>47</v>
       </c>
       <c r="K148" s="21"/>
@@ -9415,7 +9413,7 @@
       <c r="O148" s="21">
         <v>1000</v>
       </c>
-      <c r="P148" s="22"/>
+      <c r="P148" s="21"/>
       <c r="Q148" s="21"/>
       <c r="V148" t="s">
         <v>26</v>
@@ -9443,7 +9441,7 @@
       <c r="D149" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="J149" s="23" t="s">
+      <c r="J149" t="s">
         <v>37</v>
       </c>
       <c r="K149" s="21">
@@ -9461,7 +9459,7 @@
       <c r="O149" s="21">
         <v>590</v>
       </c>
-      <c r="P149" s="22">
+      <c r="P149" s="21">
         <v>2145</v>
       </c>
       <c r="Q149" s="21">
@@ -9493,7 +9491,7 @@
       <c r="D150" s="8" t="s">
         <v>566</v>
       </c>
-      <c r="J150" s="23" t="s">
+      <c r="J150" t="s">
         <v>60</v>
       </c>
       <c r="K150" s="21">
@@ -9687,7 +9685,7 @@
         <v>2600</v>
       </c>
       <c r="O155" s="21"/>
-      <c r="P155" s="22">
+      <c r="P155" s="21">
         <v>1035</v>
       </c>
       <c r="Q155" s="21"/>
@@ -9837,7 +9835,7 @@
       <c r="O159" s="21">
         <v>590</v>
       </c>
-      <c r="P159" s="22">
+      <c r="P159" s="21">
         <v>2145</v>
       </c>
       <c r="Q159" s="21">
@@ -9881,7 +9879,7 @@
         <v>1800</v>
       </c>
       <c r="O160" s="21"/>
-      <c r="P160" s="22"/>
+      <c r="P160" s="21"/>
       <c r="Q160" s="21"/>
       <c r="V160" t="s">
         <v>26</v>
@@ -10099,7 +10097,7 @@
         <v>2000</v>
       </c>
       <c r="O166" s="21"/>
-      <c r="P166" s="22"/>
+      <c r="P166" s="21"/>
       <c r="Q166" s="21"/>
       <c r="V166" t="s">
         <v>26</v>
@@ -11183,7 +11181,7 @@
       </c>
       <c r="N13" s="21"/>
       <c r="O13" s="21"/>
-      <c r="P13" s="22">
+      <c r="P13" s="21">
         <v>1300</v>
       </c>
       <c r="Q13" s="21"/>
@@ -11231,7 +11229,7 @@
       <c r="O14" s="21">
         <v>590</v>
       </c>
-      <c r="P14" s="22">
+      <c r="P14" s="21">
         <v>2410</v>
       </c>
       <c r="Q14" s="21">
@@ -11275,7 +11273,7 @@
       <c r="O15" s="21">
         <v>1000</v>
       </c>
-      <c r="P15" s="22"/>
+      <c r="P15" s="21"/>
       <c r="Q15" s="21"/>
       <c r="V15" t="s">
         <v>26</v>
@@ -11321,7 +11319,7 @@
       <c r="O16" s="21">
         <v>1490</v>
       </c>
-      <c r="P16" s="22">
+      <c r="P16" s="21">
         <v>1785</v>
       </c>
       <c r="Q16" s="21">
@@ -11369,7 +11367,7 @@
         <v>2600</v>
       </c>
       <c r="O17" s="21"/>
-      <c r="P17" s="22">
+      <c r="P17" s="21">
         <v>1035</v>
       </c>
       <c r="Q17" s="21"/>
@@ -11411,7 +11409,7 @@
       <c r="O18" s="21">
         <v>900</v>
       </c>
-      <c r="P18" s="22">
+      <c r="P18" s="21">
         <v>1742</v>
       </c>
       <c r="Q18" s="21"/>
@@ -11459,7 +11457,7 @@
       <c r="O19" s="21">
         <v>1490</v>
       </c>
-      <c r="P19" s="22">
+      <c r="P19" s="21">
         <v>1785</v>
       </c>
       <c r="Q19" s="21">
@@ -11509,7 +11507,7 @@
       <c r="O20" s="21">
         <v>1000</v>
       </c>
-      <c r="P20" s="22">
+      <c r="P20" s="21">
         <v>1600</v>
       </c>
       <c r="Q20" s="21">
@@ -11551,7 +11549,7 @@
       <c r="O21" s="21">
         <v>1000</v>
       </c>
-      <c r="P21" s="22"/>
+      <c r="P21" s="21"/>
       <c r="Q21" s="21"/>
       <c r="V21" t="s">
         <v>26</v>
@@ -11597,7 +11595,7 @@
       <c r="O22" s="21">
         <v>590</v>
       </c>
-      <c r="P22" s="22">
+      <c r="P22" s="21">
         <v>2145</v>
       </c>
       <c r="Q22" s="21">
@@ -31828,7 +31826,7 @@
     </row>
     <row r="5" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="L5" s="5">
-        <f t="shared" ref="K5:O5" si="0">L3/L4</f>
+        <f t="shared" ref="L5:O5" si="0">L3/L4</f>
         <v>0.46153846153846156</v>
       </c>
       <c r="M5" s="5">
@@ -32626,7 +32624,7 @@
     </row>
     <row r="26" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="L26" s="5">
-        <f t="shared" ref="K26:O26" si="8">L24/L25</f>
+        <f t="shared" ref="L26:O26" si="8">L24/L25</f>
         <v>0.46153846153846156</v>
       </c>
       <c r="M26" s="5">
